--- a/workbooks/urbanization-ru-1897.xlsx
+++ b/workbooks/urbanization-ru-1897.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0245FE02-8229-4C8C-82CD-9C878370536F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF2B5F1-AC5C-45F3-8D8B-7C0EE9BF997A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -612,13 +612,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -639,6 +632,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -946,7 +946,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>124</v>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="18.75">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="21" t="s">
         <v>125</v>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="18.75">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="21" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1095,123 +1095,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
     </row>
     <row r="2" spans="1:32" ht="24.95" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="14" t="s">
+      <c r="A2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
     </row>
     <row r="3" spans="1:32" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14" t="s">
+      <c r="G3" s="25"/>
+      <c r="H3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14" t="s">
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="14" t="s">
+      <c r="K3" s="25"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14" t="s">
+      <c r="N3" s="25"/>
+      <c r="O3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14" t="s">
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14" t="s">
+      <c r="R3" s="25"/>
+      <c r="S3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14" t="s">
+      <c r="T3" s="25"/>
+      <c r="U3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14" t="s">
+      <c r="V3" s="25"/>
+      <c r="W3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="X3" s="14"/>
-      <c r="Z3" s="22" t="s">
+      <c r="X3" s="25"/>
+      <c r="Z3" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="AB3" s="25" t="s">
+      <c r="AB3" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="AC3" s="25"/>
-      <c r="AE3" s="25" t="s">
+      <c r="AC3" s="22"/>
+      <c r="AE3" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="AF3" s="25"/>
+      <c r="AF3" s="22"/>
     </row>
     <row r="4" spans="1:32" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="1"/>
@@ -1245,7 +1245,7 @@
       <c r="K4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="16"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="2" t="s">
         <v>13</v>
       </c>
@@ -1282,19 +1282,19 @@
       <c r="X4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Z4" s="22" t="s">
+      <c r="Z4" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="AB4" s="22" t="s">
+      <c r="AB4" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="AC4" s="22" t="s">
+      <c r="AC4" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="AE4" s="22" t="s">
+      <c r="AE4" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="AF4" s="22" t="s">
+      <c r="AF4" s="19" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1369,22 +1369,22 @@
       <c r="X5" s="4">
         <v>269669</v>
       </c>
-      <c r="Z5" s="21">
+      <c r="Z5" s="18">
         <v>125640021</v>
       </c>
-      <c r="AB5" s="21">
+      <c r="AB5" s="18">
         <f>N(C5)+N(E5)+N(G5)+N(I5)+N(K5)+N(N5)+N(P5)+N(R5)+N(T5)+N(V5)+N(X5)</f>
         <v>39644133</v>
       </c>
-      <c r="AC5" s="21">
+      <c r="AC5" s="18">
         <f>N(I5)+N(K5)+N(X5)</f>
         <v>11806368</v>
       </c>
-      <c r="AE5" s="23">
+      <c r="AE5" s="20">
         <f>AB5/Z5*100</f>
         <v>31.553745919860997</v>
       </c>
-      <c r="AF5" s="23">
+      <c r="AF5" s="20">
         <f>AC5/Z5*100</f>
         <v>9.3969802822621311</v>
       </c>
@@ -1420,92 +1420,92 @@
         <v>111</v>
       </c>
       <c r="B7" s="4">
-        <f>B8-B9</f>
+        <f t="shared" ref="B7:K7" si="0">B8-B9</f>
         <v>0</v>
       </c>
       <c r="C7" s="4">
-        <f>C8-C9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <f>D8-D9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <f>E8-E9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F7" s="4">
-        <f>F8-F9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f>G8-G9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f>H8-H9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I7" s="4">
-        <f>I8-I9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J7" s="4">
-        <f>J8-J9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K7" s="4">
-        <f>K8-K9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4">
-        <f>M8-M9</f>
+        <f t="shared" ref="M7:X7" si="1">M8-M9</f>
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <f>N8-N9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O7" s="4">
-        <f>O8-O9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P7" s="4">
-        <f>P8-P9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q7" s="4">
-        <f>Q8-Q9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R7" s="4">
-        <f>R8-R9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S7" s="4">
-        <f>S8-S9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T7" s="4">
-        <f>T8-T9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U7" s="4">
-        <f>U8-U9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V7" s="4">
-        <f>V8-V9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W7" s="4">
-        <f>W8-W9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X7" s="4">
-        <f>X8-X9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z7" s="4">
@@ -1518,111 +1518,111 @@
         <v>112</v>
       </c>
       <c r="B8" s="4">
-        <f>SUM(B10:B59)</f>
+        <f t="shared" ref="B8:K8" si="2">SUM(B10:B59)</f>
         <v>149</v>
       </c>
       <c r="C8" s="4">
-        <f>SUM(C10:C59)</f>
+        <f t="shared" si="2"/>
         <v>528615</v>
       </c>
       <c r="D8" s="4">
-        <f>SUM(D10:D59)</f>
+        <f t="shared" si="2"/>
         <v>172</v>
       </c>
       <c r="E8" s="4">
-        <f>SUM(E10:E59)</f>
+        <f t="shared" si="2"/>
         <v>1237379</v>
       </c>
       <c r="F8" s="4">
-        <f>SUM(F10:F59)</f>
+        <f t="shared" si="2"/>
         <v>121</v>
       </c>
       <c r="G8" s="4">
-        <f>SUM(G10:G59)</f>
+        <f t="shared" si="2"/>
         <v>1671766</v>
       </c>
       <c r="H8" s="4">
-        <f>SUM(H10:H59)</f>
+        <f t="shared" si="2"/>
         <v>71</v>
       </c>
       <c r="I8" s="4">
-        <f>SUM(I10:I59)</f>
+        <f t="shared" si="2"/>
         <v>2159573</v>
       </c>
       <c r="J8" s="4">
-        <f>SUM(J10:J59)</f>
+        <f t="shared" si="2"/>
         <v>43</v>
       </c>
       <c r="K8" s="4">
-        <f>SUM(K10:K59)</f>
+        <f t="shared" si="2"/>
         <v>6331907</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4">
-        <f>SUM(M10:M59)</f>
+        <f t="shared" ref="M8:X8" si="3">SUM(M10:M59)</f>
         <v>2755</v>
       </c>
       <c r="N8" s="4">
-        <f>SUM(N10:N59)</f>
+        <f t="shared" si="3"/>
         <v>6636631</v>
       </c>
       <c r="O8" s="4">
-        <f>SUM(O10:O59)</f>
+        <f t="shared" si="3"/>
         <v>1040</v>
       </c>
       <c r="P8" s="4">
-        <f>SUM(P10:P59)</f>
+        <f t="shared" si="3"/>
         <v>3560755</v>
       </c>
       <c r="Q8" s="4">
-        <f>SUM(Q10:Q59)</f>
+        <f t="shared" si="3"/>
         <v>520</v>
       </c>
       <c r="R8" s="4">
-        <f>SUM(R10:R59)</f>
+        <f t="shared" si="3"/>
         <v>2313824</v>
       </c>
       <c r="S8" s="4">
-        <f>SUM(S10:S59)</f>
+        <f t="shared" si="3"/>
         <v>648</v>
       </c>
       <c r="T8" s="4">
-        <f>SUM(T10:T59)</f>
+        <f t="shared" si="3"/>
         <v>4272192</v>
       </c>
       <c r="U8" s="4">
-        <f>SUM(U10:U59)</f>
+        <f t="shared" si="3"/>
         <v>88</v>
       </c>
       <c r="V8" s="4">
-        <f>SUM(V10:V59)</f>
+        <f t="shared" si="3"/>
         <v>1152281</v>
       </c>
       <c r="W8" s="4">
-        <f>SUM(W10:W59)</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="X8" s="4">
-        <f>SUM(X10:X59)</f>
+        <f t="shared" si="3"/>
         <v>269669</v>
       </c>
       <c r="Z8" s="4">
         <f>SUM(Z10:Z59)</f>
         <v>93442864</v>
       </c>
-      <c r="AB8" s="21">
+      <c r="AB8" s="18">
         <f>N(C8)+N(E8)+N(G8)+N(I8)+N(K8)+N(N8)+N(P8)+N(R8)+N(T8)+N(V8)+N(X8)</f>
         <v>30134592</v>
       </c>
-      <c r="AC8" s="21">
+      <c r="AC8" s="18">
         <f>N(I8)+N(K8)+N(X8)</f>
         <v>8761149</v>
       </c>
-      <c r="AE8" s="23">
+      <c r="AE8" s="20">
         <f>AB8/Z8*100</f>
         <v>32.24921701886192</v>
       </c>
-      <c r="AF8" s="23">
+      <c r="AF8" s="20">
         <f>AC8/Z8*100</f>
         <v>9.3759422870429141</v>
       </c>
@@ -1698,23 +1698,23 @@
       <c r="X9" s="4">
         <v>269669</v>
       </c>
-      <c r="Z9" s="21">
+      <c r="Z9" s="18">
         <v>93442864</v>
       </c>
-      <c r="AB9" s="21">
-        <f t="shared" ref="AB9:AB72" si="0">N(C9)+N(E9)+N(G9)+N(I9)+N(K9)+N(N9)+N(P9)+N(R9)+N(T9)+N(V9)+N(X9)</f>
+      <c r="AB9" s="18">
+        <f t="shared" ref="AB9:AB72" si="4">N(C9)+N(E9)+N(G9)+N(I9)+N(K9)+N(N9)+N(P9)+N(R9)+N(T9)+N(V9)+N(X9)</f>
         <v>30134592</v>
       </c>
-      <c r="AC9" s="21">
-        <f t="shared" ref="AC9:AC72" si="1">N(I9)+N(K9)+N(X9)</f>
+      <c r="AC9" s="18">
+        <f t="shared" ref="AC9:AC72" si="5">N(I9)+N(K9)+N(X9)</f>
         <v>8761149</v>
       </c>
-      <c r="AE9" s="23">
-        <f t="shared" ref="AE9:AE72" si="2">AB9/Z9*100</f>
+      <c r="AE9" s="20">
+        <f t="shared" ref="AE9:AE72" si="6">AB9/Z9*100</f>
         <v>32.24921701886192</v>
       </c>
-      <c r="AF9" s="23">
-        <f t="shared" ref="AF9:AF72" si="3">AC9/Z9*100</f>
+      <c r="AF9" s="20">
+        <f t="shared" ref="AF9:AF72" si="7">AC9/Z9*100</f>
         <v>9.3759422870429141</v>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       <c r="X10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z10" s="21">
+      <c r="Z10" s="18">
         <v>346536</v>
       </c>
-      <c r="AB10" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB10" s="18">
+        <f t="shared" si="4"/>
         <v>34511</v>
       </c>
-      <c r="AC10" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC10" s="18">
+        <f t="shared" si="5"/>
         <v>20882</v>
       </c>
-      <c r="AE10" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE10" s="20">
+        <f t="shared" si="6"/>
         <v>9.9588498741833469</v>
       </c>
-      <c r="AF10" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF10" s="20">
+        <f t="shared" si="7"/>
         <v>6.0259251564051066</v>
       </c>
     </row>
@@ -1880,23 +1880,23 @@
       <c r="X11" s="9">
         <v>20725</v>
       </c>
-      <c r="Z11" s="21">
+      <c r="Z11" s="18">
         <v>1003542</v>
       </c>
-      <c r="AB11" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB11" s="18">
+        <f t="shared" si="4"/>
         <v>379273</v>
       </c>
-      <c r="AC11" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC11" s="18">
+        <f t="shared" si="5"/>
         <v>133605</v>
       </c>
-      <c r="AE11" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE11" s="20">
+        <f t="shared" si="6"/>
         <v>37.793435650924422</v>
       </c>
-      <c r="AF11" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF11" s="20">
+        <f t="shared" si="7"/>
         <v>13.313344135073567</v>
       </c>
     </row>
@@ -1971,23 +1971,23 @@
       <c r="X12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z12" s="21">
+      <c r="Z12" s="18">
         <v>1935412</v>
       </c>
-      <c r="AB12" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB12" s="18">
+        <f t="shared" si="4"/>
         <v>854664</v>
       </c>
-      <c r="AC12" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC12" s="18">
+        <f t="shared" si="5"/>
         <v>190833</v>
       </c>
-      <c r="AE12" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE12" s="20">
+        <f t="shared" si="6"/>
         <v>44.159279781255876</v>
       </c>
-      <c r="AF12" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF12" s="20">
+        <f t="shared" si="7"/>
         <v>9.8600711373082319</v>
       </c>
     </row>
@@ -2062,23 +2062,23 @@
       <c r="X13" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z13" s="21">
+      <c r="Z13" s="18">
         <v>1591207</v>
       </c>
-      <c r="AB13" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB13" s="18">
+        <f t="shared" si="4"/>
         <v>271919</v>
       </c>
-      <c r="AC13" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC13" s="18">
+        <f t="shared" si="5"/>
         <v>154532</v>
       </c>
-      <c r="AE13" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE13" s="20">
+        <f t="shared" si="6"/>
         <v>17.08885141907998</v>
       </c>
-      <c r="AF13" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF13" s="20">
+        <f t="shared" si="7"/>
         <v>9.7116214295185976</v>
       </c>
     </row>
@@ -2153,23 +2153,23 @@
       <c r="X14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z14" s="21">
+      <c r="Z14" s="18">
         <v>1489246</v>
       </c>
-      <c r="AB14" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB14" s="18">
+        <f t="shared" si="4"/>
         <v>254359</v>
       </c>
-      <c r="AC14" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC14" s="18">
+        <f t="shared" si="5"/>
         <v>155840</v>
       </c>
-      <c r="AE14" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE14" s="20">
+        <f t="shared" si="6"/>
         <v>17.07971685000329</v>
       </c>
-      <c r="AF14" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF14" s="20">
+        <f t="shared" si="7"/>
         <v>10.464355788096794</v>
       </c>
     </row>
@@ -2244,23 +2244,23 @@
       <c r="X15" s="9">
         <v>25233</v>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="18">
         <v>1515691</v>
       </c>
-      <c r="AB15" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB15" s="18">
+        <f t="shared" si="4"/>
         <v>291442</v>
       </c>
-      <c r="AC15" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC15" s="18">
+        <f t="shared" si="5"/>
         <v>107920</v>
       </c>
-      <c r="AE15" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE15" s="20">
+        <f t="shared" si="6"/>
         <v>19.228325562400254</v>
       </c>
-      <c r="AF15" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF15" s="20">
+        <f t="shared" si="7"/>
         <v>7.1201847870047397</v>
       </c>
     </row>
@@ -2335,23 +2335,23 @@
       <c r="X16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z16" s="21">
+      <c r="Z16" s="18">
         <v>1341785</v>
       </c>
-      <c r="AB16" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB16" s="18">
+        <f t="shared" si="4"/>
         <v>60820</v>
       </c>
-      <c r="AC16" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC16" s="18">
+        <f t="shared" si="5"/>
         <v>27705</v>
       </c>
-      <c r="AE16" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE16" s="20">
+        <f t="shared" si="6"/>
         <v>4.5327679173638096</v>
       </c>
-      <c r="AF16" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF16" s="20">
+        <f t="shared" si="7"/>
         <v>2.0647868324657077</v>
       </c>
     </row>
@@ -2426,23 +2426,23 @@
       <c r="X17" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z17" s="21">
+      <c r="Z17" s="18">
         <v>2989482</v>
       </c>
-      <c r="AB17" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB17" s="18">
+        <f t="shared" si="4"/>
         <v>640567</v>
       </c>
-      <c r="AC17" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC17" s="18">
+        <f t="shared" si="5"/>
         <v>90468</v>
       </c>
-      <c r="AE17" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE17" s="20">
+        <f t="shared" si="6"/>
         <v>21.427357649251611</v>
       </c>
-      <c r="AF17" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF17" s="20">
+        <f t="shared" si="7"/>
         <v>3.0262098918809346</v>
       </c>
     </row>
@@ -2517,23 +2517,23 @@
       <c r="X18" s="6">
         <v>23443</v>
       </c>
-      <c r="Z18" s="21">
+      <c r="Z18" s="18">
         <v>2531253</v>
       </c>
-      <c r="AB18" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB18" s="18">
+        <f t="shared" si="4"/>
         <v>1403609</v>
       </c>
-      <c r="AC18" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC18" s="18">
+        <f t="shared" si="5"/>
         <v>125025</v>
       </c>
-      <c r="AE18" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE18" s="20">
+        <f t="shared" si="6"/>
         <v>55.451154033200154</v>
       </c>
-      <c r="AF18" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF18" s="20">
+        <f t="shared" si="7"/>
         <v>4.939253405329298</v>
       </c>
     </row>
@@ -2608,23 +2608,23 @@
       <c r="X19" s="9">
         <v>62695</v>
       </c>
-      <c r="Z19" s="21">
+      <c r="Z19" s="18">
         <v>3030831</v>
       </c>
-      <c r="AB19" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB19" s="18">
+        <f t="shared" si="4"/>
         <v>204957</v>
       </c>
-      <c r="AC19" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC19" s="18">
+        <f t="shared" si="5"/>
         <v>109101</v>
       </c>
-      <c r="AE19" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE19" s="20">
+        <f t="shared" si="6"/>
         <v>6.7624027865624976</v>
       </c>
-      <c r="AF19" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF19" s="20">
+        <f t="shared" si="7"/>
         <v>3.5997058232544141</v>
       </c>
     </row>
@@ -2699,23 +2699,23 @@
       <c r="X20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z20" s="21">
+      <c r="Z20" s="18">
         <v>1603409</v>
       </c>
-      <c r="AB20" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB20" s="18">
+        <f t="shared" si="4"/>
         <v>362957</v>
       </c>
-      <c r="AC20" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC20" s="18">
+        <f t="shared" si="5"/>
         <v>159519</v>
       </c>
-      <c r="AE20" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE20" s="20">
+        <f t="shared" si="6"/>
         <v>22.636582431556764</v>
       </c>
-      <c r="AF20" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF20" s="20">
+        <f t="shared" si="7"/>
         <v>9.9487404648470843</v>
       </c>
     </row>
@@ -2790,23 +2790,23 @@
       <c r="X21" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z21" s="21">
+      <c r="Z21" s="18">
         <v>2564238</v>
       </c>
-      <c r="AB21" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB21" s="18">
+        <f t="shared" si="4"/>
         <v>869026</v>
       </c>
-      <c r="AC21" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC21" s="18">
+        <f t="shared" si="5"/>
         <v>251303</v>
       </c>
-      <c r="AE21" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE21" s="20">
+        <f t="shared" si="6"/>
         <v>33.890223918372634</v>
       </c>
-      <c r="AF21" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF21" s="20">
+        <f t="shared" si="7"/>
         <v>9.80029934818843</v>
       </c>
     </row>
@@ -2881,23 +2881,23 @@
       <c r="X22" s="6">
         <v>49147</v>
       </c>
-      <c r="Z22" s="21">
+      <c r="Z22" s="18">
         <v>2113674</v>
       </c>
-      <c r="AB22" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB22" s="18">
+        <f t="shared" si="4"/>
         <v>1224527</v>
       </c>
-      <c r="AC22" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC22" s="18">
+        <f t="shared" si="5"/>
         <v>213506</v>
       </c>
-      <c r="AE22" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE22" s="20">
+        <f t="shared" si="6"/>
         <v>57.933579161214077</v>
       </c>
-      <c r="AF22" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF22" s="20">
+        <f t="shared" si="7"/>
         <v>10.101179273624977</v>
       </c>
     </row>
@@ -2972,23 +2972,23 @@
       <c r="X23" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z23" s="21">
+      <c r="Z23" s="18">
         <v>2170665</v>
       </c>
-      <c r="AB23" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB23" s="18">
+        <f t="shared" si="4"/>
         <v>348680</v>
       </c>
-      <c r="AC23" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC23" s="18">
+        <f t="shared" si="5"/>
         <v>150063</v>
       </c>
-      <c r="AE23" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE23" s="20">
+        <f t="shared" si="6"/>
         <v>16.063280146867434</v>
       </c>
-      <c r="AF23" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF23" s="20">
+        <f t="shared" si="7"/>
         <v>6.9132270525391988</v>
       </c>
     </row>
@@ -3063,23 +3063,23 @@
       <c r="X24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z24" s="21">
+      <c r="Z24" s="18">
         <v>1132843</v>
       </c>
-      <c r="AB24" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB24" s="18">
+        <f t="shared" si="4"/>
         <v>139422</v>
       </c>
-      <c r="AC24" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC24" s="18">
+        <f t="shared" si="5"/>
         <v>49513</v>
       </c>
-      <c r="AE24" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE24" s="20">
+        <f t="shared" si="6"/>
         <v>12.307265878855233</v>
       </c>
-      <c r="AF24" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF24" s="20">
+        <f t="shared" si="7"/>
         <v>4.370685081692697</v>
       </c>
     </row>
@@ -3154,23 +3154,23 @@
       <c r="X25" s="9">
         <v>35378</v>
       </c>
-      <c r="Z25" s="21">
+      <c r="Z25" s="18">
         <v>3559229</v>
       </c>
-      <c r="AB25" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB25" s="18">
+        <f t="shared" si="4"/>
         <v>1880777</v>
       </c>
-      <c r="AC25" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC25" s="18">
+        <f t="shared" si="5"/>
         <v>397068</v>
       </c>
-      <c r="AE25" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE25" s="20">
+        <f t="shared" si="6"/>
         <v>52.84225881504112</v>
       </c>
-      <c r="AF25" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF25" s="20">
+        <f t="shared" si="7"/>
         <v>11.156011596893597</v>
       </c>
     </row>
@@ -3245,23 +3245,23 @@
       <c r="X26" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z26" s="21">
+      <c r="Z26" s="18">
         <v>1544564</v>
       </c>
-      <c r="AB26" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB26" s="18">
+        <f t="shared" si="4"/>
         <v>253930</v>
       </c>
-      <c r="AC26" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC26" s="18">
+        <f t="shared" si="5"/>
         <v>70920</v>
       </c>
-      <c r="AE26" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE26" s="20">
+        <f t="shared" si="6"/>
         <v>16.440238151348861</v>
       </c>
-      <c r="AF26" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF26" s="20">
+        <f t="shared" si="7"/>
         <v>4.5915870109623169</v>
       </c>
     </row>
@@ -3336,23 +3336,23 @@
       <c r="X27" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z27" s="21">
+      <c r="Z27" s="18">
         <v>1387015</v>
       </c>
-      <c r="AB27" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB27" s="18">
+        <f t="shared" si="4"/>
         <v>105548</v>
       </c>
-      <c r="AC27" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC27" s="18">
+        <f t="shared" si="5"/>
         <v>41336</v>
       </c>
-      <c r="AE27" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE27" s="20">
+        <f t="shared" si="6"/>
         <v>7.6097230383233061</v>
       </c>
-      <c r="AF27" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF27" s="20">
+        <f t="shared" si="7"/>
         <v>2.9802129032490634</v>
       </c>
     </row>
@@ -3427,23 +3427,23 @@
       <c r="X28" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z28" s="21">
+      <c r="Z28" s="18">
         <v>674034</v>
       </c>
-      <c r="AB28" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB28" s="18">
+        <f t="shared" si="4"/>
         <v>168537</v>
       </c>
-      <c r="AC28" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC28" s="18">
+        <f t="shared" si="5"/>
         <v>99620</v>
       </c>
-      <c r="AE28" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE28" s="20">
+        <f t="shared" si="6"/>
         <v>25.004228273351199</v>
       </c>
-      <c r="AF28" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF28" s="20">
+        <f t="shared" si="7"/>
         <v>14.779669868285575</v>
       </c>
     </row>
@@ -3518,23 +3518,23 @@
       <c r="X29" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z29" s="21">
+      <c r="Z29" s="18">
         <v>2371012</v>
       </c>
-      <c r="AB29" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB29" s="18">
+        <f t="shared" si="4"/>
         <v>786493</v>
       </c>
-      <c r="AC29" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC29" s="18">
+        <f t="shared" si="5"/>
         <v>102285</v>
       </c>
-      <c r="AE29" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE29" s="20">
+        <f t="shared" si="6"/>
         <v>33.171194409813189</v>
       </c>
-      <c r="AF29" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF29" s="20">
+        <f t="shared" si="7"/>
         <v>4.3139806968501215</v>
       </c>
     </row>
@@ -3609,23 +3609,23 @@
       <c r="X30" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z30" s="21">
+      <c r="Z30" s="18">
         <v>1299365</v>
       </c>
-      <c r="AB30" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB30" s="18">
+        <f t="shared" si="4"/>
         <v>394859</v>
       </c>
-      <c r="AC30" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC30" s="18">
+        <f t="shared" si="5"/>
         <v>324538</v>
       </c>
-      <c r="AE30" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE30" s="20">
+        <f t="shared" si="6"/>
         <v>30.388612899377769</v>
       </c>
-      <c r="AF30" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF30" s="20">
+        <f t="shared" si="7"/>
         <v>24.976661677049943</v>
       </c>
     </row>
@@ -3700,23 +3700,23 @@
       <c r="X31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z31" s="21">
+      <c r="Z31" s="18">
         <v>2147621</v>
       </c>
-      <c r="AB31" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB31" s="18">
+        <f t="shared" si="4"/>
         <v>378706</v>
       </c>
-      <c r="AC31" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC31" s="18">
+        <f t="shared" si="5"/>
         <v>153616</v>
       </c>
-      <c r="AE31" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE31" s="20">
+        <f t="shared" si="6"/>
         <v>17.633744501473956</v>
       </c>
-      <c r="AF31" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF31" s="20">
+        <f t="shared" si="7"/>
         <v>7.1528449386553765</v>
       </c>
     </row>
@@ -3791,23 +3791,23 @@
       <c r="X32" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z32" s="21">
+      <c r="Z32" s="18">
         <v>1686764</v>
       </c>
-      <c r="AB32" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB32" s="18">
+        <f t="shared" si="4"/>
         <v>271550</v>
       </c>
-      <c r="AC32" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC32" s="18">
+        <f t="shared" si="5"/>
         <v>79894</v>
       </c>
-      <c r="AE32" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE32" s="20">
+        <f t="shared" si="6"/>
         <v>16.09887334564883</v>
       </c>
-      <c r="AF32" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF32" s="20">
+        <f t="shared" si="7"/>
         <v>4.7365250859041339</v>
       </c>
     </row>
@@ -3882,23 +3882,23 @@
       <c r="X33" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z33" s="21">
+      <c r="Z33" s="18">
         <v>2430581</v>
       </c>
-      <c r="AB33" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB33" s="18">
+        <f t="shared" si="4"/>
         <v>1250685</v>
       </c>
-      <c r="AC33" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC33" s="18">
+        <f t="shared" si="5"/>
         <v>1089439</v>
       </c>
-      <c r="AE33" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE33" s="20">
+        <f t="shared" si="6"/>
         <v>51.456215612645707</v>
       </c>
-      <c r="AF33" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF33" s="20">
+        <f t="shared" si="7"/>
         <v>44.822163918832572</v>
       </c>
     </row>
@@ -3973,23 +3973,23 @@
       <c r="X34" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z34" s="21">
+      <c r="Z34" s="18">
         <v>1584774</v>
       </c>
-      <c r="AB34" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB34" s="18">
+        <f t="shared" si="4"/>
         <v>373629</v>
       </c>
-      <c r="AC34" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC34" s="18">
+        <f t="shared" si="5"/>
         <v>90053</v>
       </c>
-      <c r="AE34" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE34" s="20">
+        <f t="shared" si="6"/>
         <v>23.57616922034309</v>
       </c>
-      <c r="AF34" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF34" s="20">
+        <f t="shared" si="7"/>
         <v>5.6823875202394794</v>
       </c>
     </row>
@@ -4064,23 +4064,23 @@
       <c r="X35" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z35" s="21">
+      <c r="Z35" s="18">
         <v>1367022</v>
       </c>
-      <c r="AB35" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB35" s="18">
+        <f t="shared" si="4"/>
         <v>96784</v>
       </c>
-      <c r="AC35" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC35" s="18">
+        <f t="shared" si="5"/>
         <v>25736</v>
       </c>
-      <c r="AE35" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE35" s="20">
+        <f t="shared" si="6"/>
         <v>7.0799153195778857</v>
       </c>
-      <c r="AF35" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF35" s="20">
+        <f t="shared" si="7"/>
         <v>1.8826324667781498</v>
       </c>
     </row>
@@ -4155,23 +4155,23 @@
       <c r="X36" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z36" s="21">
+      <c r="Z36" s="18">
         <v>364156</v>
       </c>
-      <c r="AB36" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB36" s="18">
+        <f t="shared" si="4"/>
         <v>20081</v>
       </c>
-      <c r="AC36" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC36" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE36" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE36" s="20">
+        <f t="shared" si="6"/>
         <v>5.5143949296455368</v>
       </c>
-      <c r="AF36" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF36" s="20">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4246,23 +4246,23 @@
       <c r="X37" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z37" s="21">
+      <c r="Z37" s="18">
         <v>1600145</v>
       </c>
-      <c r="AB37" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB37" s="18">
+        <f t="shared" si="4"/>
         <v>505763</v>
       </c>
-      <c r="AC37" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC37" s="18">
+        <f t="shared" si="5"/>
         <v>95724</v>
       </c>
-      <c r="AE37" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE37" s="20">
+        <f t="shared" si="6"/>
         <v>31.6073230863453</v>
       </c>
-      <c r="AF37" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF37" s="20">
+        <f t="shared" si="7"/>
         <v>5.9822078624124693</v>
       </c>
     </row>
@@ -4337,23 +4337,23 @@
       <c r="X38" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z38" s="21">
+      <c r="Z38" s="18">
         <v>2033798</v>
       </c>
-      <c r="AB38" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB38" s="18">
+        <f t="shared" si="4"/>
         <v>409024</v>
       </c>
-      <c r="AC38" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC38" s="18">
+        <f t="shared" si="5"/>
         <v>183366</v>
       </c>
-      <c r="AE38" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE38" s="20">
+        <f t="shared" si="6"/>
         <v>20.111338490843238</v>
       </c>
-      <c r="AF38" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF38" s="20">
+        <f t="shared" si="7"/>
         <v>9.0159396360897208</v>
       </c>
     </row>
@@ -4428,23 +4428,23 @@
       <c r="X39" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z39" s="21">
+      <c r="Z39" s="18">
         <v>1470474</v>
       </c>
-      <c r="AB39" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB39" s="18">
+        <f t="shared" si="4"/>
         <v>424107</v>
       </c>
-      <c r="AC39" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC39" s="18">
+        <f t="shared" si="5"/>
         <v>59981</v>
       </c>
-      <c r="AE39" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE39" s="20">
+        <f t="shared" si="6"/>
         <v>28.84151640899465</v>
       </c>
-      <c r="AF39" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF39" s="20">
+        <f t="shared" si="7"/>
         <v>4.07902485865102</v>
       </c>
     </row>
@@ -4519,23 +4519,23 @@
       <c r="X40" s="6">
         <v>31449</v>
       </c>
-      <c r="Z40" s="21">
+      <c r="Z40" s="18">
         <v>2994302</v>
       </c>
-      <c r="AB40" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB40" s="18">
+        <f t="shared" si="4"/>
         <v>805487</v>
       </c>
-      <c r="AC40" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC40" s="18">
+        <f t="shared" si="5"/>
         <v>139955</v>
       </c>
-      <c r="AE40" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE40" s="20">
+        <f t="shared" si="6"/>
         <v>26.900659986868391</v>
       </c>
-      <c r="AF40" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF40" s="20">
+        <f t="shared" si="7"/>
         <v>4.6740442346830742</v>
       </c>
     </row>
@@ -4610,23 +4610,23 @@
       <c r="X41" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z41" s="21">
+      <c r="Z41" s="18">
         <v>3018299</v>
       </c>
-      <c r="AB41" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB41" s="18">
+        <f t="shared" si="4"/>
         <v>1242617</v>
       </c>
-      <c r="AC41" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC41" s="18">
+        <f t="shared" si="5"/>
         <v>135030</v>
       </c>
-      <c r="AE41" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE41" s="20">
+        <f t="shared" si="6"/>
         <v>41.169446764551822</v>
       </c>
-      <c r="AF41" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF41" s="20">
+        <f t="shared" si="7"/>
         <v>4.4737118489586347</v>
       </c>
     </row>
@@ -4701,23 +4701,23 @@
       <c r="X42" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z42" s="21">
+      <c r="Z42" s="18">
         <v>2778151</v>
       </c>
-      <c r="AB42" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB42" s="18">
+        <f t="shared" si="4"/>
         <v>1141008</v>
       </c>
-      <c r="AC42" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC42" s="18">
+        <f t="shared" si="5"/>
         <v>139220</v>
       </c>
-      <c r="AE42" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE42" s="20">
+        <f t="shared" si="6"/>
         <v>41.070769731378896</v>
       </c>
-      <c r="AF42" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF42" s="20">
+        <f t="shared" si="7"/>
         <v>5.0112466888948797</v>
       </c>
     </row>
@@ -4792,23 +4792,23 @@
       <c r="X43" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z43" s="21">
+      <c r="Z43" s="18">
         <v>1122317</v>
       </c>
-      <c r="AB43" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB43" s="18">
+        <f t="shared" si="4"/>
         <v>79661</v>
       </c>
-      <c r="AC43" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC43" s="18">
+        <f t="shared" si="5"/>
         <v>30478</v>
       </c>
-      <c r="AE43" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE43" s="20">
+        <f t="shared" si="6"/>
         <v>7.0979054937241433</v>
       </c>
-      <c r="AF43" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF43" s="20">
+        <f t="shared" si="7"/>
         <v>2.7156320362250597</v>
       </c>
     </row>
@@ -4883,23 +4883,23 @@
       <c r="X44" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z44" s="21">
+      <c r="Z44" s="18">
         <v>1802196</v>
       </c>
-      <c r="AB44" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB44" s="18">
+        <f t="shared" si="4"/>
         <v>524434</v>
       </c>
-      <c r="AC44" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC44" s="18">
+        <f t="shared" si="5"/>
         <v>46122</v>
       </c>
-      <c r="AE44" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE44" s="20">
+        <f t="shared" si="6"/>
         <v>29.099720563135197</v>
       </c>
-      <c r="AF44" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF44" s="20">
+        <f t="shared" si="7"/>
         <v>2.5592110957964613</v>
       </c>
     </row>
@@ -4974,23 +4974,23 @@
       <c r="X45" s="9">
         <v>21599</v>
       </c>
-      <c r="Z45" s="21">
+      <c r="Z45" s="18">
         <v>2751336</v>
       </c>
-      <c r="AB45" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB45" s="18">
+        <f t="shared" si="4"/>
         <v>1301224</v>
       </c>
-      <c r="AC45" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC45" s="18">
+        <f t="shared" si="5"/>
         <v>111598</v>
       </c>
-      <c r="AE45" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE45" s="20">
+        <f t="shared" si="6"/>
         <v>47.294259952255921</v>
       </c>
-      <c r="AF45" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF45" s="20">
+        <f t="shared" si="7"/>
         <v>4.0561385450559291</v>
       </c>
     </row>
@@ -5065,23 +5065,23 @@
       <c r="X46" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z46" s="21">
+      <c r="Z46" s="18">
         <v>2112033</v>
       </c>
-      <c r="AB46" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB46" s="18">
+        <f t="shared" si="4"/>
         <v>1459959</v>
       </c>
-      <c r="AC46" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC46" s="18">
+        <f t="shared" si="5"/>
         <v>1346925</v>
       </c>
-      <c r="AE46" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE46" s="20">
+        <f t="shared" si="6"/>
         <v>69.125766500807515</v>
       </c>
-      <c r="AF46" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF46" s="20">
+        <f t="shared" si="7"/>
         <v>63.773861487959707</v>
       </c>
     </row>
@@ -5156,23 +5156,23 @@
       <c r="X47" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z47" s="21">
+      <c r="Z47" s="18">
         <v>2405829</v>
       </c>
-      <c r="AB47" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB47" s="18">
+        <f t="shared" si="4"/>
         <v>1173209</v>
       </c>
-      <c r="AC47" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC47" s="18">
+        <f t="shared" si="5"/>
         <v>239864</v>
       </c>
-      <c r="AE47" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE47" s="20">
+        <f t="shared" si="6"/>
         <v>48.76526968458689</v>
       </c>
-      <c r="AF47" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF47" s="20">
+        <f t="shared" si="7"/>
         <v>9.9701184082492986</v>
       </c>
     </row>
@@ -5247,23 +5247,23 @@
       <c r="X48" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z48" s="21">
+      <c r="Z48" s="18">
         <v>1527848</v>
       </c>
-      <c r="AB48" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB48" s="18">
+        <f t="shared" si="4"/>
         <v>490204</v>
       </c>
-      <c r="AC48" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC48" s="18">
+        <f t="shared" si="5"/>
         <v>74067</v>
       </c>
-      <c r="AE48" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE48" s="20">
+        <f t="shared" si="6"/>
         <v>32.084605274870277</v>
       </c>
-      <c r="AF48" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF48" s="20">
+        <f t="shared" si="7"/>
         <v>4.8477989957116154</v>
       </c>
     </row>
@@ -5338,23 +5338,23 @@
       <c r="X49" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z49" s="21">
+      <c r="Z49" s="18">
         <v>1525279</v>
       </c>
-      <c r="AB49" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB49" s="18">
+        <f t="shared" si="4"/>
         <v>126656</v>
       </c>
-      <c r="AC49" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC49" s="18">
+        <f t="shared" si="5"/>
         <v>46699</v>
       </c>
-      <c r="AE49" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE49" s="20">
+        <f t="shared" si="6"/>
         <v>8.3037922898040293</v>
       </c>
-      <c r="AF49" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF49" s="20">
+        <f t="shared" si="7"/>
         <v>3.0616693732753153</v>
       </c>
     </row>
@@ -5429,23 +5429,23 @@
       <c r="X50" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z50" s="21">
+      <c r="Z50" s="18">
         <v>1447790</v>
       </c>
-      <c r="AB50" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB50" s="18">
+        <f t="shared" si="4"/>
         <v>833276</v>
       </c>
-      <c r="AC50" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC50" s="18">
+        <f t="shared" si="5"/>
         <v>186612</v>
       </c>
-      <c r="AE50" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE50" s="20">
+        <f t="shared" si="6"/>
         <v>57.555032152453045</v>
       </c>
-      <c r="AF50" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF50" s="20">
+        <f t="shared" si="7"/>
         <v>12.889438385401197</v>
       </c>
     </row>
@@ -5520,23 +5520,23 @@
       <c r="X51" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z51" s="21">
+      <c r="Z51" s="18">
         <v>2684030</v>
       </c>
-      <c r="AB51" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB51" s="18">
+        <f t="shared" si="4"/>
         <v>1162054</v>
       </c>
-      <c r="AC51" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC51" s="18">
+        <f t="shared" si="5"/>
         <v>157603</v>
       </c>
-      <c r="AE51" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE51" s="20">
+        <f t="shared" si="6"/>
         <v>43.295119652164843</v>
       </c>
-      <c r="AF51" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF51" s="20">
+        <f t="shared" si="7"/>
         <v>5.8718792263871871</v>
       </c>
     </row>
@@ -5611,23 +5611,23 @@
       <c r="X52" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z52" s="21">
+      <c r="Z52" s="18">
         <v>1769135</v>
       </c>
-      <c r="AB52" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB52" s="18">
+        <f t="shared" si="4"/>
         <v>164289</v>
       </c>
-      <c r="AC52" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC52" s="18">
+        <f t="shared" si="5"/>
         <v>74809</v>
       </c>
-      <c r="AE52" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE52" s="20">
+        <f t="shared" si="6"/>
         <v>9.2864026770144736</v>
       </c>
-      <c r="AF52" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF52" s="20">
+        <f t="shared" si="7"/>
         <v>4.2285636765990162</v>
       </c>
     </row>
@@ -5702,23 +5702,23 @@
       <c r="X53" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z53" s="21">
+      <c r="Z53" s="18">
         <v>1419456</v>
       </c>
-      <c r="AB53" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB53" s="18">
+        <f t="shared" si="4"/>
         <v>262198</v>
       </c>
-      <c r="AC53" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC53" s="18">
+        <f t="shared" si="5"/>
         <v>114733</v>
       </c>
-      <c r="AE53" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE53" s="20">
+        <f t="shared" si="6"/>
         <v>18.471724378916992</v>
       </c>
-      <c r="AF53" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF53" s="20">
+        <f t="shared" si="7"/>
         <v>8.0828852743586275</v>
       </c>
     </row>
@@ -5793,23 +5793,23 @@
       <c r="X54" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z54" s="21">
+      <c r="Z54" s="18">
         <v>2196642</v>
       </c>
-      <c r="AB54" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB54" s="18">
+        <f t="shared" si="4"/>
         <v>350444</v>
       </c>
-      <c r="AC54" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC54" s="18">
+        <f t="shared" si="5"/>
         <v>69777</v>
       </c>
-      <c r="AE54" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE54" s="20">
+        <f t="shared" si="6"/>
         <v>15.953623758445845</v>
       </c>
-      <c r="AF54" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF54" s="20">
+        <f t="shared" si="7"/>
         <v>3.1765303586110072</v>
       </c>
     </row>
@@ -5884,23 +5884,23 @@
       <c r="X55" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z55" s="21">
+      <c r="Z55" s="18">
         <v>2492316</v>
       </c>
-      <c r="AB55" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB55" s="18">
+        <f t="shared" si="4"/>
         <v>1333959</v>
       </c>
-      <c r="AC55" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC55" s="18">
+        <f t="shared" si="5"/>
         <v>224952</v>
       </c>
-      <c r="AE55" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE55" s="20">
+        <f t="shared" si="6"/>
         <v>53.52286788673667</v>
       </c>
-      <c r="AF55" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF55" s="20">
+        <f t="shared" si="7"/>
         <v>9.0258217657792983</v>
       </c>
     </row>
@@ -5975,23 +5975,23 @@
       <c r="X56" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z56" s="21">
+      <c r="Z56" s="18">
         <v>2733612</v>
       </c>
-      <c r="AB56" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB56" s="18">
+        <f t="shared" si="4"/>
         <v>1705612</v>
       </c>
-      <c r="AC56" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC56" s="18">
+        <f t="shared" si="5"/>
         <v>648007</v>
       </c>
-      <c r="AE56" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE56" s="20">
+        <f t="shared" si="6"/>
         <v>62.394077872060848</v>
       </c>
-      <c r="AF56" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF56" s="20">
+        <f t="shared" si="7"/>
         <v>23.705156401127887</v>
       </c>
     </row>
@@ -6066,23 +6066,23 @@
       <c r="X57" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z57" s="21">
+      <c r="Z57" s="18">
         <v>2297854</v>
       </c>
-      <c r="AB57" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB57" s="18">
+        <f t="shared" si="4"/>
         <v>1065498</v>
       </c>
-      <c r="AC57" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC57" s="18">
+        <f t="shared" si="5"/>
         <v>59829</v>
       </c>
-      <c r="AE57" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE57" s="20">
+        <f t="shared" si="6"/>
         <v>46.369264539870677</v>
       </c>
-      <c r="AF57" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF57" s="20">
+        <f t="shared" si="7"/>
         <v>2.6036902257497649</v>
       </c>
     </row>
@@ -6157,23 +6157,23 @@
       <c r="X58" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z58" s="21">
+      <c r="Z58" s="18">
         <v>412716</v>
       </c>
-      <c r="AB58" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB58" s="18">
+        <f t="shared" si="4"/>
         <v>91645</v>
       </c>
-      <c r="AC58" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC58" s="18">
+        <f t="shared" si="5"/>
         <v>64572</v>
       </c>
-      <c r="AE58" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE58" s="20">
+        <f t="shared" si="6"/>
         <v>22.205342172341272</v>
       </c>
-      <c r="AF58" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF58" s="20">
+        <f t="shared" si="7"/>
         <v>15.645625563341378</v>
       </c>
     </row>
@@ -6248,23 +6248,23 @@
       <c r="X59" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z59" s="21">
+      <c r="Z59" s="18">
         <v>1071355</v>
       </c>
-      <c r="AB59" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB59" s="18">
+        <f t="shared" si="4"/>
         <v>159952</v>
       </c>
-      <c r="AC59" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC59" s="18">
+        <f t="shared" si="5"/>
         <v>96906</v>
       </c>
-      <c r="AE59" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE59" s="20">
+        <f t="shared" si="6"/>
         <v>14.929878518324923</v>
       </c>
-      <c r="AF59" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF59" s="20">
+        <f t="shared" si="7"/>
         <v>9.0451811024357003</v>
       </c>
     </row>
@@ -6293,212 +6293,212 @@
       <c r="V60" s="10"/>
       <c r="W60" s="10"/>
       <c r="X60" s="10"/>
-      <c r="AB60" s="21"/>
-      <c r="AC60" s="21"/>
-      <c r="AE60" s="23"/>
-      <c r="AF60" s="23"/>
+      <c r="AB60" s="18"/>
+      <c r="AC60" s="18"/>
+      <c r="AE60" s="20"/>
+      <c r="AF60" s="20"/>
     </row>
     <row r="61" spans="1:32">
       <c r="A61" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="17">
         <f>B62-B63</f>
         <v>0</v>
       </c>
-      <c r="C61" s="20">
-        <f t="shared" ref="C61:K61" si="4">C62-C63</f>
+      <c r="C61" s="17">
+        <f t="shared" ref="C61:K61" si="8">C62-C63</f>
         <v>0</v>
       </c>
-      <c r="D61" s="20">
-        <f t="shared" si="4"/>
+      <c r="D61" s="17">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="E61" s="20">
-        <f t="shared" si="4"/>
+      <c r="E61" s="17">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F61" s="20">
-        <f t="shared" si="4"/>
+      <c r="F61" s="17">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G61" s="20">
-        <f t="shared" si="4"/>
+      <c r="G61" s="17">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H61" s="20">
-        <f t="shared" si="4"/>
+      <c r="H61" s="17">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I61" s="20">
-        <f t="shared" si="4"/>
+      <c r="I61" s="17">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J61" s="20">
-        <f t="shared" si="4"/>
+      <c r="J61" s="17">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K61" s="20">
-        <f t="shared" si="4"/>
+      <c r="K61" s="17">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L61" s="20"/>
-      <c r="M61" s="20">
-        <f t="shared" ref="M61:V61" si="5">M62-M63</f>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17">
+        <f t="shared" ref="M61:V61" si="9">M62-M63</f>
         <v>0</v>
       </c>
-      <c r="N61" s="20">
-        <f t="shared" si="5"/>
+      <c r="N61" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O61" s="20">
-        <f t="shared" si="5"/>
+      <c r="O61" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P61" s="20">
-        <f t="shared" si="5"/>
+      <c r="P61" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="20">
-        <f t="shared" si="5"/>
+      <c r="Q61" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R61" s="20">
-        <f t="shared" si="5"/>
+      <c r="R61" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S61" s="20">
-        <f t="shared" si="5"/>
+      <c r="S61" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T61" s="20">
-        <f t="shared" si="5"/>
+      <c r="T61" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U61" s="20">
-        <f t="shared" si="5"/>
+      <c r="U61" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="V61" s="20">
-        <f t="shared" si="5"/>
+      <c r="V61" s="17">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W61" s="9"/>
       <c r="X61" s="9"/>
-      <c r="Z61" s="20">
-        <f t="shared" ref="Z61" si="6">Z62-Z63</f>
+      <c r="Z61" s="17">
+        <f t="shared" ref="Z61" si="10">Z62-Z63</f>
         <v>0</v>
       </c>
-      <c r="AB61" s="21"/>
-      <c r="AC61" s="21"/>
-      <c r="AE61" s="23"/>
-      <c r="AF61" s="23"/>
+      <c r="AB61" s="18"/>
+      <c r="AC61" s="18"/>
+      <c r="AE61" s="20"/>
+      <c r="AF61" s="20"/>
     </row>
     <row r="62" spans="1:32">
       <c r="A62" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B62" s="20">
+      <c r="B62" s="17">
         <f>SUM(B64:B73)</f>
         <v>27</v>
       </c>
-      <c r="C62" s="20">
-        <f t="shared" ref="C62:K62" si="7">SUM(C64:C73)</f>
+      <c r="C62" s="17">
+        <f t="shared" ref="C62:K62" si="11">SUM(C64:C73)</f>
         <v>101654</v>
       </c>
-      <c r="D62" s="20">
-        <f t="shared" si="7"/>
+      <c r="D62" s="17">
+        <f t="shared" si="11"/>
         <v>53</v>
       </c>
-      <c r="E62" s="20">
-        <f t="shared" si="7"/>
+      <c r="E62" s="17">
+        <f t="shared" si="11"/>
         <v>385823</v>
       </c>
-      <c r="F62" s="20">
-        <f t="shared" si="7"/>
-        <v>18</v>
-      </c>
-      <c r="G62" s="20">
-        <f t="shared" si="7"/>
+      <c r="F62" s="17">
+        <f t="shared" si="11"/>
+        <v>18</v>
+      </c>
+      <c r="G62" s="17">
+        <f t="shared" si="11"/>
         <v>240179</v>
       </c>
-      <c r="H62" s="20">
-        <f t="shared" si="7"/>
+      <c r="H62" s="17">
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="I62" s="20">
-        <f t="shared" si="7"/>
+      <c r="I62" s="17">
+        <f t="shared" si="11"/>
         <v>350094</v>
       </c>
-      <c r="J62" s="20">
-        <f t="shared" si="7"/>
+      <c r="J62" s="17">
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="K62" s="20">
-        <f t="shared" si="7"/>
+      <c r="K62" s="17">
+        <f t="shared" si="11"/>
         <v>1048097</v>
       </c>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20">
-        <f t="shared" ref="M62:V62" si="8">SUM(M64:M73)</f>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17">
+        <f t="shared" ref="M62:V62" si="12">SUM(M64:M73)</f>
         <v>120</v>
       </c>
-      <c r="N62" s="20">
-        <f t="shared" si="8"/>
+      <c r="N62" s="17">
+        <f t="shared" si="12"/>
         <v>291342</v>
       </c>
-      <c r="O62" s="20">
-        <f t="shared" si="8"/>
+      <c r="O62" s="17">
+        <f t="shared" si="12"/>
         <v>43</v>
       </c>
-      <c r="P62" s="20">
-        <f t="shared" si="8"/>
+      <c r="P62" s="17">
+        <f t="shared" si="12"/>
         <v>147971</v>
       </c>
-      <c r="Q62" s="20">
-        <f t="shared" si="8"/>
-        <v>18</v>
-      </c>
-      <c r="R62" s="20">
-        <f t="shared" si="8"/>
+      <c r="Q62" s="17">
+        <f t="shared" si="12"/>
+        <v>18</v>
+      </c>
+      <c r="R62" s="17">
+        <f t="shared" si="12"/>
         <v>80095</v>
       </c>
-      <c r="S62" s="20">
-        <f t="shared" si="8"/>
+      <c r="S62" s="17">
+        <f t="shared" si="12"/>
         <v>22</v>
       </c>
-      <c r="T62" s="20">
-        <f t="shared" si="8"/>
+      <c r="T62" s="17">
+        <f t="shared" si="12"/>
         <v>140615</v>
       </c>
-      <c r="U62" s="20">
-        <f t="shared" si="8"/>
+      <c r="U62" s="17">
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="V62" s="20">
-        <f t="shared" si="8"/>
+      <c r="V62" s="17">
+        <f t="shared" si="12"/>
         <v>38272</v>
       </c>
       <c r="W62" s="9"/>
       <c r="X62" s="9"/>
-      <c r="Z62" s="20">
-        <f t="shared" ref="Z62" si="9">SUM(Z64:Z73)</f>
+      <c r="Z62" s="17">
+        <f t="shared" ref="Z62" si="13">SUM(Z64:Z73)</f>
         <v>9402253</v>
       </c>
-      <c r="AB62" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB62" s="18">
+        <f t="shared" si="4"/>
         <v>2824142</v>
       </c>
-      <c r="AC62" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC62" s="18">
+        <f t="shared" si="5"/>
         <v>1398191</v>
       </c>
-      <c r="AE62" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE62" s="20">
+        <f t="shared" si="6"/>
         <v>30.036864568524162</v>
       </c>
-      <c r="AF62" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF62" s="20">
+        <f t="shared" si="7"/>
         <v>14.870808092485918</v>
       </c>
     </row>
@@ -6573,23 +6573,23 @@
       <c r="X63" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="Z63" s="21">
+      <c r="Z63" s="18">
         <v>9402253</v>
       </c>
-      <c r="AB63" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB63" s="18">
+        <f t="shared" si="4"/>
         <v>2824142</v>
       </c>
-      <c r="AC63" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC63" s="18">
+        <f t="shared" si="5"/>
         <v>1398191</v>
       </c>
-      <c r="AE63" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE63" s="20">
+        <f t="shared" si="6"/>
         <v>30.036864568524162</v>
       </c>
-      <c r="AF63" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF63" s="20">
+        <f t="shared" si="7"/>
         <v>14.870808092485918</v>
       </c>
     </row>
@@ -6664,23 +6664,23 @@
       <c r="X64" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z64" s="21">
+      <c r="Z64" s="18">
         <v>1931867</v>
       </c>
-      <c r="AB64" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB64" s="18">
+        <f t="shared" si="4"/>
         <v>951677</v>
       </c>
-      <c r="AC64" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC64" s="18">
+        <f t="shared" si="5"/>
         <v>706599</v>
       </c>
-      <c r="AE64" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE64" s="20">
+        <f t="shared" si="6"/>
         <v>49.262035119394866</v>
       </c>
-      <c r="AF64" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF64" s="20">
+        <f t="shared" si="7"/>
         <v>36.575965115610956</v>
       </c>
     </row>
@@ -6755,23 +6755,23 @@
       <c r="X65" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z65" s="21">
+      <c r="Z65" s="18">
         <v>840597</v>
       </c>
-      <c r="AB65" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB65" s="18">
+        <f t="shared" si="4"/>
         <v>164605</v>
       </c>
-      <c r="AC65" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC65" s="18">
+        <f t="shared" si="5"/>
         <v>24418</v>
       </c>
-      <c r="AE65" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE65" s="20">
+        <f t="shared" si="6"/>
         <v>19.581916185758455</v>
       </c>
-      <c r="AF65" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF65" s="20">
+        <f t="shared" si="7"/>
         <v>2.9048402504410555</v>
       </c>
     </row>
@@ -6846,23 +6846,23 @@
       <c r="X66" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z66" s="21">
+      <c r="Z66" s="18">
         <v>761995</v>
       </c>
-      <c r="AB66" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB66" s="18">
+        <f t="shared" si="4"/>
         <v>124685</v>
       </c>
-      <c r="AC66" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC66" s="18">
+        <f t="shared" si="5"/>
         <v>23178</v>
       </c>
-      <c r="AE66" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE66" s="20">
+        <f t="shared" si="6"/>
         <v>16.362968260946595</v>
       </c>
-      <c r="AF66" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF66" s="20">
+        <f t="shared" si="7"/>
         <v>3.0417522424687826</v>
       </c>
     </row>
@@ -6937,23 +6937,23 @@
       <c r="X67" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z67" s="21">
+      <c r="Z67" s="18">
         <v>579592</v>
       </c>
-      <c r="AB67" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB67" s="18">
+        <f t="shared" si="4"/>
         <v>139072</v>
       </c>
-      <c r="AC67" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC67" s="18">
+        <f t="shared" si="5"/>
         <v>26093</v>
       </c>
-      <c r="AE67" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE67" s="20">
+        <f t="shared" si="6"/>
         <v>23.994810142307003</v>
       </c>
-      <c r="AF67" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF67" s="20">
+        <f t="shared" si="7"/>
         <v>4.5019599994478874</v>
       </c>
     </row>
@@ -7028,23 +7028,23 @@
       <c r="X68" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z68" s="21">
+      <c r="Z68" s="18">
         <v>1160662</v>
       </c>
-      <c r="AB68" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB68" s="18">
+        <f t="shared" si="4"/>
         <v>269810</v>
       </c>
-      <c r="AC68" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC68" s="18">
+        <f t="shared" si="5"/>
         <v>50385</v>
       </c>
-      <c r="AE68" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE68" s="20">
+        <f t="shared" si="6"/>
         <v>23.246216383408779</v>
       </c>
-      <c r="AF68" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF68" s="20">
+        <f t="shared" si="7"/>
         <v>4.3410570863869067</v>
       </c>
     </row>
@@ -7119,23 +7119,23 @@
       <c r="X69" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z69" s="21">
+      <c r="Z69" s="18">
         <v>1403901</v>
       </c>
-      <c r="AB69" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB69" s="18">
+        <f t="shared" si="4"/>
         <v>664220</v>
       </c>
-      <c r="AC69" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC69" s="18">
+        <f t="shared" si="5"/>
         <v>461774</v>
       </c>
-      <c r="AE69" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE69" s="20">
+        <f t="shared" si="6"/>
         <v>47.312452943619242</v>
       </c>
-      <c r="AF69" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF69" s="20">
+        <f t="shared" si="7"/>
         <v>32.892205362059009</v>
       </c>
     </row>
@@ -7210,23 +7210,23 @@
       <c r="X70" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z70" s="21">
+      <c r="Z70" s="18">
         <v>553633</v>
       </c>
-      <c r="AB70" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB70" s="18">
+        <f t="shared" si="4"/>
         <v>111178</v>
       </c>
-      <c r="AC70" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC70" s="18">
+        <f t="shared" si="5"/>
         <v>26966</v>
       </c>
-      <c r="AE70" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE70" s="20">
+        <f t="shared" si="6"/>
         <v>20.081534157104073</v>
       </c>
-      <c r="AF70" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF70" s="20">
+        <f t="shared" si="7"/>
         <v>4.8707356678521689</v>
       </c>
     </row>
@@ -7301,23 +7301,23 @@
       <c r="X71" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z71" s="21">
+      <c r="Z71" s="18">
         <v>814947</v>
       </c>
-      <c r="AB71" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB71" s="18">
+        <f t="shared" si="4"/>
         <v>150183</v>
       </c>
-      <c r="AC71" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC71" s="18">
+        <f t="shared" si="5"/>
         <v>29896</v>
       </c>
-      <c r="AE71" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE71" s="20">
+        <f t="shared" si="6"/>
         <v>18.428560384908465</v>
       </c>
-      <c r="AF71" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF71" s="20">
+        <f t="shared" si="7"/>
         <v>3.668459421287519</v>
       </c>
     </row>
@@ -7392,23 +7392,23 @@
       <c r="X72" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z72" s="21">
+      <c r="Z72" s="18">
         <v>582913</v>
       </c>
-      <c r="AB72" s="21">
-        <f t="shared" si="0"/>
+      <c r="AB72" s="18">
+        <f t="shared" si="4"/>
         <v>92813</v>
       </c>
-      <c r="AC72" s="21">
-        <f t="shared" si="1"/>
+      <c r="AC72" s="18">
+        <f t="shared" si="5"/>
         <v>22648</v>
       </c>
-      <c r="AE72" s="23">
-        <f t="shared" si="2"/>
+      <c r="AE72" s="20">
+        <f t="shared" si="6"/>
         <v>15.922273135099063</v>
       </c>
-      <c r="AF72" s="23">
-        <f t="shared" si="3"/>
+      <c r="AF72" s="20">
+        <f t="shared" si="7"/>
         <v>3.885313931924661</v>
       </c>
     </row>
@@ -7483,23 +7483,23 @@
       <c r="X73" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z73" s="21">
+      <c r="Z73" s="18">
         <v>772146</v>
       </c>
-      <c r="AB73" s="21">
-        <f t="shared" ref="AB73:AB114" si="10">N(C73)+N(E73)+N(G73)+N(I73)+N(K73)+N(N73)+N(P73)+N(R73)+N(T73)+N(V73)+N(X73)</f>
+      <c r="AB73" s="18">
+        <f t="shared" ref="AB73:AB114" si="14">N(C73)+N(E73)+N(G73)+N(I73)+N(K73)+N(N73)+N(P73)+N(R73)+N(T73)+N(V73)+N(X73)</f>
         <v>155899</v>
       </c>
-      <c r="AC73" s="21">
-        <f t="shared" ref="AC73:AC114" si="11">N(I73)+N(K73)+N(X73)</f>
+      <c r="AC73" s="18">
+        <f t="shared" ref="AC73:AC114" si="15">N(I73)+N(K73)+N(X73)</f>
         <v>26234</v>
       </c>
-      <c r="AE73" s="23">
-        <f t="shared" ref="AE73:AE114" si="12">AB73/Z73*100</f>
+      <c r="AE73" s="20">
+        <f t="shared" ref="AE73:AE114" si="16">AB73/Z73*100</f>
         <v>20.190352601710039</v>
       </c>
-      <c r="AF73" s="23">
-        <f t="shared" ref="AF73:AF114" si="13">AC73/Z73*100</f>
+      <c r="AF73" s="20">
+        <f t="shared" ref="AF73:AF114" si="17">AC73/Z73*100</f>
         <v>3.3975439877950544</v>
       </c>
     </row>
@@ -7528,212 +7528,212 @@
       <c r="V74" s="7"/>
       <c r="W74" s="7"/>
       <c r="X74" s="7"/>
-      <c r="AB74" s="21"/>
-      <c r="AC74" s="21"/>
-      <c r="AE74" s="23"/>
-      <c r="AF74" s="23"/>
+      <c r="AB74" s="18"/>
+      <c r="AC74" s="18"/>
+      <c r="AE74" s="20"/>
+      <c r="AF74" s="20"/>
     </row>
     <row r="75" spans="1:32">
       <c r="A75" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B75" s="18">
+      <c r="B75" s="15">
         <f>B76-B77</f>
         <v>0</v>
       </c>
-      <c r="C75" s="18">
-        <f t="shared" ref="C75:K75" si="14">C76-C77</f>
+      <c r="C75" s="15">
+        <f t="shared" ref="C75:K75" si="18">C76-C77</f>
         <v>0</v>
       </c>
-      <c r="D75" s="18">
-        <f t="shared" si="14"/>
+      <c r="D75" s="15">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="E75" s="18">
-        <f t="shared" si="14"/>
+      <c r="E75" s="15">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="F75" s="18">
-        <f t="shared" si="14"/>
+      <c r="F75" s="15">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G75" s="18">
-        <f t="shared" si="14"/>
+      <c r="G75" s="15">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H75" s="18">
-        <f t="shared" si="14"/>
+      <c r="H75" s="15">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="I75" s="18">
-        <f t="shared" si="14"/>
+      <c r="I75" s="15">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J75" s="18">
-        <f t="shared" si="14"/>
+      <c r="J75" s="15">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="K75" s="18">
-        <f t="shared" si="14"/>
+      <c r="K75" s="15">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L75" s="19"/>
-      <c r="M75" s="18">
-        <f t="shared" ref="M75:V75" si="15">M76-M77</f>
+      <c r="L75" s="16"/>
+      <c r="M75" s="15">
+        <f t="shared" ref="M75:V75" si="19">M76-M77</f>
         <v>0</v>
       </c>
-      <c r="N75" s="18">
-        <f t="shared" si="15"/>
+      <c r="N75" s="15">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O75" s="18">
-        <f t="shared" si="15"/>
+      <c r="O75" s="15">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P75" s="18">
-        <f t="shared" si="15"/>
+      <c r="P75" s="15">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q75" s="18">
-        <f t="shared" si="15"/>
+      <c r="Q75" s="15">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R75" s="18">
-        <f t="shared" si="15"/>
+      <c r="R75" s="15">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="S75" s="18">
-        <f t="shared" si="15"/>
+      <c r="S75" s="15">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="T75" s="18">
-        <f t="shared" si="15"/>
+      <c r="T75" s="15">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="U75" s="18">
-        <f t="shared" si="15"/>
+      <c r="U75" s="15">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V75" s="18">
-        <f t="shared" si="15"/>
+      <c r="V75" s="15">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="W75" s="7"/>
       <c r="X75" s="7"/>
-      <c r="Z75" s="18">
-        <f t="shared" ref="Z75" si="16">Z76-Z77</f>
+      <c r="Z75" s="15">
+        <f t="shared" ref="Z75" si="20">Z76-Z77</f>
         <v>0</v>
       </c>
-      <c r="AB75" s="21"/>
-      <c r="AC75" s="21"/>
-      <c r="AE75" s="23"/>
-      <c r="AF75" s="23"/>
+      <c r="AB75" s="18"/>
+      <c r="AC75" s="18"/>
+      <c r="AE75" s="20"/>
+      <c r="AF75" s="20"/>
     </row>
     <row r="76" spans="1:32">
       <c r="A76" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B76" s="18">
+      <c r="B76" s="15">
         <f>SUM(B78:B88)</f>
         <v>7</v>
       </c>
-      <c r="C76" s="18">
-        <f t="shared" ref="C76:K76" si="17">SUM(C78:C88)</f>
+      <c r="C76" s="15">
+        <f t="shared" ref="C76:K76" si="21">SUM(C78:C88)</f>
         <v>23612</v>
       </c>
-      <c r="D76" s="18">
-        <f t="shared" si="17"/>
+      <c r="D76" s="15">
+        <f t="shared" si="21"/>
         <v>13</v>
       </c>
-      <c r="E76" s="18">
-        <f t="shared" si="17"/>
+      <c r="E76" s="15">
+        <f t="shared" si="21"/>
         <v>104893</v>
       </c>
-      <c r="F76" s="18">
-        <f t="shared" si="17"/>
+      <c r="F76" s="15">
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
-      <c r="G76" s="18">
-        <f t="shared" si="17"/>
+      <c r="G76" s="15">
+        <f t="shared" si="21"/>
         <v>169622</v>
       </c>
-      <c r="H76" s="18">
-        <f t="shared" si="17"/>
+      <c r="H76" s="15">
+        <f t="shared" si="21"/>
         <v>13</v>
       </c>
-      <c r="I76" s="18">
-        <f t="shared" si="17"/>
+      <c r="I76" s="15">
+        <f t="shared" si="21"/>
         <v>400729</v>
       </c>
-      <c r="J76" s="18">
-        <f t="shared" si="17"/>
+      <c r="J76" s="15">
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
-      <c r="K76" s="18">
-        <f t="shared" si="17"/>
+      <c r="K76" s="15">
+        <f t="shared" si="21"/>
         <v>337100</v>
       </c>
-      <c r="L76" s="19"/>
-      <c r="M76" s="18">
-        <f t="shared" ref="M76:V76" si="18">SUM(M78:M88)</f>
+      <c r="L76" s="16"/>
+      <c r="M76" s="15">
+        <f t="shared" ref="M76:V76" si="22">SUM(M78:M88)</f>
         <v>265</v>
       </c>
-      <c r="N76" s="18">
-        <f t="shared" si="18"/>
+      <c r="N76" s="15">
+        <f t="shared" si="22"/>
         <v>635873</v>
       </c>
-      <c r="O76" s="18">
-        <f t="shared" si="18"/>
+      <c r="O76" s="15">
+        <f t="shared" si="22"/>
         <v>115</v>
       </c>
-      <c r="P76" s="18">
-        <f t="shared" si="18"/>
+      <c r="P76" s="15">
+        <f t="shared" si="22"/>
         <v>395941</v>
       </c>
-      <c r="Q76" s="18">
-        <f t="shared" si="18"/>
+      <c r="Q76" s="15">
+        <f t="shared" si="22"/>
         <v>92</v>
       </c>
-      <c r="R76" s="18">
-        <f t="shared" si="18"/>
+      <c r="R76" s="15">
+        <f t="shared" si="22"/>
         <v>413925</v>
       </c>
-      <c r="S76" s="18">
-        <f t="shared" si="18"/>
+      <c r="S76" s="15">
+        <f t="shared" si="22"/>
         <v>150</v>
       </c>
-      <c r="T76" s="18">
-        <f t="shared" si="18"/>
+      <c r="T76" s="15">
+        <f t="shared" si="22"/>
         <v>1037053</v>
       </c>
-      <c r="U76" s="18">
-        <f t="shared" si="18"/>
+      <c r="U76" s="15">
+        <f t="shared" si="22"/>
         <v>46</v>
       </c>
-      <c r="V76" s="18">
-        <f t="shared" si="18"/>
+      <c r="V76" s="15">
+        <f t="shared" si="22"/>
         <v>539331</v>
       </c>
       <c r="W76" s="7"/>
       <c r="X76" s="7"/>
-      <c r="Z76" s="18">
-        <f t="shared" ref="Z76" si="19">SUM(Z78:Z88)</f>
+      <c r="Z76" s="15">
+        <f t="shared" ref="Z76" si="23">SUM(Z78:Z88)</f>
         <v>9289364</v>
       </c>
-      <c r="AB76" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB76" s="18">
+        <f t="shared" si="14"/>
         <v>4058079</v>
       </c>
-      <c r="AC76" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC76" s="18">
+        <f t="shared" si="15"/>
         <v>737829</v>
       </c>
-      <c r="AE76" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE76" s="20">
+        <f t="shared" si="16"/>
         <v>43.685218923491426</v>
       </c>
-      <c r="AF76" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF76" s="20">
+        <f t="shared" si="17"/>
         <v>7.9427289101815806</v>
       </c>
     </row>
@@ -7808,23 +7808,23 @@
       <c r="X77" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="Z77" s="21">
+      <c r="Z77" s="18">
         <v>9289364</v>
       </c>
-      <c r="AB77" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB77" s="18">
+        <f t="shared" si="14"/>
         <v>4058079</v>
       </c>
-      <c r="AC77" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC77" s="18">
+        <f t="shared" si="15"/>
         <v>737829</v>
       </c>
-      <c r="AE77" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE77" s="20">
+        <f t="shared" si="16"/>
         <v>43.685218923491426</v>
       </c>
-      <c r="AF77" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF77" s="20">
+        <f t="shared" si="17"/>
         <v>7.9427289101815806</v>
       </c>
     </row>
@@ -7899,23 +7899,23 @@
       <c r="X78" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z78" s="21">
+      <c r="Z78" s="18">
         <v>826716</v>
       </c>
-      <c r="AB78" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB78" s="18">
+        <f t="shared" si="14"/>
         <v>230688</v>
       </c>
-      <c r="AC78" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC78" s="18">
+        <f t="shared" si="15"/>
         <v>131911</v>
       </c>
-      <c r="AE78" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE78" s="20">
+        <f t="shared" si="16"/>
         <v>27.904141204476506</v>
       </c>
-      <c r="AF78" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF78" s="20">
+        <f t="shared" si="17"/>
         <v>15.95602359214047</v>
       </c>
     </row>
@@ -7990,23 +7990,23 @@
       <c r="X79" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z79" s="21">
+      <c r="Z79" s="18">
         <v>571154</v>
       </c>
-      <c r="AB79" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB79" s="18">
+        <f t="shared" si="14"/>
         <v>113197</v>
       </c>
-      <c r="AC79" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC79" s="18">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE79" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE79" s="20">
+        <f t="shared" si="16"/>
         <v>19.81899802855272</v>
       </c>
-      <c r="AF79" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF79" s="20">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -8081,23 +8081,23 @@
       <c r="X80" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z80" s="21">
+      <c r="Z80" s="18">
         <v>878415</v>
       </c>
-      <c r="AB80" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB80" s="18">
+        <f t="shared" si="14"/>
         <v>168284</v>
       </c>
-      <c r="AC80" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC80" s="18">
+        <f t="shared" si="15"/>
         <v>84240</v>
       </c>
-      <c r="AE80" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE80" s="20">
+        <f t="shared" si="16"/>
         <v>19.157687425647328</v>
       </c>
-      <c r="AF80" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF80" s="20">
+        <f t="shared" si="17"/>
         <v>9.5900001707621119</v>
       </c>
     </row>
@@ -8172,23 +8172,23 @@
       <c r="X81" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z81" s="21">
+      <c r="Z81" s="18">
         <v>290654</v>
       </c>
-      <c r="AB81" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB81" s="18">
+        <f t="shared" si="14"/>
         <v>42148</v>
       </c>
-      <c r="AC81" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC81" s="18">
+        <f t="shared" si="15"/>
         <v>20805</v>
       </c>
-      <c r="AE81" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE81" s="20">
+        <f t="shared" si="16"/>
         <v>14.501090643858333</v>
       </c>
-      <c r="AF81" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF81" s="20">
+        <f t="shared" si="17"/>
         <v>7.1579954172314846</v>
       </c>
     </row>
@@ -8263,23 +8263,23 @@
       <c r="X82" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z82" s="21">
+      <c r="Z82" s="18">
         <v>1918881</v>
       </c>
-      <c r="AB82" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB82" s="18">
+        <f t="shared" si="14"/>
         <v>1444278</v>
       </c>
-      <c r="AC82" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC82" s="18">
+        <f t="shared" si="15"/>
         <v>135347</v>
       </c>
-      <c r="AE82" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE82" s="20">
+        <f t="shared" si="16"/>
         <v>75.266678861273846</v>
       </c>
-      <c r="AF82" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF82" s="20">
+        <f t="shared" si="17"/>
         <v>7.0534337460217698</v>
       </c>
     </row>
@@ -8354,23 +8354,23 @@
       <c r="X83" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z83" s="21">
+      <c r="Z83" s="18">
         <v>1058241</v>
       </c>
-      <c r="AB83" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB83" s="18">
+        <f t="shared" si="14"/>
         <v>229420</v>
       </c>
-      <c r="AC83" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC83" s="18">
+        <f t="shared" si="15"/>
         <v>60984</v>
       </c>
-      <c r="AE83" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE83" s="20">
+        <f t="shared" si="16"/>
         <v>21.679371712114726</v>
       </c>
-      <c r="AF83" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF83" s="20">
+        <f t="shared" si="17"/>
         <v>5.7627704842280725</v>
       </c>
     </row>
@@ -8445,23 +8445,23 @@
       <c r="X84" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z84" s="21">
+      <c r="Z84" s="18">
         <v>873301</v>
       </c>
-      <c r="AB84" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB84" s="18">
+        <f t="shared" si="14"/>
         <v>749856</v>
       </c>
-      <c r="AC84" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC84" s="18">
+        <f t="shared" si="15"/>
         <v>41590</v>
       </c>
-      <c r="AE84" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE84" s="20">
+        <f t="shared" si="16"/>
         <v>85.864553000626358</v>
       </c>
-      <c r="AF84" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF84" s="20">
+        <f t="shared" si="17"/>
         <v>4.7623900579525271</v>
       </c>
     </row>
@@ -8536,23 +8536,23 @@
       <c r="X85" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z85" s="21">
+      <c r="Z85" s="18">
         <v>933936</v>
       </c>
-      <c r="AB85" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB85" s="18">
+        <f t="shared" si="14"/>
         <v>485817</v>
       </c>
-      <c r="AC85" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC85" s="18">
+        <f t="shared" si="15"/>
         <v>43740</v>
       </c>
-      <c r="AE85" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE85" s="20">
+        <f t="shared" si="16"/>
         <v>52.018232512720353</v>
       </c>
-      <c r="AF85" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF85" s="20">
+        <f t="shared" si="17"/>
         <v>4.6834044302821605</v>
       </c>
     </row>
@@ -8627,23 +8627,23 @@
       <c r="X86" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z86" s="21">
+      <c r="Z86" s="18">
         <v>1051032</v>
       </c>
-      <c r="AB86" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB86" s="18">
+        <f t="shared" si="14"/>
         <v>391657</v>
       </c>
-      <c r="AC86" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC86" s="18">
+        <f t="shared" si="15"/>
         <v>159590</v>
       </c>
-      <c r="AE86" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE86" s="20">
+        <f t="shared" si="16"/>
         <v>37.26404143736822</v>
       </c>
-      <c r="AF86" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF86" s="20">
+        <f t="shared" si="17"/>
         <v>15.18412379451815</v>
       </c>
     </row>
@@ -8718,23 +8718,23 @@
       <c r="X87" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z87" s="21">
+      <c r="Z87" s="18">
         <v>57478</v>
       </c>
-      <c r="AB87" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB87" s="18">
+        <f t="shared" si="14"/>
         <v>21742</v>
       </c>
-      <c r="AC87" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC87" s="18">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE87" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE87" s="20">
+        <f t="shared" si="16"/>
         <v>37.82664671700477</v>
       </c>
-      <c r="AF87" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF87" s="20">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -8809,23 +8809,23 @@
       <c r="X88" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z88" s="21">
+      <c r="Z88" s="18">
         <v>829556</v>
       </c>
-      <c r="AB88" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB88" s="18">
+        <f t="shared" si="14"/>
         <v>180992</v>
       </c>
-      <c r="AC88" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC88" s="18">
+        <f t="shared" si="15"/>
         <v>59622</v>
       </c>
-      <c r="AE88" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE88" s="20">
+        <f t="shared" si="16"/>
         <v>21.817936341850338</v>
       </c>
-      <c r="AF88" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF88" s="20">
+        <f t="shared" si="17"/>
         <v>7.1872182227601282</v>
       </c>
     </row>
@@ -8854,200 +8854,200 @@
       <c r="V89" s="7"/>
       <c r="W89" s="7"/>
       <c r="X89" s="7"/>
-      <c r="AB89" s="21"/>
-      <c r="AC89" s="21"/>
-      <c r="AE89" s="23"/>
-      <c r="AF89" s="23"/>
+      <c r="AB89" s="18"/>
+      <c r="AC89" s="18"/>
+      <c r="AE89" s="20"/>
+      <c r="AF89" s="20"/>
     </row>
     <row r="90" spans="1:32">
       <c r="A90" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B90" s="18">
+      <c r="B90" s="15">
         <f>B91-B92</f>
         <v>0</v>
       </c>
-      <c r="C90" s="18">
-        <f t="shared" ref="C90:K90" si="20">C91-C92</f>
+      <c r="C90" s="15">
+        <f t="shared" ref="C90:K90" si="24">C91-C92</f>
         <v>0</v>
       </c>
-      <c r="D90" s="18">
-        <f t="shared" si="20"/>
+      <c r="D90" s="15">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="E90" s="18">
-        <f t="shared" si="20"/>
+      <c r="E90" s="15">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="F90" s="18">
-        <f t="shared" si="20"/>
+      <c r="F90" s="15">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G90" s="18">
-        <f t="shared" si="20"/>
+      <c r="G90" s="15">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="H90" s="18">
-        <f t="shared" si="20"/>
+      <c r="H90" s="15">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="I90" s="18">
-        <f t="shared" si="20"/>
+      <c r="I90" s="15">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J90" s="18">
-        <f t="shared" si="20"/>
+      <c r="J90" s="15">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K90" s="18">
-        <f t="shared" si="20"/>
+      <c r="K90" s="15">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L90" s="19"/>
-      <c r="M90" s="18">
-        <f t="shared" ref="M90:V90" si="21">M91-M92</f>
+      <c r="L90" s="16"/>
+      <c r="M90" s="15">
+        <f t="shared" ref="M90:T90" si="25">M91-M92</f>
         <v>0</v>
       </c>
-      <c r="N90" s="18">
-        <f t="shared" si="21"/>
+      <c r="N90" s="15">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="O90" s="18">
-        <f t="shared" si="21"/>
+      <c r="O90" s="15">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="P90" s="18">
-        <f t="shared" si="21"/>
+      <c r="P90" s="15">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="Q90" s="18">
-        <f t="shared" si="21"/>
+      <c r="Q90" s="15">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="R90" s="18">
-        <f t="shared" si="21"/>
+      <c r="R90" s="15">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="S90" s="18">
-        <f t="shared" si="21"/>
+      <c r="S90" s="15">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="T90" s="18">
-        <f t="shared" si="21"/>
+      <c r="T90" s="15">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U90" s="6"/>
       <c r="V90" s="6"/>
       <c r="W90" s="7"/>
       <c r="X90" s="7"/>
-      <c r="Z90" s="18">
-        <f t="shared" ref="Z90" si="22">Z91-Z92</f>
+      <c r="Z90" s="15">
+        <f t="shared" ref="Z90" si="26">Z91-Z92</f>
         <v>0</v>
       </c>
-      <c r="AB90" s="21"/>
-      <c r="AC90" s="21"/>
-      <c r="AE90" s="23"/>
-      <c r="AF90" s="23"/>
+      <c r="AB90" s="18"/>
+      <c r="AC90" s="18"/>
+      <c r="AE90" s="20"/>
+      <c r="AF90" s="20"/>
     </row>
     <row r="91" spans="1:32">
       <c r="A91" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B91" s="18">
+      <c r="B91" s="15">
         <f>SUM(B93:B101)</f>
         <v>5</v>
       </c>
-      <c r="C91" s="18">
-        <f t="shared" ref="C91:K91" si="23">SUM(C93:C101)</f>
+      <c r="C91" s="15">
+        <f t="shared" ref="C91:K91" si="27">SUM(C93:C101)</f>
         <v>15912</v>
       </c>
-      <c r="D91" s="18">
-        <f t="shared" si="23"/>
+      <c r="D91" s="15">
+        <f t="shared" si="27"/>
         <v>13</v>
       </c>
-      <c r="E91" s="18">
-        <f t="shared" si="23"/>
+      <c r="E91" s="15">
+        <f t="shared" si="27"/>
         <v>91574</v>
       </c>
-      <c r="F91" s="18">
-        <f t="shared" si="23"/>
+      <c r="F91" s="15">
+        <f t="shared" si="27"/>
         <v>8</v>
       </c>
-      <c r="G91" s="18">
-        <f t="shared" si="23"/>
+      <c r="G91" s="15">
+        <f t="shared" si="27"/>
         <v>98312</v>
       </c>
-      <c r="H91" s="18">
-        <f t="shared" si="23"/>
+      <c r="H91" s="15">
+        <f t="shared" si="27"/>
         <v>6</v>
       </c>
-      <c r="I91" s="18">
-        <f t="shared" si="23"/>
+      <c r="I91" s="15">
+        <f t="shared" si="27"/>
         <v>159508</v>
       </c>
-      <c r="J91" s="18">
-        <f t="shared" si="23"/>
-        <v>2</v>
-      </c>
-      <c r="K91" s="18">
-        <f t="shared" si="23"/>
+      <c r="J91" s="15">
+        <f t="shared" si="27"/>
+        <v>2</v>
+      </c>
+      <c r="K91" s="15">
+        <f t="shared" si="27"/>
         <v>103683</v>
       </c>
-      <c r="L91" s="19"/>
-      <c r="M91" s="18">
-        <f t="shared" ref="M91:V91" si="24">SUM(M93:M101)</f>
+      <c r="L91" s="16"/>
+      <c r="M91" s="15">
+        <f t="shared" ref="M91:T91" si="28">SUM(M93:M101)</f>
         <v>101</v>
       </c>
-      <c r="N91" s="18">
-        <f t="shared" si="24"/>
+      <c r="N91" s="15">
+        <f t="shared" si="28"/>
         <v>243191</v>
       </c>
-      <c r="O91" s="18">
+      <c r="O91" s="15">
         <f>SUM(O93:O101)</f>
         <v>40</v>
       </c>
-      <c r="P91" s="18">
+      <c r="P91" s="15">
         <f>SUM(P93:P101)</f>
         <v>135515</v>
       </c>
-      <c r="Q91" s="18">
-        <f t="shared" si="24"/>
+      <c r="Q91" s="15">
+        <f t="shared" si="28"/>
         <v>12</v>
       </c>
-      <c r="R91" s="18">
-        <f t="shared" si="24"/>
+      <c r="R91" s="15">
+        <f t="shared" si="28"/>
         <v>51601</v>
       </c>
-      <c r="S91" s="18">
-        <f t="shared" si="24"/>
+      <c r="S91" s="15">
+        <f t="shared" si="28"/>
         <v>7</v>
       </c>
-      <c r="T91" s="18">
-        <f t="shared" si="24"/>
+      <c r="T91" s="15">
+        <f t="shared" si="28"/>
         <v>44607</v>
       </c>
       <c r="U91" s="6"/>
       <c r="V91" s="6"/>
       <c r="W91" s="7"/>
       <c r="X91" s="7"/>
-      <c r="Z91" s="18">
-        <f t="shared" ref="Z91" si="25">SUM(Z93:Z101)</f>
+      <c r="Z91" s="15">
+        <f t="shared" ref="Z91" si="29">SUM(Z93:Z101)</f>
         <v>5758822</v>
       </c>
-      <c r="AB91" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB91" s="18">
+        <f t="shared" si="14"/>
         <v>943903</v>
       </c>
-      <c r="AC91" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC91" s="18">
+        <f t="shared" si="15"/>
         <v>263191</v>
       </c>
-      <c r="AE91" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE91" s="20">
+        <f t="shared" si="16"/>
         <v>16.390556957655576</v>
       </c>
-      <c r="AF91" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF91" s="20">
+        <f t="shared" si="17"/>
         <v>4.5702228684963693</v>
       </c>
     </row>
@@ -9122,23 +9122,23 @@
       <c r="X92" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="Z92" s="21">
+      <c r="Z92" s="18">
         <v>5758822</v>
       </c>
-      <c r="AB92" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB92" s="18">
+        <f t="shared" si="14"/>
         <v>943903</v>
       </c>
-      <c r="AC92" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC92" s="18">
+        <f t="shared" si="15"/>
         <v>263191</v>
       </c>
-      <c r="AE92" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE92" s="20">
+        <f t="shared" si="16"/>
         <v>16.390556957655576</v>
       </c>
-      <c r="AF92" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF92" s="20">
+        <f t="shared" si="17"/>
         <v>4.5702228684963693</v>
       </c>
     </row>
@@ -9213,23 +9213,23 @@
       <c r="X93" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z93" s="21">
+      <c r="Z93" s="18">
         <v>120306</v>
       </c>
-      <c r="AB93" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB93" s="18">
+        <f t="shared" si="14"/>
         <v>35871</v>
       </c>
-      <c r="AC93" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC93" s="18">
+        <f t="shared" si="15"/>
         <v>32834</v>
       </c>
-      <c r="AE93" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE93" s="20">
+        <f t="shared" si="16"/>
         <v>29.816468006583214</v>
       </c>
-      <c r="AF93" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF93" s="20">
+        <f t="shared" si="17"/>
         <v>27.292071883364088</v>
       </c>
     </row>
@@ -9304,23 +9304,23 @@
       <c r="X94" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z94" s="21">
+      <c r="Z94" s="18">
         <v>570161</v>
       </c>
-      <c r="AB94" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB94" s="18">
+        <f t="shared" si="14"/>
         <v>78535</v>
       </c>
-      <c r="AC94" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC94" s="18">
+        <f t="shared" si="15"/>
         <v>26699</v>
       </c>
-      <c r="AE94" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE94" s="20">
+        <f t="shared" si="16"/>
         <v>13.774179573839671</v>
       </c>
-      <c r="AF94" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF94" s="20">
+        <f t="shared" si="17"/>
         <v>4.6827124268408395</v>
       </c>
     </row>
@@ -9395,23 +9395,23 @@
       <c r="X95" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z95" s="21">
+      <c r="Z95" s="18">
         <v>672037</v>
       </c>
-      <c r="AB95" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB95" s="18">
+        <f t="shared" si="14"/>
         <v>80764</v>
       </c>
-      <c r="AC95" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC95" s="18">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE95" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE95" s="20">
+        <f t="shared" si="16"/>
         <v>12.017790687119906</v>
       </c>
-      <c r="AF95" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF95" s="20">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -9486,23 +9486,23 @@
       <c r="X96" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z96" s="21">
+      <c r="Z96" s="18">
         <v>514267</v>
       </c>
-      <c r="AB96" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB96" s="18">
+        <f t="shared" si="14"/>
         <v>107104</v>
       </c>
-      <c r="AC96" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC96" s="18">
+        <f t="shared" si="15"/>
         <v>51473</v>
       </c>
-      <c r="AE96" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE96" s="20">
+        <f t="shared" si="16"/>
         <v>20.826535632268843</v>
       </c>
-      <c r="AF96" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF96" s="20">
+        <f t="shared" si="17"/>
         <v>10.009003105390779</v>
       </c>
     </row>
@@ -9577,23 +9577,23 @@
       <c r="X97" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z97" s="21">
+      <c r="Z97" s="18">
         <v>223336</v>
       </c>
-      <c r="AB97" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB97" s="18">
+        <f t="shared" si="14"/>
         <v>67647</v>
       </c>
-      <c r="AC97" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC97" s="18">
+        <f t="shared" si="15"/>
         <v>28933</v>
       </c>
-      <c r="AE97" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE97" s="20">
+        <f t="shared" si="16"/>
         <v>30.289339828778161</v>
       </c>
-      <c r="AF97" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF97" s="20">
+        <f t="shared" si="17"/>
         <v>12.954919941254433</v>
       </c>
     </row>
@@ -9668,23 +9668,23 @@
       <c r="X98" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z98" s="21">
+      <c r="Z98" s="18">
         <v>28113</v>
       </c>
-      <c r="AB98" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB98" s="18">
+        <f t="shared" si="14"/>
         <v>6893</v>
       </c>
-      <c r="AC98" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC98" s="18">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE98" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE98" s="20">
+        <f t="shared" si="16"/>
         <v>24.518905844271334</v>
       </c>
-      <c r="AF98" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF98" s="20">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -9759,23 +9759,23 @@
       <c r="X99" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z99" s="21">
+      <c r="Z99" s="18">
         <v>1433043</v>
       </c>
-      <c r="AB99" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB99" s="18">
+        <f t="shared" si="14"/>
         <v>105371</v>
       </c>
-      <c r="AC99" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC99" s="18">
+        <f t="shared" si="15"/>
         <v>49969</v>
       </c>
-      <c r="AE99" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE99" s="20">
+        <f t="shared" si="16"/>
         <v>7.3529545170661308</v>
       </c>
-      <c r="AF99" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF99" s="20">
+        <f t="shared" si="17"/>
         <v>3.4869156054633392</v>
       </c>
     </row>
@@ -9850,23 +9850,23 @@
       <c r="X100" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z100" s="21">
+      <c r="Z100" s="18">
         <v>1927679</v>
       </c>
-      <c r="AB100" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB100" s="18">
+        <f t="shared" si="14"/>
         <v>455183</v>
       </c>
-      <c r="AC100" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC100" s="18">
+        <f t="shared" si="15"/>
         <v>73283</v>
       </c>
-      <c r="AE100" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE100" s="20">
+        <f t="shared" si="16"/>
         <v>23.613008182378913</v>
       </c>
-      <c r="AF100" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF100" s="20">
+        <f t="shared" si="17"/>
         <v>3.8016184229843248</v>
       </c>
     </row>
@@ -9941,23 +9941,23 @@
       <c r="X101" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z101" s="21">
+      <c r="Z101" s="18">
         <v>269880</v>
       </c>
-      <c r="AB101" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB101" s="18">
+        <f t="shared" si="14"/>
         <v>6535</v>
       </c>
-      <c r="AC101" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC101" s="18">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE101" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE101" s="20">
+        <f t="shared" si="16"/>
         <v>2.421446568845413</v>
       </c>
-      <c r="AF101" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF101" s="20">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -9986,11 +9986,11 @@
       <c r="V102" s="7"/>
       <c r="W102" s="7"/>
       <c r="X102" s="7"/>
-      <c r="Z102" s="21"/>
-      <c r="AB102" s="21"/>
-      <c r="AC102" s="21"/>
-      <c r="AE102" s="23"/>
-      <c r="AF102" s="23"/>
+      <c r="Z102" s="18"/>
+      <c r="AB102" s="18"/>
+      <c r="AC102" s="18"/>
+      <c r="AE102" s="20"/>
+      <c r="AF102" s="20"/>
     </row>
     <row r="103" spans="1:32">
       <c r="A103" s="8" t="s">
@@ -10001,92 +10001,92 @@
         <v>0</v>
       </c>
       <c r="C103" s="6">
-        <f t="shared" ref="C103:K103" si="26">C104-C105</f>
+        <f t="shared" ref="C103:K103" si="30">C104-C105</f>
         <v>0</v>
       </c>
       <c r="D103" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E103" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F103" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G103" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I103" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J103" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K103" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L103" s="17"/>
+      <c r="L103" s="14"/>
       <c r="M103" s="6">
-        <f t="shared" ref="M103:V103" si="27">M104-M105</f>
+        <f t="shared" ref="M103:V103" si="31">M104-M105</f>
         <v>0</v>
       </c>
       <c r="N103" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="O103" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="P103" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="Q103" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="R103" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="S103" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="T103" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="U103" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="V103" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="W103" s="7"/>
       <c r="X103" s="7"/>
       <c r="Z103" s="6">
-        <f t="shared" ref="Z103" si="28">Z104-Z105</f>
+        <f t="shared" ref="Z103" si="32">Z104-Z105</f>
         <v>0</v>
       </c>
-      <c r="AB103" s="21"/>
-      <c r="AC103" s="21"/>
-      <c r="AE103" s="23"/>
-      <c r="AF103" s="23"/>
+      <c r="AB103" s="18"/>
+      <c r="AC103" s="18"/>
+      <c r="AE103" s="20"/>
+      <c r="AF103" s="20"/>
     </row>
     <row r="104" spans="1:32">
       <c r="A104" s="8" t="s">
@@ -10097,102 +10097,102 @@
         <v>10</v>
       </c>
       <c r="C104" s="6">
-        <f t="shared" ref="C104:K104" si="29">SUM(C106:C114)</f>
+        <f t="shared" ref="C104:K104" si="33">SUM(C106:C114)</f>
         <v>36697</v>
       </c>
       <c r="D104" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>13</v>
       </c>
       <c r="E104" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>99955</v>
       </c>
       <c r="F104" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>10</v>
       </c>
       <c r="G104" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>143234</v>
       </c>
       <c r="H104" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>9</v>
       </c>
       <c r="I104" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>291836</v>
       </c>
       <c r="J104" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4</v>
       </c>
       <c r="K104" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>354172</v>
       </c>
-      <c r="L104" s="17"/>
+      <c r="L104" s="14"/>
       <c r="M104" s="6">
-        <f t="shared" ref="M104:V104" si="30">SUM(M106:M114)</f>
+        <f t="shared" ref="M104:V104" si="34">SUM(M106:M114)</f>
         <v>206</v>
       </c>
       <c r="N104" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>486543</v>
       </c>
       <c r="O104" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>48</v>
       </c>
       <c r="P104" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>161327</v>
       </c>
       <c r="Q104" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>12</v>
       </c>
       <c r="R104" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>53002</v>
       </c>
       <c r="S104" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>7</v>
       </c>
       <c r="T104" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>45677</v>
       </c>
       <c r="U104" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="V104" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>10974</v>
       </c>
       <c r="W104" s="7"/>
       <c r="X104" s="7"/>
       <c r="Z104" s="6">
-        <f t="shared" ref="Z104" si="31">SUM(Z106:Z114)</f>
+        <f t="shared" ref="Z104" si="35">SUM(Z106:Z114)</f>
         <v>7746718</v>
       </c>
-      <c r="AB104" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB104" s="18">
+        <f t="shared" si="14"/>
         <v>1683417</v>
       </c>
-      <c r="AC104" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC104" s="18">
+        <f t="shared" si="15"/>
         <v>646008</v>
       </c>
-      <c r="AE104" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE104" s="20">
+        <f t="shared" si="16"/>
         <v>21.730712283576089</v>
       </c>
-      <c r="AF104" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF104" s="20">
+        <f t="shared" si="17"/>
         <v>8.3391185789904831</v>
       </c>
     </row>
@@ -10267,23 +10267,23 @@
       <c r="X105" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="Z105" s="21">
+      <c r="Z105" s="18">
         <v>7746718</v>
       </c>
-      <c r="AB105" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB105" s="18">
+        <f t="shared" si="14"/>
         <v>1683417</v>
       </c>
-      <c r="AC105" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC105" s="18">
+        <f t="shared" si="15"/>
         <v>646008</v>
       </c>
-      <c r="AE105" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE105" s="20">
+        <f t="shared" si="16"/>
         <v>21.730712283576089</v>
       </c>
-      <c r="AF105" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF105" s="20">
+        <f t="shared" si="17"/>
         <v>8.3391185789904831</v>
       </c>
     </row>
@@ -10358,23 +10358,23 @@
       <c r="X106" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z106" s="21">
+      <c r="Z106" s="18">
         <v>682608</v>
       </c>
-      <c r="AB106" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB106" s="18">
+        <f t="shared" si="14"/>
         <v>129912</v>
       </c>
-      <c r="AC106" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC106" s="18">
+        <f t="shared" si="15"/>
         <v>37376</v>
       </c>
-      <c r="AE106" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE106" s="20">
+        <f t="shared" si="16"/>
         <v>19.031713662892905</v>
       </c>
-      <c r="AF106" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF106" s="20">
+        <f t="shared" si="17"/>
         <v>5.4754705482502404</v>
       </c>
     </row>
@@ -10449,23 +10449,23 @@
       <c r="X107" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z107" s="21">
+      <c r="Z107" s="18">
         <v>382487</v>
       </c>
-      <c r="AB107" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB107" s="18">
+        <f t="shared" si="14"/>
         <v>45329</v>
       </c>
-      <c r="AC107" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC107" s="18">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE107" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE107" s="20">
+        <f t="shared" si="16"/>
         <v>11.851121737470816</v>
       </c>
-      <c r="AF107" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF107" s="20">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -10540,23 +10540,23 @@
       <c r="X108" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z108" s="21">
+      <c r="Z108" s="18">
         <v>860021</v>
       </c>
-      <c r="AB108" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB108" s="18">
+        <f t="shared" si="14"/>
         <v>161845</v>
       </c>
-      <c r="AC108" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC108" s="18">
+        <f t="shared" si="15"/>
         <v>105858</v>
       </c>
-      <c r="AE108" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE108" s="20">
+        <f t="shared" si="16"/>
         <v>18.818726519468711</v>
       </c>
-      <c r="AF108" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF108" s="20">
+        <f t="shared" si="17"/>
         <v>12.308769204472913</v>
       </c>
     </row>
@@ -10631,23 +10631,23 @@
       <c r="X109" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z109" s="21">
+      <c r="Z109" s="18">
         <v>684590</v>
       </c>
-      <c r="AB109" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB109" s="18">
+        <f t="shared" si="14"/>
         <v>92401</v>
       </c>
-      <c r="AC109" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC109" s="18">
+        <f t="shared" si="15"/>
         <v>26246</v>
       </c>
-      <c r="AE109" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE109" s="20">
+        <f t="shared" si="16"/>
         <v>13.497275741684803</v>
       </c>
-      <c r="AF109" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF109" s="20">
+        <f t="shared" si="17"/>
         <v>3.8338275464146419</v>
       </c>
     </row>
@@ -10722,23 +10722,23 @@
       <c r="X110" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z110" s="21">
+      <c r="Z110" s="18">
         <v>987863</v>
       </c>
-      <c r="AB110" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB110" s="18">
+        <f t="shared" si="14"/>
         <v>142095</v>
       </c>
-      <c r="AC110" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC110" s="18">
+        <f t="shared" si="15"/>
         <v>22744</v>
       </c>
-      <c r="AE110" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE110" s="20">
+        <f t="shared" si="16"/>
         <v>14.384079573787053</v>
       </c>
-      <c r="AF110" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF110" s="20">
+        <f t="shared" si="17"/>
         <v>2.3023435435885342</v>
       </c>
     </row>
@@ -10813,23 +10813,23 @@
       <c r="X111" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z111" s="21">
+      <c r="Z111" s="18">
         <v>1478398</v>
       </c>
-      <c r="AB111" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB111" s="18">
+        <f t="shared" si="14"/>
         <v>417987</v>
       </c>
-      <c r="AC111" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC111" s="18">
+        <f t="shared" si="15"/>
         <v>155673</v>
       </c>
-      <c r="AE111" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE111" s="20">
+        <f t="shared" si="16"/>
         <v>28.272968442868564</v>
       </c>
-      <c r="AF111" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF111" s="20">
+        <f t="shared" si="17"/>
         <v>10.529843790373093</v>
       </c>
     </row>
@@ -10904,23 +10904,23 @@
       <c r="X112" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z112" s="21">
+      <c r="Z112" s="18">
         <v>453416</v>
       </c>
-      <c r="AB112" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB112" s="18">
+        <f t="shared" si="14"/>
         <v>69271</v>
       </c>
-      <c r="AC112" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC112" s="18">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AE112" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE112" s="20">
+        <f t="shared" si="16"/>
         <v>15.277581735095366</v>
       </c>
-      <c r="AF112" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF112" s="20">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -10995,23 +10995,23 @@
       <c r="X113" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z113" s="21">
+      <c r="Z113" s="18">
         <v>645121</v>
       </c>
-      <c r="AB113" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB113" s="18">
+        <f t="shared" si="14"/>
         <v>93289</v>
       </c>
-      <c r="AC113" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC113" s="18">
+        <f t="shared" si="15"/>
         <v>36466</v>
       </c>
-      <c r="AE113" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE113" s="20">
+        <f t="shared" si="16"/>
         <v>14.460698070594507</v>
       </c>
-      <c r="AF113" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF113" s="20">
+        <f t="shared" si="17"/>
         <v>5.652583003808588</v>
       </c>
     </row>
@@ -11086,28 +11086,29 @@
       <c r="X114" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z114" s="21">
+      <c r="Z114" s="18">
         <v>1572214</v>
       </c>
-      <c r="AB114" s="21">
-        <f t="shared" si="10"/>
+      <c r="AB114" s="18">
+        <f t="shared" si="14"/>
         <v>531288</v>
       </c>
-      <c r="AC114" s="21">
-        <f t="shared" si="11"/>
+      <c r="AC114" s="18">
+        <f t="shared" si="15"/>
         <v>261645</v>
       </c>
-      <c r="AE114" s="23">
-        <f t="shared" si="12"/>
+      <c r="AE114" s="20">
+        <f t="shared" si="16"/>
         <v>33.79234633453207</v>
       </c>
-      <c r="AF114" s="23">
-        <f t="shared" si="13"/>
+      <c r="AF114" s="20">
+        <f t="shared" si="17"/>
         <v>16.641818480181449</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="W3:X3"/>
     <mergeCell ref="AB3:AC3"/>
     <mergeCell ref="AE3:AF3"/>
     <mergeCell ref="A1:X1"/>
@@ -11124,7 +11125,6 @@
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11156,95 +11156,95 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:32">
-      <c r="A2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="14" t="s">
+      <c r="A2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
     </row>
     <row r="3" spans="1:32">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14" t="s">
+      <c r="G3" s="25"/>
+      <c r="H3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14" t="s">
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="14" t="s">
+      <c r="K3" s="25"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14" t="s">
+      <c r="N3" s="25"/>
+      <c r="O3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14" t="s">
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14" t="s">
+      <c r="R3" s="25"/>
+      <c r="S3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14" t="s">
+      <c r="T3" s="25"/>
+      <c r="U3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14" t="s">
+      <c r="V3" s="25"/>
+      <c r="W3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="X3" s="14"/>
-      <c r="Z3" s="22" t="s">
+      <c r="X3" s="25"/>
+      <c r="Z3" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="AB3" s="25" t="s">
+      <c r="AB3" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="AC3" s="25"/>
-      <c r="AE3" s="25" t="s">
+      <c r="AC3" s="22"/>
+      <c r="AE3" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="AF3" s="25"/>
+      <c r="AF3" s="22"/>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" s="1"/>
@@ -11278,7 +11278,7 @@
       <c r="K4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="16"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="2" t="s">
         <v>13</v>
       </c>
@@ -11315,19 +11315,19 @@
       <c r="X4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Z4" s="22" t="s">
+      <c r="Z4" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="AB4" s="22" t="s">
+      <c r="AB4" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="AC4" s="22" t="s">
+      <c r="AC4" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="AE4" s="22" t="s">
+      <c r="AE4" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="AF4" s="22" t="s">
+      <c r="AF4" s="19" t="s">
         <v>119</v>
       </c>
     </row>
@@ -11402,22 +11402,22 @@
       <c r="X5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z5" s="21">
+      <c r="Z5" s="18">
         <v>346536</v>
       </c>
-      <c r="AB5" s="21">
+      <c r="AB5" s="18">
         <f t="shared" ref="AB5:AB54" si="0">N(C5)+N(E5)+N(G5)+N(I5)+N(K5)+N(N5)+N(P5)+N(R5)+N(T5)+N(V5)+N(X5)</f>
         <v>34511</v>
       </c>
-      <c r="AC5" s="21">
+      <c r="AC5" s="18">
         <f t="shared" ref="AC5:AC54" si="1">N(I5)+N(K5)+N(X5)</f>
         <v>20882</v>
       </c>
-      <c r="AE5" s="23">
+      <c r="AE5" s="20">
         <f t="shared" ref="AE5:AE54" si="2">AB5/Z5*100</f>
         <v>9.9588498741833469</v>
       </c>
-      <c r="AF5" s="23">
+      <c r="AF5" s="20">
         <f t="shared" ref="AF5:AF54" si="3">AC5/Z5*100</f>
         <v>6.0259251564051066</v>
       </c>
@@ -11493,22 +11493,22 @@
       <c r="X6" s="9">
         <v>20725</v>
       </c>
-      <c r="Z6" s="21">
+      <c r="Z6" s="18">
         <v>1003542</v>
       </c>
-      <c r="AB6" s="21">
+      <c r="AB6" s="18">
         <f t="shared" si="0"/>
         <v>379273</v>
       </c>
-      <c r="AC6" s="21">
+      <c r="AC6" s="18">
         <f t="shared" si="1"/>
         <v>133605</v>
       </c>
-      <c r="AE6" s="23">
+      <c r="AE6" s="20">
         <f t="shared" si="2"/>
         <v>37.793435650924422</v>
       </c>
-      <c r="AF6" s="23">
+      <c r="AF6" s="20">
         <f t="shared" si="3"/>
         <v>13.313344135073567</v>
       </c>
@@ -11584,22 +11584,22 @@
       <c r="X7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z7" s="21">
+      <c r="Z7" s="18">
         <v>1935412</v>
       </c>
-      <c r="AB7" s="21">
+      <c r="AB7" s="18">
         <f t="shared" si="0"/>
         <v>854664</v>
       </c>
-      <c r="AC7" s="21">
+      <c r="AC7" s="18">
         <f t="shared" si="1"/>
         <v>190833</v>
       </c>
-      <c r="AE7" s="23">
+      <c r="AE7" s="20">
         <f t="shared" si="2"/>
         <v>44.159279781255876</v>
       </c>
-      <c r="AF7" s="23">
+      <c r="AF7" s="20">
         <f t="shared" si="3"/>
         <v>9.8600711373082319</v>
       </c>
@@ -11675,22 +11675,22 @@
       <c r="X8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z8" s="21">
+      <c r="Z8" s="18">
         <v>1591207</v>
       </c>
-      <c r="AB8" s="21">
+      <c r="AB8" s="18">
         <f t="shared" si="0"/>
         <v>271919</v>
       </c>
-      <c r="AC8" s="21">
+      <c r="AC8" s="18">
         <f t="shared" si="1"/>
         <v>154532</v>
       </c>
-      <c r="AE8" s="23">
+      <c r="AE8" s="20">
         <f t="shared" si="2"/>
         <v>17.08885141907998</v>
       </c>
-      <c r="AF8" s="23">
+      <c r="AF8" s="20">
         <f t="shared" si="3"/>
         <v>9.7116214295185976</v>
       </c>
@@ -11766,22 +11766,22 @@
       <c r="X9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z9" s="21">
+      <c r="Z9" s="18">
         <v>1489246</v>
       </c>
-      <c r="AB9" s="21">
+      <c r="AB9" s="18">
         <f t="shared" si="0"/>
         <v>254359</v>
       </c>
-      <c r="AC9" s="21">
+      <c r="AC9" s="18">
         <f t="shared" si="1"/>
         <v>155840</v>
       </c>
-      <c r="AE9" s="23">
+      <c r="AE9" s="20">
         <f t="shared" si="2"/>
         <v>17.07971685000329</v>
       </c>
-      <c r="AF9" s="23">
+      <c r="AF9" s="20">
         <f t="shared" si="3"/>
         <v>10.464355788096794</v>
       </c>
@@ -11857,22 +11857,22 @@
       <c r="X10" s="9">
         <v>25233</v>
       </c>
-      <c r="Z10" s="21">
+      <c r="Z10" s="18">
         <v>1515691</v>
       </c>
-      <c r="AB10" s="21">
+      <c r="AB10" s="18">
         <f t="shared" si="0"/>
         <v>291442</v>
       </c>
-      <c r="AC10" s="21">
+      <c r="AC10" s="18">
         <f t="shared" si="1"/>
         <v>107920</v>
       </c>
-      <c r="AE10" s="23">
+      <c r="AE10" s="20">
         <f t="shared" si="2"/>
         <v>19.228325562400254</v>
       </c>
-      <c r="AF10" s="23">
+      <c r="AF10" s="20">
         <f t="shared" si="3"/>
         <v>7.1201847870047397</v>
       </c>
@@ -11948,22 +11948,22 @@
       <c r="X11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z11" s="21">
+      <c r="Z11" s="18">
         <v>1341785</v>
       </c>
-      <c r="AB11" s="21">
+      <c r="AB11" s="18">
         <f t="shared" si="0"/>
         <v>60820</v>
       </c>
-      <c r="AC11" s="21">
+      <c r="AC11" s="18">
         <f t="shared" si="1"/>
         <v>27705</v>
       </c>
-      <c r="AE11" s="23">
+      <c r="AE11" s="20">
         <f t="shared" si="2"/>
         <v>4.5327679173638096</v>
       </c>
-      <c r="AF11" s="23">
+      <c r="AF11" s="20">
         <f t="shared" si="3"/>
         <v>2.0647868324657077</v>
       </c>
@@ -12039,22 +12039,22 @@
       <c r="X12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z12" s="21">
+      <c r="Z12" s="18">
         <v>2989482</v>
       </c>
-      <c r="AB12" s="21">
+      <c r="AB12" s="18">
         <f t="shared" si="0"/>
         <v>640567</v>
       </c>
-      <c r="AC12" s="21">
+      <c r="AC12" s="18">
         <f t="shared" si="1"/>
         <v>90468</v>
       </c>
-      <c r="AE12" s="23">
+      <c r="AE12" s="20">
         <f t="shared" si="2"/>
         <v>21.427357649251611</v>
       </c>
-      <c r="AF12" s="23">
+      <c r="AF12" s="20">
         <f t="shared" si="3"/>
         <v>3.0262098918809346</v>
       </c>
@@ -12130,22 +12130,22 @@
       <c r="X13" s="6">
         <v>23443</v>
       </c>
-      <c r="Z13" s="21">
+      <c r="Z13" s="18">
         <v>2531253</v>
       </c>
-      <c r="AB13" s="21">
+      <c r="AB13" s="18">
         <f t="shared" si="0"/>
         <v>1403609</v>
       </c>
-      <c r="AC13" s="21">
+      <c r="AC13" s="18">
         <f t="shared" si="1"/>
         <v>125025</v>
       </c>
-      <c r="AE13" s="23">
+      <c r="AE13" s="20">
         <f t="shared" si="2"/>
         <v>55.451154033200154</v>
       </c>
-      <c r="AF13" s="23">
+      <c r="AF13" s="20">
         <f t="shared" si="3"/>
         <v>4.939253405329298</v>
       </c>
@@ -12221,22 +12221,22 @@
       <c r="X14" s="9">
         <v>62695</v>
       </c>
-      <c r="Z14" s="21">
+      <c r="Z14" s="18">
         <v>3030831</v>
       </c>
-      <c r="AB14" s="21">
+      <c r="AB14" s="18">
         <f t="shared" si="0"/>
         <v>204957</v>
       </c>
-      <c r="AC14" s="21">
+      <c r="AC14" s="18">
         <f t="shared" si="1"/>
         <v>109101</v>
       </c>
-      <c r="AE14" s="23">
+      <c r="AE14" s="20">
         <f t="shared" si="2"/>
         <v>6.7624027865624976</v>
       </c>
-      <c r="AF14" s="23">
+      <c r="AF14" s="20">
         <f t="shared" si="3"/>
         <v>3.5997058232544141</v>
       </c>
@@ -12312,22 +12312,22 @@
       <c r="X15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="18">
         <v>1603409</v>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="18">
         <f t="shared" si="0"/>
         <v>362957</v>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="18">
         <f t="shared" si="1"/>
         <v>159519</v>
       </c>
-      <c r="AE15" s="23">
+      <c r="AE15" s="20">
         <f t="shared" si="2"/>
         <v>22.636582431556764</v>
       </c>
-      <c r="AF15" s="23">
+      <c r="AF15" s="20">
         <f t="shared" si="3"/>
         <v>9.9487404648470843</v>
       </c>
@@ -12403,22 +12403,22 @@
       <c r="X16" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z16" s="21">
+      <c r="Z16" s="18">
         <v>2564238</v>
       </c>
-      <c r="AB16" s="21">
+      <c r="AB16" s="18">
         <f t="shared" si="0"/>
         <v>869026</v>
       </c>
-      <c r="AC16" s="21">
+      <c r="AC16" s="18">
         <f t="shared" si="1"/>
         <v>251303</v>
       </c>
-      <c r="AE16" s="23">
+      <c r="AE16" s="20">
         <f t="shared" si="2"/>
         <v>33.890223918372634</v>
       </c>
-      <c r="AF16" s="23">
+      <c r="AF16" s="20">
         <f t="shared" si="3"/>
         <v>9.80029934818843</v>
       </c>
@@ -12494,22 +12494,22 @@
       <c r="X17" s="6">
         <v>49147</v>
       </c>
-      <c r="Z17" s="21">
+      <c r="Z17" s="18">
         <v>2113674</v>
       </c>
-      <c r="AB17" s="21">
+      <c r="AB17" s="18">
         <f t="shared" si="0"/>
         <v>1224527</v>
       </c>
-      <c r="AC17" s="21">
+      <c r="AC17" s="18">
         <f t="shared" si="1"/>
         <v>213506</v>
       </c>
-      <c r="AE17" s="23">
+      <c r="AE17" s="20">
         <f t="shared" si="2"/>
         <v>57.933579161214077</v>
       </c>
-      <c r="AF17" s="23">
+      <c r="AF17" s="20">
         <f t="shared" si="3"/>
         <v>10.101179273624977</v>
       </c>
@@ -12585,22 +12585,22 @@
       <c r="X18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z18" s="21">
+      <c r="Z18" s="18">
         <v>2170665</v>
       </c>
-      <c r="AB18" s="21">
+      <c r="AB18" s="18">
         <f t="shared" si="0"/>
         <v>348680</v>
       </c>
-      <c r="AC18" s="21">
+      <c r="AC18" s="18">
         <f t="shared" si="1"/>
         <v>150063</v>
       </c>
-      <c r="AE18" s="23">
+      <c r="AE18" s="20">
         <f t="shared" si="2"/>
         <v>16.063280146867434</v>
       </c>
-      <c r="AF18" s="23">
+      <c r="AF18" s="20">
         <f t="shared" si="3"/>
         <v>6.9132270525391988</v>
       </c>
@@ -12676,22 +12676,22 @@
       <c r="X19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z19" s="21">
+      <c r="Z19" s="18">
         <v>1132843</v>
       </c>
-      <c r="AB19" s="21">
+      <c r="AB19" s="18">
         <f t="shared" si="0"/>
         <v>139422</v>
       </c>
-      <c r="AC19" s="21">
+      <c r="AC19" s="18">
         <f t="shared" si="1"/>
         <v>49513</v>
       </c>
-      <c r="AE19" s="23">
+      <c r="AE19" s="20">
         <f t="shared" si="2"/>
         <v>12.307265878855233</v>
       </c>
-      <c r="AF19" s="23">
+      <c r="AF19" s="20">
         <f t="shared" si="3"/>
         <v>4.370685081692697</v>
       </c>
@@ -12767,22 +12767,22 @@
       <c r="X20" s="9">
         <v>35378</v>
       </c>
-      <c r="Z20" s="21">
+      <c r="Z20" s="18">
         <v>3559229</v>
       </c>
-      <c r="AB20" s="21">
+      <c r="AB20" s="18">
         <f t="shared" si="0"/>
         <v>1880777</v>
       </c>
-      <c r="AC20" s="21">
+      <c r="AC20" s="18">
         <f t="shared" si="1"/>
         <v>397068</v>
       </c>
-      <c r="AE20" s="23">
+      <c r="AE20" s="20">
         <f t="shared" si="2"/>
         <v>52.84225881504112</v>
       </c>
-      <c r="AF20" s="23">
+      <c r="AF20" s="20">
         <f t="shared" si="3"/>
         <v>11.156011596893597</v>
       </c>
@@ -12858,22 +12858,22 @@
       <c r="X21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z21" s="21">
+      <c r="Z21" s="18">
         <v>1544564</v>
       </c>
-      <c r="AB21" s="21">
+      <c r="AB21" s="18">
         <f t="shared" si="0"/>
         <v>253930</v>
       </c>
-      <c r="AC21" s="21">
+      <c r="AC21" s="18">
         <f t="shared" si="1"/>
         <v>70920</v>
       </c>
-      <c r="AE21" s="23">
+      <c r="AE21" s="20">
         <f t="shared" si="2"/>
         <v>16.440238151348861</v>
       </c>
-      <c r="AF21" s="23">
+      <c r="AF21" s="20">
         <f t="shared" si="3"/>
         <v>4.5915870109623169</v>
       </c>
@@ -12949,22 +12949,22 @@
       <c r="X22" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z22" s="21">
+      <c r="Z22" s="18">
         <v>1387015</v>
       </c>
-      <c r="AB22" s="21">
+      <c r="AB22" s="18">
         <f t="shared" si="0"/>
         <v>105548</v>
       </c>
-      <c r="AC22" s="21">
+      <c r="AC22" s="18">
         <f t="shared" si="1"/>
         <v>41336</v>
       </c>
-      <c r="AE22" s="23">
+      <c r="AE22" s="20">
         <f t="shared" si="2"/>
         <v>7.6097230383233061</v>
       </c>
-      <c r="AF22" s="23">
+      <c r="AF22" s="20">
         <f t="shared" si="3"/>
         <v>2.9802129032490634</v>
       </c>
@@ -13040,22 +13040,22 @@
       <c r="X23" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z23" s="21">
+      <c r="Z23" s="18">
         <v>674034</v>
       </c>
-      <c r="AB23" s="21">
+      <c r="AB23" s="18">
         <f t="shared" si="0"/>
         <v>168537</v>
       </c>
-      <c r="AC23" s="21">
+      <c r="AC23" s="18">
         <f t="shared" si="1"/>
         <v>99620</v>
       </c>
-      <c r="AE23" s="23">
+      <c r="AE23" s="20">
         <f t="shared" si="2"/>
         <v>25.004228273351199</v>
       </c>
-      <c r="AF23" s="23">
+      <c r="AF23" s="20">
         <f t="shared" si="3"/>
         <v>14.779669868285575</v>
       </c>
@@ -13131,22 +13131,22 @@
       <c r="X24" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z24" s="21">
+      <c r="Z24" s="18">
         <v>2371012</v>
       </c>
-      <c r="AB24" s="21">
+      <c r="AB24" s="18">
         <f t="shared" si="0"/>
         <v>786493</v>
       </c>
-      <c r="AC24" s="21">
+      <c r="AC24" s="18">
         <f t="shared" si="1"/>
         <v>102285</v>
       </c>
-      <c r="AE24" s="23">
+      <c r="AE24" s="20">
         <f t="shared" si="2"/>
         <v>33.171194409813189</v>
       </c>
-      <c r="AF24" s="23">
+      <c r="AF24" s="20">
         <f t="shared" si="3"/>
         <v>4.3139806968501215</v>
       </c>
@@ -13222,22 +13222,22 @@
       <c r="X25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z25" s="21">
+      <c r="Z25" s="18">
         <v>1299365</v>
       </c>
-      <c r="AB25" s="21">
+      <c r="AB25" s="18">
         <f t="shared" si="0"/>
         <v>394859</v>
       </c>
-      <c r="AC25" s="21">
+      <c r="AC25" s="18">
         <f t="shared" si="1"/>
         <v>324538</v>
       </c>
-      <c r="AE25" s="23">
+      <c r="AE25" s="20">
         <f t="shared" si="2"/>
         <v>30.388612899377769</v>
       </c>
-      <c r="AF25" s="23">
+      <c r="AF25" s="20">
         <f t="shared" si="3"/>
         <v>24.976661677049943</v>
       </c>
@@ -13313,22 +13313,22 @@
       <c r="X26" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z26" s="21">
+      <c r="Z26" s="18">
         <v>2147621</v>
       </c>
-      <c r="AB26" s="21">
+      <c r="AB26" s="18">
         <f t="shared" si="0"/>
         <v>378706</v>
       </c>
-      <c r="AC26" s="21">
+      <c r="AC26" s="18">
         <f t="shared" si="1"/>
         <v>153616</v>
       </c>
-      <c r="AE26" s="23">
+      <c r="AE26" s="20">
         <f t="shared" si="2"/>
         <v>17.633744501473956</v>
       </c>
-      <c r="AF26" s="23">
+      <c r="AF26" s="20">
         <f t="shared" si="3"/>
         <v>7.1528449386553765</v>
       </c>
@@ -13404,22 +13404,22 @@
       <c r="X27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z27" s="21">
+      <c r="Z27" s="18">
         <v>1686764</v>
       </c>
-      <c r="AB27" s="21">
+      <c r="AB27" s="18">
         <f t="shared" si="0"/>
         <v>271550</v>
       </c>
-      <c r="AC27" s="21">
+      <c r="AC27" s="18">
         <f t="shared" si="1"/>
         <v>79894</v>
       </c>
-      <c r="AE27" s="23">
+      <c r="AE27" s="20">
         <f t="shared" si="2"/>
         <v>16.09887334564883</v>
       </c>
-      <c r="AF27" s="23">
+      <c r="AF27" s="20">
         <f t="shared" si="3"/>
         <v>4.7365250859041339</v>
       </c>
@@ -13495,22 +13495,22 @@
       <c r="X28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z28" s="21">
+      <c r="Z28" s="18">
         <v>2430581</v>
       </c>
-      <c r="AB28" s="21">
+      <c r="AB28" s="18">
         <f t="shared" si="0"/>
         <v>1250685</v>
       </c>
-      <c r="AC28" s="21">
+      <c r="AC28" s="18">
         <f t="shared" si="1"/>
         <v>1089439</v>
       </c>
-      <c r="AE28" s="23">
+      <c r="AE28" s="20">
         <f t="shared" si="2"/>
         <v>51.456215612645707</v>
       </c>
-      <c r="AF28" s="23">
+      <c r="AF28" s="20">
         <f t="shared" si="3"/>
         <v>44.822163918832572</v>
       </c>
@@ -13586,22 +13586,22 @@
       <c r="X29" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z29" s="21">
+      <c r="Z29" s="18">
         <v>1584774</v>
       </c>
-      <c r="AB29" s="21">
+      <c r="AB29" s="18">
         <f t="shared" si="0"/>
         <v>373629</v>
       </c>
-      <c r="AC29" s="21">
+      <c r="AC29" s="18">
         <f t="shared" si="1"/>
         <v>90053</v>
       </c>
-      <c r="AE29" s="23">
+      <c r="AE29" s="20">
         <f t="shared" si="2"/>
         <v>23.57616922034309</v>
       </c>
-      <c r="AF29" s="23">
+      <c r="AF29" s="20">
         <f t="shared" si="3"/>
         <v>5.6823875202394794</v>
       </c>
@@ -13677,22 +13677,22 @@
       <c r="X30" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z30" s="21">
+      <c r="Z30" s="18">
         <v>1367022</v>
       </c>
-      <c r="AB30" s="21">
+      <c r="AB30" s="18">
         <f t="shared" si="0"/>
         <v>96784</v>
       </c>
-      <c r="AC30" s="21">
+      <c r="AC30" s="18">
         <f t="shared" si="1"/>
         <v>25736</v>
       </c>
-      <c r="AE30" s="23">
+      <c r="AE30" s="20">
         <f t="shared" si="2"/>
         <v>7.0799153195778857</v>
       </c>
-      <c r="AF30" s="23">
+      <c r="AF30" s="20">
         <f t="shared" si="3"/>
         <v>1.8826324667781498</v>
       </c>
@@ -13768,22 +13768,22 @@
       <c r="X31" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z31" s="21">
+      <c r="Z31" s="18">
         <v>364156</v>
       </c>
-      <c r="AB31" s="21">
+      <c r="AB31" s="18">
         <f t="shared" si="0"/>
         <v>20081</v>
       </c>
-      <c r="AC31" s="21">
+      <c r="AC31" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE31" s="23">
+      <c r="AE31" s="20">
         <f t="shared" si="2"/>
         <v>5.5143949296455368</v>
       </c>
-      <c r="AF31" s="23">
+      <c r="AF31" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13859,22 +13859,22 @@
       <c r="X32" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z32" s="21">
+      <c r="Z32" s="18">
         <v>1600145</v>
       </c>
-      <c r="AB32" s="21">
+      <c r="AB32" s="18">
         <f t="shared" si="0"/>
         <v>505763</v>
       </c>
-      <c r="AC32" s="21">
+      <c r="AC32" s="18">
         <f t="shared" si="1"/>
         <v>95724</v>
       </c>
-      <c r="AE32" s="23">
+      <c r="AE32" s="20">
         <f t="shared" si="2"/>
         <v>31.6073230863453</v>
       </c>
-      <c r="AF32" s="23">
+      <c r="AF32" s="20">
         <f t="shared" si="3"/>
         <v>5.9822078624124693</v>
       </c>
@@ -13950,22 +13950,22 @@
       <c r="X33" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z33" s="21">
+      <c r="Z33" s="18">
         <v>2033798</v>
       </c>
-      <c r="AB33" s="21">
+      <c r="AB33" s="18">
         <f t="shared" si="0"/>
         <v>409024</v>
       </c>
-      <c r="AC33" s="21">
+      <c r="AC33" s="18">
         <f t="shared" si="1"/>
         <v>183366</v>
       </c>
-      <c r="AE33" s="23">
+      <c r="AE33" s="20">
         <f t="shared" si="2"/>
         <v>20.111338490843238</v>
       </c>
-      <c r="AF33" s="23">
+      <c r="AF33" s="20">
         <f t="shared" si="3"/>
         <v>9.0159396360897208</v>
       </c>
@@ -14041,22 +14041,22 @@
       <c r="X34" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z34" s="21">
+      <c r="Z34" s="18">
         <v>1470474</v>
       </c>
-      <c r="AB34" s="21">
+      <c r="AB34" s="18">
         <f t="shared" si="0"/>
         <v>424107</v>
       </c>
-      <c r="AC34" s="21">
+      <c r="AC34" s="18">
         <f t="shared" si="1"/>
         <v>59981</v>
       </c>
-      <c r="AE34" s="23">
+      <c r="AE34" s="20">
         <f t="shared" si="2"/>
         <v>28.84151640899465</v>
       </c>
-      <c r="AF34" s="23">
+      <c r="AF34" s="20">
         <f t="shared" si="3"/>
         <v>4.07902485865102</v>
       </c>
@@ -14132,22 +14132,22 @@
       <c r="X35" s="6">
         <v>31449</v>
       </c>
-      <c r="Z35" s="21">
+      <c r="Z35" s="18">
         <v>2994302</v>
       </c>
-      <c r="AB35" s="21">
+      <c r="AB35" s="18">
         <f t="shared" si="0"/>
         <v>805487</v>
       </c>
-      <c r="AC35" s="21">
+      <c r="AC35" s="18">
         <f t="shared" si="1"/>
         <v>139955</v>
       </c>
-      <c r="AE35" s="23">
+      <c r="AE35" s="20">
         <f t="shared" si="2"/>
         <v>26.900659986868391</v>
       </c>
-      <c r="AF35" s="23">
+      <c r="AF35" s="20">
         <f t="shared" si="3"/>
         <v>4.6740442346830742</v>
       </c>
@@ -14223,22 +14223,22 @@
       <c r="X36" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z36" s="21">
+      <c r="Z36" s="18">
         <v>3018299</v>
       </c>
-      <c r="AB36" s="21">
+      <c r="AB36" s="18">
         <f t="shared" si="0"/>
         <v>1242617</v>
       </c>
-      <c r="AC36" s="21">
+      <c r="AC36" s="18">
         <f t="shared" si="1"/>
         <v>135030</v>
       </c>
-      <c r="AE36" s="23">
+      <c r="AE36" s="20">
         <f t="shared" si="2"/>
         <v>41.169446764551822</v>
       </c>
-      <c r="AF36" s="23">
+      <c r="AF36" s="20">
         <f t="shared" si="3"/>
         <v>4.4737118489586347</v>
       </c>
@@ -14314,22 +14314,22 @@
       <c r="X37" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z37" s="21">
+      <c r="Z37" s="18">
         <v>2778151</v>
       </c>
-      <c r="AB37" s="21">
+      <c r="AB37" s="18">
         <f t="shared" si="0"/>
         <v>1141008</v>
       </c>
-      <c r="AC37" s="21">
+      <c r="AC37" s="18">
         <f t="shared" si="1"/>
         <v>139220</v>
       </c>
-      <c r="AE37" s="23">
+      <c r="AE37" s="20">
         <f t="shared" si="2"/>
         <v>41.070769731378896</v>
       </c>
-      <c r="AF37" s="23">
+      <c r="AF37" s="20">
         <f t="shared" si="3"/>
         <v>5.0112466888948797</v>
       </c>
@@ -14405,22 +14405,22 @@
       <c r="X38" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z38" s="21">
+      <c r="Z38" s="18">
         <v>1122317</v>
       </c>
-      <c r="AB38" s="21">
+      <c r="AB38" s="18">
         <f t="shared" si="0"/>
         <v>79661</v>
       </c>
-      <c r="AC38" s="21">
+      <c r="AC38" s="18">
         <f t="shared" si="1"/>
         <v>30478</v>
       </c>
-      <c r="AE38" s="23">
+      <c r="AE38" s="20">
         <f t="shared" si="2"/>
         <v>7.0979054937241433</v>
       </c>
-      <c r="AF38" s="23">
+      <c r="AF38" s="20">
         <f t="shared" si="3"/>
         <v>2.7156320362250597</v>
       </c>
@@ -14496,22 +14496,22 @@
       <c r="X39" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z39" s="21">
+      <c r="Z39" s="18">
         <v>1802196</v>
       </c>
-      <c r="AB39" s="21">
+      <c r="AB39" s="18">
         <f t="shared" si="0"/>
         <v>524434</v>
       </c>
-      <c r="AC39" s="21">
+      <c r="AC39" s="18">
         <f t="shared" si="1"/>
         <v>46122</v>
       </c>
-      <c r="AE39" s="23">
+      <c r="AE39" s="20">
         <f t="shared" si="2"/>
         <v>29.099720563135197</v>
       </c>
-      <c r="AF39" s="23">
+      <c r="AF39" s="20">
         <f t="shared" si="3"/>
         <v>2.5592110957964613</v>
       </c>
@@ -14587,22 +14587,22 @@
       <c r="X40" s="9">
         <v>21599</v>
       </c>
-      <c r="Z40" s="21">
+      <c r="Z40" s="18">
         <v>2751336</v>
       </c>
-      <c r="AB40" s="21">
+      <c r="AB40" s="18">
         <f t="shared" si="0"/>
         <v>1301224</v>
       </c>
-      <c r="AC40" s="21">
+      <c r="AC40" s="18">
         <f t="shared" si="1"/>
         <v>111598</v>
       </c>
-      <c r="AE40" s="23">
+      <c r="AE40" s="20">
         <f t="shared" si="2"/>
         <v>47.294259952255921</v>
       </c>
-      <c r="AF40" s="23">
+      <c r="AF40" s="20">
         <f t="shared" si="3"/>
         <v>4.0561385450559291</v>
       </c>
@@ -14678,22 +14678,22 @@
       <c r="X41" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z41" s="21">
+      <c r="Z41" s="18">
         <v>2112033</v>
       </c>
-      <c r="AB41" s="21">
+      <c r="AB41" s="18">
         <f t="shared" si="0"/>
         <v>1459959</v>
       </c>
-      <c r="AC41" s="21">
+      <c r="AC41" s="18">
         <f t="shared" si="1"/>
         <v>1346925</v>
       </c>
-      <c r="AE41" s="23">
+      <c r="AE41" s="20">
         <f t="shared" si="2"/>
         <v>69.125766500807515</v>
       </c>
-      <c r="AF41" s="23">
+      <c r="AF41" s="20">
         <f t="shared" si="3"/>
         <v>63.773861487959707</v>
       </c>
@@ -14769,22 +14769,22 @@
       <c r="X42" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z42" s="21">
+      <c r="Z42" s="18">
         <v>2405829</v>
       </c>
-      <c r="AB42" s="21">
+      <c r="AB42" s="18">
         <f t="shared" si="0"/>
         <v>1173209</v>
       </c>
-      <c r="AC42" s="21">
+      <c r="AC42" s="18">
         <f t="shared" si="1"/>
         <v>239864</v>
       </c>
-      <c r="AE42" s="23">
+      <c r="AE42" s="20">
         <f t="shared" si="2"/>
         <v>48.76526968458689</v>
       </c>
-      <c r="AF42" s="23">
+      <c r="AF42" s="20">
         <f t="shared" si="3"/>
         <v>9.9701184082492986</v>
       </c>
@@ -14860,22 +14860,22 @@
       <c r="X43" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z43" s="21">
+      <c r="Z43" s="18">
         <v>1527848</v>
       </c>
-      <c r="AB43" s="21">
+      <c r="AB43" s="18">
         <f t="shared" si="0"/>
         <v>490204</v>
       </c>
-      <c r="AC43" s="21">
+      <c r="AC43" s="18">
         <f t="shared" si="1"/>
         <v>74067</v>
       </c>
-      <c r="AE43" s="23">
+      <c r="AE43" s="20">
         <f t="shared" si="2"/>
         <v>32.084605274870277</v>
       </c>
-      <c r="AF43" s="23">
+      <c r="AF43" s="20">
         <f t="shared" si="3"/>
         <v>4.8477989957116154</v>
       </c>
@@ -14951,22 +14951,22 @@
       <c r="X44" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z44" s="21">
+      <c r="Z44" s="18">
         <v>1525279</v>
       </c>
-      <c r="AB44" s="21">
+      <c r="AB44" s="18">
         <f t="shared" si="0"/>
         <v>126656</v>
       </c>
-      <c r="AC44" s="21">
+      <c r="AC44" s="18">
         <f t="shared" si="1"/>
         <v>46699</v>
       </c>
-      <c r="AE44" s="23">
+      <c r="AE44" s="20">
         <f t="shared" si="2"/>
         <v>8.3037922898040293</v>
       </c>
-      <c r="AF44" s="23">
+      <c r="AF44" s="20">
         <f t="shared" si="3"/>
         <v>3.0616693732753153</v>
       </c>
@@ -15042,22 +15042,22 @@
       <c r="X45" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z45" s="21">
+      <c r="Z45" s="18">
         <v>1447790</v>
       </c>
-      <c r="AB45" s="21">
+      <c r="AB45" s="18">
         <f t="shared" si="0"/>
         <v>833276</v>
       </c>
-      <c r="AC45" s="21">
+      <c r="AC45" s="18">
         <f t="shared" si="1"/>
         <v>186612</v>
       </c>
-      <c r="AE45" s="23">
+      <c r="AE45" s="20">
         <f t="shared" si="2"/>
         <v>57.555032152453045</v>
       </c>
-      <c r="AF45" s="23">
+      <c r="AF45" s="20">
         <f t="shared" si="3"/>
         <v>12.889438385401197</v>
       </c>
@@ -15133,22 +15133,22 @@
       <c r="X46" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z46" s="21">
+      <c r="Z46" s="18">
         <v>2684030</v>
       </c>
-      <c r="AB46" s="21">
+      <c r="AB46" s="18">
         <f t="shared" si="0"/>
         <v>1162054</v>
       </c>
-      <c r="AC46" s="21">
+      <c r="AC46" s="18">
         <f t="shared" si="1"/>
         <v>157603</v>
       </c>
-      <c r="AE46" s="23">
+      <c r="AE46" s="20">
         <f t="shared" si="2"/>
         <v>43.295119652164843</v>
       </c>
-      <c r="AF46" s="23">
+      <c r="AF46" s="20">
         <f t="shared" si="3"/>
         <v>5.8718792263871871</v>
       </c>
@@ -15224,22 +15224,22 @@
       <c r="X47" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z47" s="21">
+      <c r="Z47" s="18">
         <v>1769135</v>
       </c>
-      <c r="AB47" s="21">
+      <c r="AB47" s="18">
         <f t="shared" si="0"/>
         <v>164289</v>
       </c>
-      <c r="AC47" s="21">
+      <c r="AC47" s="18">
         <f t="shared" si="1"/>
         <v>74809</v>
       </c>
-      <c r="AE47" s="23">
+      <c r="AE47" s="20">
         <f t="shared" si="2"/>
         <v>9.2864026770144736</v>
       </c>
-      <c r="AF47" s="23">
+      <c r="AF47" s="20">
         <f t="shared" si="3"/>
         <v>4.2285636765990162</v>
       </c>
@@ -15315,22 +15315,22 @@
       <c r="X48" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z48" s="21">
+      <c r="Z48" s="18">
         <v>1419456</v>
       </c>
-      <c r="AB48" s="21">
+      <c r="AB48" s="18">
         <f t="shared" si="0"/>
         <v>262198</v>
       </c>
-      <c r="AC48" s="21">
+      <c r="AC48" s="18">
         <f t="shared" si="1"/>
         <v>114733</v>
       </c>
-      <c r="AE48" s="23">
+      <c r="AE48" s="20">
         <f t="shared" si="2"/>
         <v>18.471724378916992</v>
       </c>
-      <c r="AF48" s="23">
+      <c r="AF48" s="20">
         <f t="shared" si="3"/>
         <v>8.0828852743586275</v>
       </c>
@@ -15406,22 +15406,22 @@
       <c r="X49" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z49" s="21">
+      <c r="Z49" s="18">
         <v>2196642</v>
       </c>
-      <c r="AB49" s="21">
+      <c r="AB49" s="18">
         <f t="shared" si="0"/>
         <v>350444</v>
       </c>
-      <c r="AC49" s="21">
+      <c r="AC49" s="18">
         <f t="shared" si="1"/>
         <v>69777</v>
       </c>
-      <c r="AE49" s="23">
+      <c r="AE49" s="20">
         <f t="shared" si="2"/>
         <v>15.953623758445845</v>
       </c>
-      <c r="AF49" s="23">
+      <c r="AF49" s="20">
         <f t="shared" si="3"/>
         <v>3.1765303586110072</v>
       </c>
@@ -15497,22 +15497,22 @@
       <c r="X50" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z50" s="21">
+      <c r="Z50" s="18">
         <v>2492316</v>
       </c>
-      <c r="AB50" s="21">
+      <c r="AB50" s="18">
         <f t="shared" si="0"/>
         <v>1333959</v>
       </c>
-      <c r="AC50" s="21">
+      <c r="AC50" s="18">
         <f t="shared" si="1"/>
         <v>224952</v>
       </c>
-      <c r="AE50" s="23">
+      <c r="AE50" s="20">
         <f t="shared" si="2"/>
         <v>53.52286788673667</v>
       </c>
-      <c r="AF50" s="23">
+      <c r="AF50" s="20">
         <f t="shared" si="3"/>
         <v>9.0258217657792983</v>
       </c>
@@ -15588,22 +15588,22 @@
       <c r="X51" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z51" s="21">
+      <c r="Z51" s="18">
         <v>2733612</v>
       </c>
-      <c r="AB51" s="21">
+      <c r="AB51" s="18">
         <f t="shared" si="0"/>
         <v>1705612</v>
       </c>
-      <c r="AC51" s="21">
+      <c r="AC51" s="18">
         <f t="shared" si="1"/>
         <v>648007</v>
       </c>
-      <c r="AE51" s="23">
+      <c r="AE51" s="20">
         <f t="shared" si="2"/>
         <v>62.394077872060848</v>
       </c>
-      <c r="AF51" s="23">
+      <c r="AF51" s="20">
         <f t="shared" si="3"/>
         <v>23.705156401127887</v>
       </c>
@@ -15679,22 +15679,22 @@
       <c r="X52" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z52" s="21">
+      <c r="Z52" s="18">
         <v>2297854</v>
       </c>
-      <c r="AB52" s="21">
+      <c r="AB52" s="18">
         <f t="shared" si="0"/>
         <v>1065498</v>
       </c>
-      <c r="AC52" s="21">
+      <c r="AC52" s="18">
         <f t="shared" si="1"/>
         <v>59829</v>
       </c>
-      <c r="AE52" s="23">
+      <c r="AE52" s="20">
         <f t="shared" si="2"/>
         <v>46.369264539870677</v>
       </c>
-      <c r="AF52" s="23">
+      <c r="AF52" s="20">
         <f t="shared" si="3"/>
         <v>2.6036902257497649</v>
       </c>
@@ -15770,22 +15770,22 @@
       <c r="X53" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z53" s="21">
+      <c r="Z53" s="18">
         <v>412716</v>
       </c>
-      <c r="AB53" s="21">
+      <c r="AB53" s="18">
         <f t="shared" si="0"/>
         <v>91645</v>
       </c>
-      <c r="AC53" s="21">
+      <c r="AC53" s="18">
         <f t="shared" si="1"/>
         <v>64572</v>
       </c>
-      <c r="AE53" s="23">
+      <c r="AE53" s="20">
         <f t="shared" si="2"/>
         <v>22.205342172341272</v>
       </c>
-      <c r="AF53" s="23">
+      <c r="AF53" s="20">
         <f t="shared" si="3"/>
         <v>15.645625563341378</v>
       </c>
@@ -15861,22 +15861,22 @@
       <c r="X54" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z54" s="21">
+      <c r="Z54" s="18">
         <v>1071355</v>
       </c>
-      <c r="AB54" s="21">
+      <c r="AB54" s="18">
         <f t="shared" si="0"/>
         <v>159952</v>
       </c>
-      <c r="AC54" s="21">
+      <c r="AC54" s="18">
         <f t="shared" si="1"/>
         <v>96906</v>
       </c>
-      <c r="AE54" s="23">
+      <c r="AE54" s="20">
         <f t="shared" si="2"/>
         <v>14.929878518324923</v>
       </c>
-      <c r="AF54" s="23">
+      <c r="AF54" s="20">
         <f t="shared" si="3"/>
         <v>9.0451811024357003</v>
       </c>
@@ -15906,10 +15906,10 @@
       <c r="V55" s="10"/>
       <c r="W55" s="10"/>
       <c r="X55" s="10"/>
-      <c r="AB55" s="21"/>
-      <c r="AC55" s="21"/>
-      <c r="AE55" s="23"/>
-      <c r="AF55" s="23"/>
+      <c r="AB55" s="18"/>
+      <c r="AC55" s="18"/>
+      <c r="AE55" s="20"/>
+      <c r="AF55" s="20"/>
     </row>
     <row r="56" spans="1:32">
       <c r="A56" s="5" t="s">
@@ -15982,22 +15982,22 @@
       <c r="X56" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z56" s="21">
+      <c r="Z56" s="18">
         <v>826716</v>
       </c>
-      <c r="AB56" s="21">
+      <c r="AB56" s="18">
         <f t="shared" ref="AB56:AB85" si="4">N(C56)+N(E56)+N(G56)+N(I56)+N(K56)+N(N56)+N(P56)+N(R56)+N(T56)+N(V56)+N(X56)</f>
         <v>230688</v>
       </c>
-      <c r="AC56" s="21">
+      <c r="AC56" s="18">
         <f t="shared" ref="AC56:AC85" si="5">N(I56)+N(K56)+N(X56)</f>
         <v>131911</v>
       </c>
-      <c r="AE56" s="23">
+      <c r="AE56" s="20">
         <f t="shared" ref="AE56:AE85" si="6">AB56/Z56*100</f>
         <v>27.904141204476506</v>
       </c>
-      <c r="AF56" s="23">
+      <c r="AF56" s="20">
         <f t="shared" ref="AF56:AF85" si="7">AC56/Z56*100</f>
         <v>15.95602359214047</v>
       </c>
@@ -16073,22 +16073,22 @@
       <c r="X57" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z57" s="21">
+      <c r="Z57" s="18">
         <v>571154</v>
       </c>
-      <c r="AB57" s="21">
+      <c r="AB57" s="18">
         <f t="shared" si="4"/>
         <v>113197</v>
       </c>
-      <c r="AC57" s="21">
+      <c r="AC57" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE57" s="23">
+      <c r="AE57" s="20">
         <f t="shared" si="6"/>
         <v>19.81899802855272</v>
       </c>
-      <c r="AF57" s="23">
+      <c r="AF57" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -16164,22 +16164,22 @@
       <c r="X58" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z58" s="21">
+      <c r="Z58" s="18">
         <v>878415</v>
       </c>
-      <c r="AB58" s="21">
+      <c r="AB58" s="18">
         <f t="shared" si="4"/>
         <v>168284</v>
       </c>
-      <c r="AC58" s="21">
+      <c r="AC58" s="18">
         <f t="shared" si="5"/>
         <v>84240</v>
       </c>
-      <c r="AE58" s="23">
+      <c r="AE58" s="20">
         <f t="shared" si="6"/>
         <v>19.157687425647328</v>
       </c>
-      <c r="AF58" s="23">
+      <c r="AF58" s="20">
         <f t="shared" si="7"/>
         <v>9.5900001707621119</v>
       </c>
@@ -16255,22 +16255,22 @@
       <c r="X59" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z59" s="21">
+      <c r="Z59" s="18">
         <v>1918881</v>
       </c>
-      <c r="AB59" s="21">
+      <c r="AB59" s="18">
         <f t="shared" si="4"/>
         <v>1444278</v>
       </c>
-      <c r="AC59" s="21">
+      <c r="AC59" s="18">
         <f t="shared" si="5"/>
         <v>135347</v>
       </c>
-      <c r="AE59" s="23">
+      <c r="AE59" s="20">
         <f t="shared" si="6"/>
         <v>75.266678861273846</v>
       </c>
-      <c r="AF59" s="23">
+      <c r="AF59" s="20">
         <f t="shared" si="7"/>
         <v>7.0534337460217698</v>
       </c>
@@ -16346,22 +16346,22 @@
       <c r="X60" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z60" s="21">
+      <c r="Z60" s="18">
         <v>1058241</v>
       </c>
-      <c r="AB60" s="21">
+      <c r="AB60" s="18">
         <f t="shared" si="4"/>
         <v>229420</v>
       </c>
-      <c r="AC60" s="21">
+      <c r="AC60" s="18">
         <f t="shared" si="5"/>
         <v>60984</v>
       </c>
-      <c r="AE60" s="23">
+      <c r="AE60" s="20">
         <f t="shared" si="6"/>
         <v>21.679371712114726</v>
       </c>
-      <c r="AF60" s="23">
+      <c r="AF60" s="20">
         <f t="shared" si="7"/>
         <v>5.7627704842280725</v>
       </c>
@@ -16437,22 +16437,22 @@
       <c r="X61" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z61" s="21">
+      <c r="Z61" s="18">
         <v>873301</v>
       </c>
-      <c r="AB61" s="21">
+      <c r="AB61" s="18">
         <f t="shared" si="4"/>
         <v>749856</v>
       </c>
-      <c r="AC61" s="21">
+      <c r="AC61" s="18">
         <f t="shared" si="5"/>
         <v>41590</v>
       </c>
-      <c r="AE61" s="23">
+      <c r="AE61" s="20">
         <f t="shared" si="6"/>
         <v>85.864553000626358</v>
       </c>
-      <c r="AF61" s="23">
+      <c r="AF61" s="20">
         <f t="shared" si="7"/>
         <v>4.7623900579525271</v>
       </c>
@@ -16528,22 +16528,22 @@
       <c r="X62" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z62" s="21">
+      <c r="Z62" s="18">
         <v>933936</v>
       </c>
-      <c r="AB62" s="21">
+      <c r="AB62" s="18">
         <f t="shared" si="4"/>
         <v>485817</v>
       </c>
-      <c r="AC62" s="21">
+      <c r="AC62" s="18">
         <f t="shared" si="5"/>
         <v>43740</v>
       </c>
-      <c r="AE62" s="23">
+      <c r="AE62" s="20">
         <f t="shared" si="6"/>
         <v>52.018232512720353</v>
       </c>
-      <c r="AF62" s="23">
+      <c r="AF62" s="20">
         <f t="shared" si="7"/>
         <v>4.6834044302821605</v>
       </c>
@@ -16619,22 +16619,22 @@
       <c r="X63" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z63" s="21">
+      <c r="Z63" s="18">
         <v>1051032</v>
       </c>
-      <c r="AB63" s="21">
+      <c r="AB63" s="18">
         <f t="shared" si="4"/>
         <v>391657</v>
       </c>
-      <c r="AC63" s="21">
+      <c r="AC63" s="18">
         <f t="shared" si="5"/>
         <v>159590</v>
       </c>
-      <c r="AE63" s="23">
+      <c r="AE63" s="20">
         <f t="shared" si="6"/>
         <v>37.26404143736822</v>
       </c>
-      <c r="AF63" s="23">
+      <c r="AF63" s="20">
         <f t="shared" si="7"/>
         <v>15.18412379451815</v>
       </c>
@@ -16710,22 +16710,22 @@
       <c r="X64" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z64" s="21">
+      <c r="Z64" s="18">
         <v>57478</v>
       </c>
-      <c r="AB64" s="21">
+      <c r="AB64" s="18">
         <f t="shared" si="4"/>
         <v>21742</v>
       </c>
-      <c r="AC64" s="21">
+      <c r="AC64" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE64" s="23">
+      <c r="AE64" s="20">
         <f t="shared" si="6"/>
         <v>37.82664671700477</v>
       </c>
-      <c r="AF64" s="23">
+      <c r="AF64" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -16801,22 +16801,22 @@
       <c r="X65" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z65" s="21">
+      <c r="Z65" s="18">
         <v>829556</v>
       </c>
-      <c r="AB65" s="21">
+      <c r="AB65" s="18">
         <f t="shared" si="4"/>
         <v>180992</v>
       </c>
-      <c r="AC65" s="21">
+      <c r="AC65" s="18">
         <f t="shared" si="5"/>
         <v>59622</v>
       </c>
-      <c r="AE65" s="23">
+      <c r="AE65" s="20">
         <f t="shared" si="6"/>
         <v>21.817936341850338</v>
       </c>
-      <c r="AF65" s="23">
+      <c r="AF65" s="20">
         <f t="shared" si="7"/>
         <v>7.1872182227601282</v>
       </c>
@@ -16846,10 +16846,10 @@
       <c r="V66" s="7"/>
       <c r="W66" s="7"/>
       <c r="X66" s="7"/>
-      <c r="AB66" s="21"/>
-      <c r="AC66" s="21"/>
-      <c r="AE66" s="23"/>
-      <c r="AF66" s="23"/>
+      <c r="AB66" s="18"/>
+      <c r="AC66" s="18"/>
+      <c r="AE66" s="20"/>
+      <c r="AF66" s="20"/>
     </row>
     <row r="67" spans="1:32">
       <c r="A67" s="5" t="s">
@@ -16922,22 +16922,22 @@
       <c r="X67" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z67" s="21">
+      <c r="Z67" s="18">
         <v>120306</v>
       </c>
-      <c r="AB67" s="21">
+      <c r="AB67" s="18">
         <f t="shared" si="4"/>
         <v>35871</v>
       </c>
-      <c r="AC67" s="21">
+      <c r="AC67" s="18">
         <f t="shared" si="5"/>
         <v>32834</v>
       </c>
-      <c r="AE67" s="23">
+      <c r="AE67" s="20">
         <f t="shared" si="6"/>
         <v>29.816468006583214</v>
       </c>
-      <c r="AF67" s="23">
+      <c r="AF67" s="20">
         <f t="shared" si="7"/>
         <v>27.292071883364088</v>
       </c>
@@ -17013,22 +17013,22 @@
       <c r="X68" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z68" s="21">
+      <c r="Z68" s="18">
         <v>570161</v>
       </c>
-      <c r="AB68" s="21">
+      <c r="AB68" s="18">
         <f t="shared" si="4"/>
         <v>78535</v>
       </c>
-      <c r="AC68" s="21">
+      <c r="AC68" s="18">
         <f t="shared" si="5"/>
         <v>26699</v>
       </c>
-      <c r="AE68" s="23">
+      <c r="AE68" s="20">
         <f t="shared" si="6"/>
         <v>13.774179573839671</v>
       </c>
-      <c r="AF68" s="23">
+      <c r="AF68" s="20">
         <f t="shared" si="7"/>
         <v>4.6827124268408395</v>
       </c>
@@ -17104,22 +17104,22 @@
       <c r="X69" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z69" s="21">
+      <c r="Z69" s="18">
         <v>672037</v>
       </c>
-      <c r="AB69" s="21">
+      <c r="AB69" s="18">
         <f t="shared" si="4"/>
         <v>80764</v>
       </c>
-      <c r="AC69" s="21">
+      <c r="AC69" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE69" s="23">
+      <c r="AE69" s="20">
         <f t="shared" si="6"/>
         <v>12.017790687119906</v>
       </c>
-      <c r="AF69" s="23">
+      <c r="AF69" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -17195,22 +17195,22 @@
       <c r="X70" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z70" s="21">
+      <c r="Z70" s="18">
         <v>514267</v>
       </c>
-      <c r="AB70" s="21">
+      <c r="AB70" s="18">
         <f t="shared" si="4"/>
         <v>107104</v>
       </c>
-      <c r="AC70" s="21">
+      <c r="AC70" s="18">
         <f t="shared" si="5"/>
         <v>51473</v>
       </c>
-      <c r="AE70" s="23">
+      <c r="AE70" s="20">
         <f t="shared" si="6"/>
         <v>20.826535632268843</v>
       </c>
-      <c r="AF70" s="23">
+      <c r="AF70" s="20">
         <f t="shared" si="7"/>
         <v>10.009003105390779</v>
       </c>
@@ -17286,22 +17286,22 @@
       <c r="X71" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z71" s="21">
+      <c r="Z71" s="18">
         <v>223336</v>
       </c>
-      <c r="AB71" s="21">
+      <c r="AB71" s="18">
         <f t="shared" si="4"/>
         <v>67647</v>
       </c>
-      <c r="AC71" s="21">
+      <c r="AC71" s="18">
         <f t="shared" si="5"/>
         <v>28933</v>
       </c>
-      <c r="AE71" s="23">
+      <c r="AE71" s="20">
         <f t="shared" si="6"/>
         <v>30.289339828778161</v>
       </c>
-      <c r="AF71" s="23">
+      <c r="AF71" s="20">
         <f t="shared" si="7"/>
         <v>12.954919941254433</v>
       </c>
@@ -17377,22 +17377,22 @@
       <c r="X72" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z72" s="21">
+      <c r="Z72" s="18">
         <v>28113</v>
       </c>
-      <c r="AB72" s="21">
+      <c r="AB72" s="18">
         <f t="shared" si="4"/>
         <v>6893</v>
       </c>
-      <c r="AC72" s="21">
+      <c r="AC72" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE72" s="23">
+      <c r="AE72" s="20">
         <f t="shared" si="6"/>
         <v>24.518905844271334</v>
       </c>
-      <c r="AF72" s="23">
+      <c r="AF72" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -17468,22 +17468,22 @@
       <c r="X73" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z73" s="21">
+      <c r="Z73" s="18">
         <v>1433043</v>
       </c>
-      <c r="AB73" s="21">
+      <c r="AB73" s="18">
         <f t="shared" si="4"/>
         <v>105371</v>
       </c>
-      <c r="AC73" s="21">
+      <c r="AC73" s="18">
         <f t="shared" si="5"/>
         <v>49969</v>
       </c>
-      <c r="AE73" s="23">
+      <c r="AE73" s="20">
         <f t="shared" si="6"/>
         <v>7.3529545170661308</v>
       </c>
-      <c r="AF73" s="23">
+      <c r="AF73" s="20">
         <f t="shared" si="7"/>
         <v>3.4869156054633392</v>
       </c>
@@ -17559,22 +17559,22 @@
       <c r="X74" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z74" s="21">
+      <c r="Z74" s="18">
         <v>1927679</v>
       </c>
-      <c r="AB74" s="21">
+      <c r="AB74" s="18">
         <f t="shared" si="4"/>
         <v>455183</v>
       </c>
-      <c r="AC74" s="21">
+      <c r="AC74" s="18">
         <f t="shared" si="5"/>
         <v>73283</v>
       </c>
-      <c r="AE74" s="23">
+      <c r="AE74" s="20">
         <f t="shared" si="6"/>
         <v>23.613008182378913</v>
       </c>
-      <c r="AF74" s="23">
+      <c r="AF74" s="20">
         <f t="shared" si="7"/>
         <v>3.8016184229843248</v>
       </c>
@@ -17650,22 +17650,22 @@
       <c r="X75" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z75" s="21">
+      <c r="Z75" s="18">
         <v>269880</v>
       </c>
-      <c r="AB75" s="21">
+      <c r="AB75" s="18">
         <f t="shared" si="4"/>
         <v>6535</v>
       </c>
-      <c r="AC75" s="21">
+      <c r="AC75" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE75" s="23">
+      <c r="AE75" s="20">
         <f t="shared" si="6"/>
         <v>2.421446568845413</v>
       </c>
-      <c r="AF75" s="23">
+      <c r="AF75" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -17695,11 +17695,11 @@
       <c r="V76" s="7"/>
       <c r="W76" s="7"/>
       <c r="X76" s="7"/>
-      <c r="Z76" s="21"/>
-      <c r="AB76" s="21"/>
-      <c r="AC76" s="21"/>
-      <c r="AE76" s="23"/>
-      <c r="AF76" s="23"/>
+      <c r="Z76" s="18"/>
+      <c r="AB76" s="18"/>
+      <c r="AC76" s="18"/>
+      <c r="AE76" s="20"/>
+      <c r="AF76" s="20"/>
     </row>
     <row r="77" spans="1:32">
       <c r="A77" s="5" t="s">
@@ -17772,22 +17772,22 @@
       <c r="X77" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z77" s="21">
+      <c r="Z77" s="18">
         <v>682608</v>
       </c>
-      <c r="AB77" s="21">
+      <c r="AB77" s="18">
         <f t="shared" si="4"/>
         <v>129912</v>
       </c>
-      <c r="AC77" s="21">
+      <c r="AC77" s="18">
         <f t="shared" si="5"/>
         <v>37376</v>
       </c>
-      <c r="AE77" s="23">
+      <c r="AE77" s="20">
         <f t="shared" si="6"/>
         <v>19.031713662892905</v>
       </c>
-      <c r="AF77" s="23">
+      <c r="AF77" s="20">
         <f t="shared" si="7"/>
         <v>5.4754705482502404</v>
       </c>
@@ -17863,22 +17863,22 @@
       <c r="X78" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z78" s="21">
+      <c r="Z78" s="18">
         <v>382487</v>
       </c>
-      <c r="AB78" s="21">
+      <c r="AB78" s="18">
         <f t="shared" si="4"/>
         <v>45329</v>
       </c>
-      <c r="AC78" s="21">
+      <c r="AC78" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE78" s="23">
+      <c r="AE78" s="20">
         <f t="shared" si="6"/>
         <v>11.851121737470816</v>
       </c>
-      <c r="AF78" s="23">
+      <c r="AF78" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -17954,22 +17954,22 @@
       <c r="X79" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z79" s="21">
+      <c r="Z79" s="18">
         <v>860021</v>
       </c>
-      <c r="AB79" s="21">
+      <c r="AB79" s="18">
         <f t="shared" si="4"/>
         <v>161845</v>
       </c>
-      <c r="AC79" s="21">
+      <c r="AC79" s="18">
         <f t="shared" si="5"/>
         <v>105858</v>
       </c>
-      <c r="AE79" s="23">
+      <c r="AE79" s="20">
         <f t="shared" si="6"/>
         <v>18.818726519468711</v>
       </c>
-      <c r="AF79" s="23">
+      <c r="AF79" s="20">
         <f t="shared" si="7"/>
         <v>12.308769204472913</v>
       </c>
@@ -18045,22 +18045,22 @@
       <c r="X80" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z80" s="21">
+      <c r="Z80" s="18">
         <v>684590</v>
       </c>
-      <c r="AB80" s="21">
+      <c r="AB80" s="18">
         <f t="shared" si="4"/>
         <v>92401</v>
       </c>
-      <c r="AC80" s="21">
+      <c r="AC80" s="18">
         <f t="shared" si="5"/>
         <v>26246</v>
       </c>
-      <c r="AE80" s="23">
+      <c r="AE80" s="20">
         <f t="shared" si="6"/>
         <v>13.497275741684803</v>
       </c>
-      <c r="AF80" s="23">
+      <c r="AF80" s="20">
         <f t="shared" si="7"/>
         <v>3.8338275464146419</v>
       </c>
@@ -18136,22 +18136,22 @@
       <c r="X81" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z81" s="21">
+      <c r="Z81" s="18">
         <v>987863</v>
       </c>
-      <c r="AB81" s="21">
+      <c r="AB81" s="18">
         <f t="shared" si="4"/>
         <v>142095</v>
       </c>
-      <c r="AC81" s="21">
+      <c r="AC81" s="18">
         <f t="shared" si="5"/>
         <v>22744</v>
       </c>
-      <c r="AE81" s="23">
+      <c r="AE81" s="20">
         <f t="shared" si="6"/>
         <v>14.384079573787053</v>
       </c>
-      <c r="AF81" s="23">
+      <c r="AF81" s="20">
         <f t="shared" si="7"/>
         <v>2.3023435435885342</v>
       </c>
@@ -18227,22 +18227,22 @@
       <c r="X82" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z82" s="21">
+      <c r="Z82" s="18">
         <v>1478398</v>
       </c>
-      <c r="AB82" s="21">
+      <c r="AB82" s="18">
         <f t="shared" si="4"/>
         <v>417987</v>
       </c>
-      <c r="AC82" s="21">
+      <c r="AC82" s="18">
         <f t="shared" si="5"/>
         <v>155673</v>
       </c>
-      <c r="AE82" s="23">
+      <c r="AE82" s="20">
         <f t="shared" si="6"/>
         <v>28.272968442868564</v>
       </c>
-      <c r="AF82" s="23">
+      <c r="AF82" s="20">
         <f t="shared" si="7"/>
         <v>10.529843790373093</v>
       </c>
@@ -18318,22 +18318,22 @@
       <c r="X83" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z83" s="21">
+      <c r="Z83" s="18">
         <v>453416</v>
       </c>
-      <c r="AB83" s="21">
+      <c r="AB83" s="18">
         <f t="shared" si="4"/>
         <v>69271</v>
       </c>
-      <c r="AC83" s="21">
+      <c r="AC83" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE83" s="23">
+      <c r="AE83" s="20">
         <f t="shared" si="6"/>
         <v>15.277581735095366</v>
       </c>
-      <c r="AF83" s="23">
+      <c r="AF83" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -18409,22 +18409,22 @@
       <c r="X84" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z84" s="21">
+      <c r="Z84" s="18">
         <v>645121</v>
       </c>
-      <c r="AB84" s="21">
+      <c r="AB84" s="18">
         <f t="shared" si="4"/>
         <v>93289</v>
       </c>
-      <c r="AC84" s="21">
+      <c r="AC84" s="18">
         <f t="shared" si="5"/>
         <v>36466</v>
       </c>
-      <c r="AE84" s="23">
+      <c r="AE84" s="20">
         <f t="shared" si="6"/>
         <v>14.460698070594507</v>
       </c>
-      <c r="AF84" s="23">
+      <c r="AF84" s="20">
         <f t="shared" si="7"/>
         <v>5.652583003808588</v>
       </c>
@@ -18500,55 +18500,50 @@
       <c r="X85" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z85" s="21">
+      <c r="Z85" s="18">
         <v>1572214</v>
       </c>
-      <c r="AB85" s="21">
+      <c r="AB85" s="18">
         <f t="shared" si="4"/>
         <v>531288</v>
       </c>
-      <c r="AC85" s="21">
+      <c r="AC85" s="18">
         <f t="shared" si="5"/>
         <v>261645</v>
       </c>
-      <c r="AE85" s="23">
+      <c r="AE85" s="20">
         <f t="shared" si="6"/>
         <v>33.79234633453207</v>
       </c>
-      <c r="AF85" s="23">
+      <c r="AF85" s="20">
         <f t="shared" si="7"/>
         <v>16.641818480181449</v>
       </c>
     </row>
     <row r="87" spans="1:32">
-      <c r="Z87" s="21">
+      <c r="Z87" s="18">
         <f>SUM(Z5:Z85)</f>
         <v>115947114</v>
       </c>
-      <c r="AB87" s="21">
+      <c r="AB87" s="18">
         <f>SUM(AB5:AB85)</f>
         <v>36777843</v>
       </c>
-      <c r="AC87" s="21">
+      <c r="AC87" s="18">
         <f>SUM(AC5:AC85)</f>
         <v>10387372</v>
       </c>
-      <c r="AE87" s="23">
+      <c r="AE87" s="20">
         <f t="shared" ref="AE87" si="8">AB87/Z87*100</f>
         <v>31.719498425808169</v>
       </c>
-      <c r="AF87" s="23">
+      <c r="AF87" s="20">
         <f t="shared" ref="AF87" si="9">AC87/Z87*100</f>
         <v>8.9587154364187107</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="AB3:AC3"/>
     <mergeCell ref="AE3:AF3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:K2"/>
@@ -18560,6 +18555,11 @@
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="AB3:AC3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18589,95 +18589,95 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:32">
-      <c r="A2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="14" t="s">
+      <c r="A2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
     </row>
     <row r="3" spans="1:32">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14" t="s">
+      <c r="G3" s="25"/>
+      <c r="H3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14" t="s">
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="14" t="s">
+      <c r="K3" s="25"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14" t="s">
+      <c r="N3" s="25"/>
+      <c r="O3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14" t="s">
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14" t="s">
+      <c r="R3" s="25"/>
+      <c r="S3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14" t="s">
+      <c r="T3" s="25"/>
+      <c r="U3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14" t="s">
+      <c r="V3" s="25"/>
+      <c r="W3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="X3" s="14"/>
-      <c r="Z3" s="22" t="s">
+      <c r="X3" s="25"/>
+      <c r="Z3" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="AB3" s="25" t="s">
+      <c r="AB3" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="AC3" s="25"/>
-      <c r="AE3" s="25" t="s">
+      <c r="AC3" s="22"/>
+      <c r="AE3" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="AF3" s="25"/>
+      <c r="AF3" s="22"/>
     </row>
     <row r="4" spans="1:32">
       <c r="A4" s="1"/>
@@ -18711,7 +18711,7 @@
       <c r="K4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="16"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="2" t="s">
         <v>13</v>
       </c>
@@ -18748,19 +18748,19 @@
       <c r="X4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Z4" s="22" t="s">
+      <c r="Z4" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="AB4" s="22" t="s">
+      <c r="AB4" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="AC4" s="22" t="s">
+      <c r="AC4" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="AE4" s="22" t="s">
+      <c r="AE4" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="AF4" s="22" t="s">
+      <c r="AF4" s="19" t="s">
         <v>119</v>
       </c>
     </row>
@@ -18835,22 +18835,22 @@
       <c r="X5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z5" s="21">
+      <c r="Z5" s="18">
         <v>346536</v>
       </c>
-      <c r="AB5" s="21">
+      <c r="AB5" s="18">
         <f t="shared" ref="AB5:AB35" si="0">N(C5)+N(E5)+N(G5)+N(I5)+N(K5)+N(N5)+N(P5)+N(R5)+N(T5)+N(V5)+N(X5)</f>
         <v>34511</v>
       </c>
-      <c r="AC5" s="21">
+      <c r="AC5" s="18">
         <f t="shared" ref="AC5:AC35" si="1">N(I5)+N(K5)+N(X5)</f>
         <v>20882</v>
       </c>
-      <c r="AE5" s="23">
+      <c r="AE5" s="20">
         <f t="shared" ref="AE5:AE35" si="2">AB5/Z5*100</f>
         <v>9.9588498741833469</v>
       </c>
-      <c r="AF5" s="23">
+      <c r="AF5" s="20">
         <f t="shared" ref="AF5:AF35" si="3">AC5/Z5*100</f>
         <v>6.0259251564051066</v>
       </c>
@@ -18926,22 +18926,22 @@
       <c r="X6" s="9">
         <v>20725</v>
       </c>
-      <c r="Z6" s="21">
+      <c r="Z6" s="18">
         <v>1003542</v>
       </c>
-      <c r="AB6" s="21">
+      <c r="AB6" s="18">
         <f t="shared" si="0"/>
         <v>379273</v>
       </c>
-      <c r="AC6" s="21">
+      <c r="AC6" s="18">
         <f t="shared" si="1"/>
         <v>133605</v>
       </c>
-      <c r="AE6" s="23">
+      <c r="AE6" s="20">
         <f t="shared" si="2"/>
         <v>37.793435650924422</v>
       </c>
-      <c r="AF6" s="23">
+      <c r="AF6" s="20">
         <f t="shared" si="3"/>
         <v>13.313344135073567</v>
       </c>
@@ -19017,22 +19017,22 @@
       <c r="X7" s="9">
         <v>25233</v>
       </c>
-      <c r="Z7" s="21">
+      <c r="Z7" s="18">
         <v>1515691</v>
       </c>
-      <c r="AB7" s="21">
+      <c r="AB7" s="18">
         <f t="shared" si="0"/>
         <v>291442</v>
       </c>
-      <c r="AC7" s="21">
+      <c r="AC7" s="18">
         <f t="shared" si="1"/>
         <v>107920</v>
       </c>
-      <c r="AE7" s="23">
+      <c r="AE7" s="20">
         <f t="shared" si="2"/>
         <v>19.228325562400254</v>
       </c>
-      <c r="AF7" s="23">
+      <c r="AF7" s="20">
         <f t="shared" si="3"/>
         <v>7.1201847870047397</v>
       </c>
@@ -19108,22 +19108,22 @@
       <c r="X8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z8" s="21">
+      <c r="Z8" s="18">
         <v>1341785</v>
       </c>
-      <c r="AB8" s="21">
+      <c r="AB8" s="18">
         <f t="shared" si="0"/>
         <v>60820</v>
       </c>
-      <c r="AC8" s="21">
+      <c r="AC8" s="18">
         <f t="shared" si="1"/>
         <v>27705</v>
       </c>
-      <c r="AE8" s="23">
+      <c r="AE8" s="20">
         <f t="shared" si="2"/>
         <v>4.5327679173638096</v>
       </c>
-      <c r="AF8" s="23">
+      <c r="AF8" s="20">
         <f t="shared" si="3"/>
         <v>2.0647868324657077</v>
       </c>
@@ -19199,22 +19199,22 @@
       <c r="X9" s="6">
         <v>23443</v>
       </c>
-      <c r="Z9" s="21">
+      <c r="Z9" s="18">
         <v>2531253</v>
       </c>
-      <c r="AB9" s="21">
+      <c r="AB9" s="18">
         <f t="shared" si="0"/>
         <v>1403609</v>
       </c>
-      <c r="AC9" s="21">
+      <c r="AC9" s="18">
         <f t="shared" si="1"/>
         <v>125025</v>
       </c>
-      <c r="AE9" s="23">
+      <c r="AE9" s="20">
         <f t="shared" si="2"/>
         <v>55.451154033200154</v>
       </c>
-      <c r="AF9" s="23">
+      <c r="AF9" s="20">
         <f t="shared" si="3"/>
         <v>4.939253405329298</v>
       </c>
@@ -19290,22 +19290,22 @@
       <c r="X10" s="9">
         <v>62695</v>
       </c>
-      <c r="Z10" s="21">
+      <c r="Z10" s="18">
         <v>3030831</v>
       </c>
-      <c r="AB10" s="21">
+      <c r="AB10" s="18">
         <f t="shared" si="0"/>
         <v>204957</v>
       </c>
-      <c r="AC10" s="21">
+      <c r="AC10" s="18">
         <f t="shared" si="1"/>
         <v>109101</v>
       </c>
-      <c r="AE10" s="23">
+      <c r="AE10" s="20">
         <f t="shared" si="2"/>
         <v>6.7624027865624976</v>
       </c>
-      <c r="AF10" s="23">
+      <c r="AF10" s="20">
         <f t="shared" si="3"/>
         <v>3.5997058232544141</v>
       </c>
@@ -19381,22 +19381,22 @@
       <c r="X11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z11" s="21">
+      <c r="Z11" s="18">
         <v>2564238</v>
       </c>
-      <c r="AB11" s="21">
+      <c r="AB11" s="18">
         <f t="shared" si="0"/>
         <v>869026</v>
       </c>
-      <c r="AC11" s="21">
+      <c r="AC11" s="18">
         <f t="shared" si="1"/>
         <v>251303</v>
       </c>
-      <c r="AE11" s="23">
+      <c r="AE11" s="20">
         <f t="shared" si="2"/>
         <v>33.890223918372634</v>
       </c>
-      <c r="AF11" s="23">
+      <c r="AF11" s="20">
         <f t="shared" si="3"/>
         <v>9.80029934818843</v>
       </c>
@@ -19472,22 +19472,22 @@
       <c r="X12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z12" s="21">
+      <c r="Z12" s="18">
         <v>2170665</v>
       </c>
-      <c r="AB12" s="21">
+      <c r="AB12" s="18">
         <f t="shared" si="0"/>
         <v>348680</v>
       </c>
-      <c r="AC12" s="21">
+      <c r="AC12" s="18">
         <f t="shared" si="1"/>
         <v>150063</v>
       </c>
-      <c r="AE12" s="23">
+      <c r="AE12" s="20">
         <f t="shared" si="2"/>
         <v>16.063280146867434</v>
       </c>
-      <c r="AF12" s="23">
+      <c r="AF12" s="20">
         <f t="shared" si="3"/>
         <v>6.9132270525391988</v>
       </c>
@@ -19563,22 +19563,22 @@
       <c r="X13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z13" s="21">
+      <c r="Z13" s="18">
         <v>1132843</v>
       </c>
-      <c r="AB13" s="21">
+      <c r="AB13" s="18">
         <f t="shared" si="0"/>
         <v>139422</v>
       </c>
-      <c r="AC13" s="21">
+      <c r="AC13" s="18">
         <f t="shared" si="1"/>
         <v>49513</v>
       </c>
-      <c r="AE13" s="23">
+      <c r="AE13" s="20">
         <f t="shared" si="2"/>
         <v>12.307265878855233</v>
       </c>
-      <c r="AF13" s="23">
+      <c r="AF13" s="20">
         <f t="shared" si="3"/>
         <v>4.370685081692697</v>
       </c>
@@ -19654,22 +19654,22 @@
       <c r="X14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z14" s="21">
+      <c r="Z14" s="18">
         <v>1387015</v>
       </c>
-      <c r="AB14" s="21">
+      <c r="AB14" s="18">
         <f t="shared" si="0"/>
         <v>105548</v>
       </c>
-      <c r="AC14" s="21">
+      <c r="AC14" s="18">
         <f t="shared" si="1"/>
         <v>41336</v>
       </c>
-      <c r="AE14" s="23">
+      <c r="AE14" s="20">
         <f t="shared" si="2"/>
         <v>7.6097230383233061</v>
       </c>
-      <c r="AF14" s="23">
+      <c r="AF14" s="20">
         <f t="shared" si="3"/>
         <v>2.9802129032490634</v>
       </c>
@@ -19745,22 +19745,22 @@
       <c r="X15" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="18">
         <v>2371012</v>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="18">
         <f t="shared" si="0"/>
         <v>786493</v>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="18">
         <f t="shared" si="1"/>
         <v>102285</v>
       </c>
-      <c r="AE15" s="23">
+      <c r="AE15" s="20">
         <f t="shared" si="2"/>
         <v>33.171194409813189</v>
       </c>
-      <c r="AF15" s="23">
+      <c r="AF15" s="20">
         <f t="shared" si="3"/>
         <v>4.3139806968501215</v>
       </c>
@@ -19836,22 +19836,22 @@
       <c r="X16" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z16" s="21">
+      <c r="Z16" s="18">
         <v>2430581</v>
       </c>
-      <c r="AB16" s="21">
+      <c r="AB16" s="18">
         <f t="shared" si="0"/>
         <v>1250685</v>
       </c>
-      <c r="AC16" s="21">
+      <c r="AC16" s="18">
         <f t="shared" si="1"/>
         <v>1089439</v>
       </c>
-      <c r="AE16" s="23">
+      <c r="AE16" s="20">
         <f t="shared" si="2"/>
         <v>51.456215612645707</v>
       </c>
-      <c r="AF16" s="23">
+      <c r="AF16" s="20">
         <f t="shared" si="3"/>
         <v>44.822163918832572</v>
       </c>
@@ -19927,22 +19927,22 @@
       <c r="X17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z17" s="21">
+      <c r="Z17" s="18">
         <v>1584774</v>
       </c>
-      <c r="AB17" s="21">
+      <c r="AB17" s="18">
         <f t="shared" si="0"/>
         <v>373629</v>
       </c>
-      <c r="AC17" s="21">
+      <c r="AC17" s="18">
         <f t="shared" si="1"/>
         <v>90053</v>
       </c>
-      <c r="AE17" s="23">
+      <c r="AE17" s="20">
         <f t="shared" si="2"/>
         <v>23.57616922034309</v>
       </c>
-      <c r="AF17" s="23">
+      <c r="AF17" s="20">
         <f t="shared" si="3"/>
         <v>5.6823875202394794</v>
       </c>
@@ -20018,22 +20018,22 @@
       <c r="X18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z18" s="21">
+      <c r="Z18" s="18">
         <v>1367022</v>
       </c>
-      <c r="AB18" s="21">
+      <c r="AB18" s="18">
         <f t="shared" si="0"/>
         <v>96784</v>
       </c>
-      <c r="AC18" s="21">
+      <c r="AC18" s="18">
         <f t="shared" si="1"/>
         <v>25736</v>
       </c>
-      <c r="AE18" s="23">
+      <c r="AE18" s="20">
         <f t="shared" si="2"/>
         <v>7.0799153195778857</v>
       </c>
-      <c r="AF18" s="23">
+      <c r="AF18" s="20">
         <f t="shared" si="3"/>
         <v>1.8826324667781498</v>
       </c>
@@ -20109,22 +20109,22 @@
       <c r="X19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z19" s="21">
+      <c r="Z19" s="18">
         <v>364156</v>
       </c>
-      <c r="AB19" s="21">
+      <c r="AB19" s="18">
         <f t="shared" si="0"/>
         <v>20081</v>
       </c>
-      <c r="AC19" s="21">
+      <c r="AC19" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE19" s="23">
+      <c r="AE19" s="20">
         <f t="shared" si="2"/>
         <v>5.5143949296455368</v>
       </c>
-      <c r="AF19" s="23">
+      <c r="AF19" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -20200,22 +20200,22 @@
       <c r="X20" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z20" s="21">
+      <c r="Z20" s="18">
         <v>1600145</v>
       </c>
-      <c r="AB20" s="21">
+      <c r="AB20" s="18">
         <f t="shared" si="0"/>
         <v>505763</v>
       </c>
-      <c r="AC20" s="21">
+      <c r="AC20" s="18">
         <f t="shared" si="1"/>
         <v>95724</v>
       </c>
-      <c r="AE20" s="23">
+      <c r="AE20" s="20">
         <f t="shared" si="2"/>
         <v>31.6073230863453</v>
       </c>
-      <c r="AF20" s="23">
+      <c r="AF20" s="20">
         <f t="shared" si="3"/>
         <v>5.9822078624124693</v>
       </c>
@@ -20291,22 +20291,22 @@
       <c r="X21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z21" s="21">
+      <c r="Z21" s="18">
         <v>2033798</v>
       </c>
-      <c r="AB21" s="21">
+      <c r="AB21" s="18">
         <f t="shared" si="0"/>
         <v>409024</v>
       </c>
-      <c r="AC21" s="21">
+      <c r="AC21" s="18">
         <f t="shared" si="1"/>
         <v>183366</v>
       </c>
-      <c r="AE21" s="23">
+      <c r="AE21" s="20">
         <f t="shared" si="2"/>
         <v>20.111338490843238</v>
       </c>
-      <c r="AF21" s="23">
+      <c r="AF21" s="20">
         <f t="shared" si="3"/>
         <v>9.0159396360897208</v>
       </c>
@@ -20382,22 +20382,22 @@
       <c r="X22" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z22" s="21">
+      <c r="Z22" s="18">
         <v>1470474</v>
       </c>
-      <c r="AB22" s="21">
+      <c r="AB22" s="18">
         <f t="shared" si="0"/>
         <v>424107</v>
       </c>
-      <c r="AC22" s="21">
+      <c r="AC22" s="18">
         <f t="shared" si="1"/>
         <v>59981</v>
       </c>
-      <c r="AE22" s="23">
+      <c r="AE22" s="20">
         <f t="shared" si="2"/>
         <v>28.84151640899465</v>
       </c>
-      <c r="AF22" s="23">
+      <c r="AF22" s="20">
         <f t="shared" si="3"/>
         <v>4.07902485865102</v>
       </c>
@@ -20473,22 +20473,22 @@
       <c r="X23" s="6">
         <v>31449</v>
       </c>
-      <c r="Z23" s="21">
+      <c r="Z23" s="18">
         <v>2994302</v>
       </c>
-      <c r="AB23" s="21">
+      <c r="AB23" s="18">
         <f t="shared" si="0"/>
         <v>805487</v>
       </c>
-      <c r="AC23" s="21">
+      <c r="AC23" s="18">
         <f t="shared" si="1"/>
         <v>139955</v>
       </c>
-      <c r="AE23" s="23">
+      <c r="AE23" s="20">
         <f t="shared" si="2"/>
         <v>26.900659986868391</v>
       </c>
-      <c r="AF23" s="23">
+      <c r="AF23" s="20">
         <f t="shared" si="3"/>
         <v>4.6740442346830742</v>
       </c>
@@ -20564,22 +20564,22 @@
       <c r="X24" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z24" s="21">
+      <c r="Z24" s="18">
         <v>1122317</v>
       </c>
-      <c r="AB24" s="21">
+      <c r="AB24" s="18">
         <f t="shared" si="0"/>
         <v>79661</v>
       </c>
-      <c r="AC24" s="21">
+      <c r="AC24" s="18">
         <f t="shared" si="1"/>
         <v>30478</v>
       </c>
-      <c r="AE24" s="23">
+      <c r="AE24" s="20">
         <f t="shared" si="2"/>
         <v>7.0979054937241433</v>
       </c>
-      <c r="AF24" s="23">
+      <c r="AF24" s="20">
         <f t="shared" si="3"/>
         <v>2.7156320362250597</v>
       </c>
@@ -20655,22 +20655,22 @@
       <c r="X25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z25" s="21">
+      <c r="Z25" s="18">
         <v>1802196</v>
       </c>
-      <c r="AB25" s="21">
+      <c r="AB25" s="18">
         <f t="shared" si="0"/>
         <v>524434</v>
       </c>
-      <c r="AC25" s="21">
+      <c r="AC25" s="18">
         <f t="shared" si="1"/>
         <v>46122</v>
       </c>
-      <c r="AE25" s="23">
+      <c r="AE25" s="20">
         <f t="shared" si="2"/>
         <v>29.099720563135197</v>
       </c>
-      <c r="AF25" s="23">
+      <c r="AF25" s="20">
         <f t="shared" si="3"/>
         <v>2.5592110957964613</v>
       </c>
@@ -20746,22 +20746,22 @@
       <c r="X26" s="9">
         <v>21599</v>
       </c>
-      <c r="Z26" s="21">
+      <c r="Z26" s="18">
         <v>2751336</v>
       </c>
-      <c r="AB26" s="21">
+      <c r="AB26" s="18">
         <f t="shared" si="0"/>
         <v>1301224</v>
       </c>
-      <c r="AC26" s="21">
+      <c r="AC26" s="18">
         <f t="shared" si="1"/>
         <v>111598</v>
       </c>
-      <c r="AE26" s="23">
+      <c r="AE26" s="20">
         <f t="shared" si="2"/>
         <v>47.294259952255921</v>
       </c>
-      <c r="AF26" s="23">
+      <c r="AF26" s="20">
         <f t="shared" si="3"/>
         <v>4.0561385450559291</v>
       </c>
@@ -20837,22 +20837,22 @@
       <c r="X27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z27" s="21">
+      <c r="Z27" s="18">
         <v>2112033</v>
       </c>
-      <c r="AB27" s="21">
+      <c r="AB27" s="18">
         <f t="shared" si="0"/>
         <v>1459959</v>
       </c>
-      <c r="AC27" s="21">
+      <c r="AC27" s="18">
         <f t="shared" si="1"/>
         <v>1346925</v>
       </c>
-      <c r="AE27" s="23">
+      <c r="AE27" s="20">
         <f t="shared" si="2"/>
         <v>69.125766500807515</v>
       </c>
-      <c r="AF27" s="23">
+      <c r="AF27" s="20">
         <f t="shared" si="3"/>
         <v>63.773861487959707</v>
       </c>
@@ -20928,22 +20928,22 @@
       <c r="X28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z28" s="21">
+      <c r="Z28" s="18">
         <v>2405829</v>
       </c>
-      <c r="AB28" s="21">
+      <c r="AB28" s="18">
         <f t="shared" si="0"/>
         <v>1173209</v>
       </c>
-      <c r="AC28" s="21">
+      <c r="AC28" s="18">
         <f t="shared" si="1"/>
         <v>239864</v>
       </c>
-      <c r="AE28" s="23">
+      <c r="AE28" s="20">
         <f t="shared" si="2"/>
         <v>48.76526968458689</v>
       </c>
-      <c r="AF28" s="23">
+      <c r="AF28" s="20">
         <f t="shared" si="3"/>
         <v>9.9701184082492986</v>
       </c>
@@ -21019,22 +21019,22 @@
       <c r="X29" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z29" s="21">
+      <c r="Z29" s="18">
         <v>1527848</v>
       </c>
-      <c r="AB29" s="21">
+      <c r="AB29" s="18">
         <f t="shared" si="0"/>
         <v>490204</v>
       </c>
-      <c r="AC29" s="21">
+      <c r="AC29" s="18">
         <f t="shared" si="1"/>
         <v>74067</v>
       </c>
-      <c r="AE29" s="23">
+      <c r="AE29" s="20">
         <f t="shared" si="2"/>
         <v>32.084605274870277</v>
       </c>
-      <c r="AF29" s="23">
+      <c r="AF29" s="20">
         <f t="shared" si="3"/>
         <v>4.8477989957116154</v>
       </c>
@@ -21110,22 +21110,22 @@
       <c r="X30" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z30" s="21">
+      <c r="Z30" s="18">
         <v>1525279</v>
       </c>
-      <c r="AB30" s="21">
+      <c r="AB30" s="18">
         <f t="shared" si="0"/>
         <v>126656</v>
       </c>
-      <c r="AC30" s="21">
+      <c r="AC30" s="18">
         <f t="shared" si="1"/>
         <v>46699</v>
       </c>
-      <c r="AE30" s="23">
+      <c r="AE30" s="20">
         <f t="shared" si="2"/>
         <v>8.3037922898040293</v>
       </c>
-      <c r="AF30" s="23">
+      <c r="AF30" s="20">
         <f t="shared" si="3"/>
         <v>3.0616693732753153</v>
       </c>
@@ -21201,22 +21201,22 @@
       <c r="X31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z31" s="21">
+      <c r="Z31" s="18">
         <v>2684030</v>
       </c>
-      <c r="AB31" s="21">
+      <c r="AB31" s="18">
         <f t="shared" si="0"/>
         <v>1162054</v>
       </c>
-      <c r="AC31" s="21">
+      <c r="AC31" s="18">
         <f t="shared" si="1"/>
         <v>157603</v>
       </c>
-      <c r="AE31" s="23">
+      <c r="AE31" s="20">
         <f t="shared" si="2"/>
         <v>43.295119652164843</v>
       </c>
-      <c r="AF31" s="23">
+      <c r="AF31" s="20">
         <f t="shared" si="3"/>
         <v>5.8718792263871871</v>
       </c>
@@ -21292,22 +21292,22 @@
       <c r="X32" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z32" s="21">
+      <c r="Z32" s="18">
         <v>1769135</v>
       </c>
-      <c r="AB32" s="21">
+      <c r="AB32" s="18">
         <f t="shared" si="0"/>
         <v>164289</v>
       </c>
-      <c r="AC32" s="21">
+      <c r="AC32" s="18">
         <f t="shared" si="1"/>
         <v>74809</v>
       </c>
-      <c r="AE32" s="23">
+      <c r="AE32" s="20">
         <f t="shared" si="2"/>
         <v>9.2864026770144736</v>
       </c>
-      <c r="AF32" s="23">
+      <c r="AF32" s="20">
         <f t="shared" si="3"/>
         <v>4.2285636765990162</v>
       </c>
@@ -21383,22 +21383,22 @@
       <c r="X33" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z33" s="21">
+      <c r="Z33" s="18">
         <v>1419456</v>
       </c>
-      <c r="AB33" s="21">
+      <c r="AB33" s="18">
         <f t="shared" si="0"/>
         <v>262198</v>
       </c>
-      <c r="AC33" s="21">
+      <c r="AC33" s="18">
         <f t="shared" si="1"/>
         <v>114733</v>
       </c>
-      <c r="AE33" s="23">
+      <c r="AE33" s="20">
         <f t="shared" si="2"/>
         <v>18.471724378916992</v>
       </c>
-      <c r="AF33" s="23">
+      <c r="AF33" s="20">
         <f t="shared" si="3"/>
         <v>8.0828852743586275</v>
       </c>
@@ -21474,22 +21474,22 @@
       <c r="X34" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z34" s="21">
+      <c r="Z34" s="18">
         <v>2196642</v>
       </c>
-      <c r="AB34" s="21">
+      <c r="AB34" s="18">
         <f t="shared" si="0"/>
         <v>350444</v>
       </c>
-      <c r="AC34" s="21">
+      <c r="AC34" s="18">
         <f t="shared" si="1"/>
         <v>69777</v>
       </c>
-      <c r="AE34" s="23">
+      <c r="AE34" s="20">
         <f t="shared" si="2"/>
         <v>15.953623758445845</v>
       </c>
-      <c r="AF34" s="23">
+      <c r="AF34" s="20">
         <f t="shared" si="3"/>
         <v>3.1765303586110072</v>
       </c>
@@ -21565,22 +21565,22 @@
       <c r="X35" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z35" s="21">
+      <c r="Z35" s="18">
         <v>1071355</v>
       </c>
-      <c r="AB35" s="21">
+      <c r="AB35" s="18">
         <f t="shared" si="0"/>
         <v>159952</v>
       </c>
-      <c r="AC35" s="21">
+      <c r="AC35" s="18">
         <f t="shared" si="1"/>
         <v>96906</v>
       </c>
-      <c r="AE35" s="23">
+      <c r="AE35" s="20">
         <f t="shared" si="2"/>
         <v>14.929878518324923</v>
       </c>
-      <c r="AF35" s="23">
+      <c r="AF35" s="20">
         <f t="shared" si="3"/>
         <v>9.0451811024357003</v>
       </c>
@@ -21610,10 +21610,10 @@
       <c r="V36" s="10"/>
       <c r="W36" s="10"/>
       <c r="X36" s="10"/>
-      <c r="AB36" s="21"/>
-      <c r="AC36" s="21"/>
-      <c r="AE36" s="23"/>
-      <c r="AF36" s="23"/>
+      <c r="AB36" s="18"/>
+      <c r="AC36" s="18"/>
+      <c r="AE36" s="20"/>
+      <c r="AF36" s="20"/>
     </row>
     <row r="37" spans="1:32">
       <c r="A37" s="8" t="s">
@@ -21686,22 +21686,22 @@
       <c r="X37" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z37" s="21">
+      <c r="Z37" s="18">
         <v>571154</v>
       </c>
-      <c r="AB37" s="21">
+      <c r="AB37" s="18">
         <f t="shared" ref="AB37:AB51" si="4">N(C37)+N(E37)+N(G37)+N(I37)+N(K37)+N(N37)+N(P37)+N(R37)+N(T37)+N(V37)+N(X37)</f>
         <v>113197</v>
       </c>
-      <c r="AC37" s="21">
+      <c r="AC37" s="18">
         <f t="shared" ref="AC37:AC51" si="5">N(I37)+N(K37)+N(X37)</f>
         <v>0</v>
       </c>
-      <c r="AE37" s="23">
+      <c r="AE37" s="20">
         <f t="shared" ref="AE37:AE51" si="6">AB37/Z37*100</f>
         <v>19.81899802855272</v>
       </c>
-      <c r="AF37" s="23">
+      <c r="AF37" s="20">
         <f t="shared" ref="AF37:AF51" si="7">AC37/Z37*100</f>
         <v>0</v>
       </c>
@@ -21777,22 +21777,22 @@
       <c r="X38" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z38" s="21">
+      <c r="Z38" s="18">
         <v>1918881</v>
       </c>
-      <c r="AB38" s="21">
+      <c r="AB38" s="18">
         <f t="shared" si="4"/>
         <v>1444278</v>
       </c>
-      <c r="AC38" s="21">
+      <c r="AC38" s="18">
         <f t="shared" si="5"/>
         <v>135347</v>
       </c>
-      <c r="AE38" s="23">
+      <c r="AE38" s="20">
         <f t="shared" si="6"/>
         <v>75.266678861273846</v>
       </c>
-      <c r="AF38" s="23">
+      <c r="AF38" s="20">
         <f t="shared" si="7"/>
         <v>7.0534337460217698</v>
       </c>
@@ -21868,22 +21868,22 @@
       <c r="X39" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z39" s="21">
+      <c r="Z39" s="18">
         <v>873301</v>
       </c>
-      <c r="AB39" s="21">
+      <c r="AB39" s="18">
         <f t="shared" si="4"/>
         <v>749856</v>
       </c>
-      <c r="AC39" s="21">
+      <c r="AC39" s="18">
         <f t="shared" si="5"/>
         <v>41590</v>
       </c>
-      <c r="AE39" s="23">
+      <c r="AE39" s="20">
         <f t="shared" si="6"/>
         <v>85.864553000626358</v>
       </c>
-      <c r="AF39" s="23">
+      <c r="AF39" s="20">
         <f t="shared" si="7"/>
         <v>4.7623900579525271</v>
       </c>
@@ -21959,22 +21959,22 @@
       <c r="X40" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z40" s="21">
+      <c r="Z40" s="18">
         <v>933936</v>
       </c>
-      <c r="AB40" s="21">
+      <c r="AB40" s="18">
         <f t="shared" si="4"/>
         <v>485817</v>
       </c>
-      <c r="AC40" s="21">
+      <c r="AC40" s="18">
         <f t="shared" si="5"/>
         <v>43740</v>
       </c>
-      <c r="AE40" s="23">
+      <c r="AE40" s="20">
         <f t="shared" si="6"/>
         <v>52.018232512720353</v>
       </c>
-      <c r="AF40" s="23">
+      <c r="AF40" s="20">
         <f t="shared" si="7"/>
         <v>4.6834044302821605</v>
       </c>
@@ -22050,22 +22050,22 @@
       <c r="X41" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z41" s="21">
+      <c r="Z41" s="18">
         <v>57478</v>
       </c>
-      <c r="AB41" s="21">
+      <c r="AB41" s="18">
         <f t="shared" si="4"/>
         <v>21742</v>
       </c>
-      <c r="AC41" s="21">
+      <c r="AC41" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE41" s="23">
+      <c r="AE41" s="20">
         <f t="shared" si="6"/>
         <v>37.82664671700477</v>
       </c>
-      <c r="AF41" s="23">
+      <c r="AF41" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -22095,10 +22095,10 @@
       <c r="V42" s="7"/>
       <c r="W42" s="7"/>
       <c r="X42" s="7"/>
-      <c r="AB42" s="21"/>
-      <c r="AC42" s="21"/>
-      <c r="AE42" s="23"/>
-      <c r="AF42" s="23"/>
+      <c r="AB42" s="18"/>
+      <c r="AC42" s="18"/>
+      <c r="AE42" s="20"/>
+      <c r="AF42" s="20"/>
     </row>
     <row r="43" spans="1:32">
       <c r="A43" s="5" t="s">
@@ -22171,22 +22171,22 @@
       <c r="X43" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z43" s="21">
+      <c r="Z43" s="18">
         <v>120306</v>
       </c>
-      <c r="AB43" s="21">
+      <c r="AB43" s="18">
         <f t="shared" si="4"/>
         <v>35871</v>
       </c>
-      <c r="AC43" s="21">
+      <c r="AC43" s="18">
         <f t="shared" si="5"/>
         <v>32834</v>
       </c>
-      <c r="AE43" s="23">
+      <c r="AE43" s="20">
         <f t="shared" si="6"/>
         <v>29.816468006583214</v>
       </c>
-      <c r="AF43" s="23">
+      <c r="AF43" s="20">
         <f t="shared" si="7"/>
         <v>27.292071883364088</v>
       </c>
@@ -22262,22 +22262,22 @@
       <c r="X44" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z44" s="21">
+      <c r="Z44" s="18">
         <v>570161</v>
       </c>
-      <c r="AB44" s="21">
+      <c r="AB44" s="18">
         <f t="shared" si="4"/>
         <v>78535</v>
       </c>
-      <c r="AC44" s="21">
+      <c r="AC44" s="18">
         <f t="shared" si="5"/>
         <v>26699</v>
       </c>
-      <c r="AE44" s="23">
+      <c r="AE44" s="20">
         <f t="shared" si="6"/>
         <v>13.774179573839671</v>
       </c>
-      <c r="AF44" s="23">
+      <c r="AF44" s="20">
         <f t="shared" si="7"/>
         <v>4.6827124268408395</v>
       </c>
@@ -22353,22 +22353,22 @@
       <c r="X45" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z45" s="21">
+      <c r="Z45" s="18">
         <v>672037</v>
       </c>
-      <c r="AB45" s="21">
+      <c r="AB45" s="18">
         <f t="shared" si="4"/>
         <v>80764</v>
       </c>
-      <c r="AC45" s="21">
+      <c r="AC45" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE45" s="23">
+      <c r="AE45" s="20">
         <f t="shared" si="6"/>
         <v>12.017790687119906</v>
       </c>
-      <c r="AF45" s="23">
+      <c r="AF45" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -22444,22 +22444,22 @@
       <c r="X46" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z46" s="21">
+      <c r="Z46" s="18">
         <v>514267</v>
       </c>
-      <c r="AB46" s="21">
+      <c r="AB46" s="18">
         <f t="shared" si="4"/>
         <v>107104</v>
       </c>
-      <c r="AC46" s="21">
+      <c r="AC46" s="18">
         <f t="shared" si="5"/>
         <v>51473</v>
       </c>
-      <c r="AE46" s="23">
+      <c r="AE46" s="20">
         <f t="shared" si="6"/>
         <v>20.826535632268843</v>
       </c>
-      <c r="AF46" s="23">
+      <c r="AF46" s="20">
         <f t="shared" si="7"/>
         <v>10.009003105390779</v>
       </c>
@@ -22535,22 +22535,22 @@
       <c r="X47" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z47" s="21">
+      <c r="Z47" s="18">
         <v>223336</v>
       </c>
-      <c r="AB47" s="21">
+      <c r="AB47" s="18">
         <f t="shared" si="4"/>
         <v>67647</v>
       </c>
-      <c r="AC47" s="21">
+      <c r="AC47" s="18">
         <f t="shared" si="5"/>
         <v>28933</v>
       </c>
-      <c r="AE47" s="23">
+      <c r="AE47" s="20">
         <f t="shared" si="6"/>
         <v>30.289339828778161</v>
       </c>
-      <c r="AF47" s="23">
+      <c r="AF47" s="20">
         <f t="shared" si="7"/>
         <v>12.954919941254433</v>
       </c>
@@ -22626,22 +22626,22 @@
       <c r="X48" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z48" s="21">
+      <c r="Z48" s="18">
         <v>28113</v>
       </c>
-      <c r="AB48" s="21">
+      <c r="AB48" s="18">
         <f t="shared" si="4"/>
         <v>6893</v>
       </c>
-      <c r="AC48" s="21">
+      <c r="AC48" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE48" s="23">
+      <c r="AE48" s="20">
         <f t="shared" si="6"/>
         <v>24.518905844271334</v>
       </c>
-      <c r="AF48" s="23">
+      <c r="AF48" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -22717,22 +22717,22 @@
       <c r="X49" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z49" s="21">
+      <c r="Z49" s="18">
         <v>1433043</v>
       </c>
-      <c r="AB49" s="21">
+      <c r="AB49" s="18">
         <f t="shared" si="4"/>
         <v>105371</v>
       </c>
-      <c r="AC49" s="21">
+      <c r="AC49" s="18">
         <f t="shared" si="5"/>
         <v>49969</v>
       </c>
-      <c r="AE49" s="23">
+      <c r="AE49" s="20">
         <f t="shared" si="6"/>
         <v>7.3529545170661308</v>
       </c>
-      <c r="AF49" s="23">
+      <c r="AF49" s="20">
         <f t="shared" si="7"/>
         <v>3.4869156054633392</v>
       </c>
@@ -22808,22 +22808,22 @@
       <c r="X50" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="Z50" s="21">
+      <c r="Z50" s="18">
         <v>1927679</v>
       </c>
-      <c r="AB50" s="21">
+      <c r="AB50" s="18">
         <f t="shared" si="4"/>
         <v>455183</v>
       </c>
-      <c r="AC50" s="21">
+      <c r="AC50" s="18">
         <f t="shared" si="5"/>
         <v>73283</v>
       </c>
-      <c r="AE50" s="23">
+      <c r="AE50" s="20">
         <f t="shared" si="6"/>
         <v>23.613008182378913</v>
       </c>
-      <c r="AF50" s="23">
+      <c r="AF50" s="20">
         <f t="shared" si="7"/>
         <v>3.8016184229843248</v>
       </c>
@@ -22899,22 +22899,22 @@
       <c r="X51" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="Z51" s="21">
+      <c r="Z51" s="18">
         <v>269880</v>
       </c>
-      <c r="AB51" s="21">
+      <c r="AB51" s="18">
         <f t="shared" si="4"/>
         <v>6535</v>
       </c>
-      <c r="AC51" s="21">
+      <c r="AC51" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE51" s="23">
+      <c r="AE51" s="20">
         <f t="shared" si="6"/>
         <v>2.421446568845413</v>
       </c>
-      <c r="AF51" s="23">
+      <c r="AF51" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -22944,48 +22944,43 @@
       <c r="V52" s="7"/>
       <c r="W52" s="7"/>
       <c r="X52" s="7"/>
-      <c r="Z52" s="21"/>
-      <c r="AB52" s="21"/>
-      <c r="AC52" s="21"/>
-      <c r="AE52" s="23"/>
-      <c r="AF52" s="23"/>
+      <c r="Z52" s="18"/>
+      <c r="AB52" s="18"/>
+      <c r="AC52" s="18"/>
+      <c r="AE52" s="20"/>
+      <c r="AF52" s="20"/>
     </row>
     <row r="53" spans="1:32">
-      <c r="Z53" s="21">
+      <c r="Z53" s="18">
         <f>SUM(Z5:Z51)</f>
         <v>65741691</v>
       </c>
-      <c r="AB53" s="21">
+      <c r="AB53" s="18">
         <f>SUM(AB5:AB51)</f>
         <v>19522418</v>
       </c>
-      <c r="AC53" s="21">
+      <c r="AC53" s="18">
         <f>SUM(AC5:AC51)</f>
         <v>5696441</v>
       </c>
-      <c r="AE53" s="23">
+      <c r="AE53" s="20">
         <f t="shared" ref="AE53" si="8">AB53/Z53*100</f>
         <v>29.695643210637829</v>
       </c>
-      <c r="AF53" s="23">
+      <c r="AF53" s="20">
         <f t="shared" ref="AF53" si="9">AC53/Z53*100</f>
         <v>8.6648835972290392</v>
       </c>
     </row>
     <row r="54" spans="1:32">
-      <c r="Z54" s="21"/>
-      <c r="AB54" s="21"/>
-      <c r="AC54" s="21"/>
-      <c r="AE54" s="23"/>
-      <c r="AF54" s="23"/>
+      <c r="Z54" s="18"/>
+      <c r="AB54" s="18"/>
+      <c r="AC54" s="18"/>
+      <c r="AE54" s="20"/>
+      <c r="AF54" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="AB3:AC3"/>
     <mergeCell ref="AE3:AF3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:K2"/>
@@ -22997,6 +22992,11 @@
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="AB3:AC3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
